--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:R184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -429,16 +429,18 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,50 +476,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Ultimo post Facebook</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ultimo post Instagram</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Ultima revisione Google</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ultima revisione The Fork</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Ultima revisione Tripadvisor</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Orari apertura</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Orari chiusura</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Social attivo?</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Menzioni notizie</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Note aggiuntive</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Data verifica</t>
         </is>
@@ -549,52 +561,52 @@
           <t>andreaaprea_official</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Solo cena mer-sab</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Dom, Lun, Mar</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Si (Michelin 2026 2 stelle)</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2 stelle Michelin. Fondazione Rovati.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -626,52 +638,52 @@
           <t>autem_milano</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Mar; mer pranzo</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Si (Michelin 2026 1 stella)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1 stella Michelin. Chef Luca Natalini.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -708,52 +720,52 @@
           <t>eugenio_boer</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Lun e Mar; pranzo mer-ven</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Si (Gambero Rosso, Passione Gourmet)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Chef Eugenio Boer.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -790,32 +802,32 @@
           <t>contrastemilano_</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Chef Matias Perdomo.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -837,42 +849,42 @@
           <t>02/36517496</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>12:30, 19:00</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>14:30, 21:45</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1 stella + Stella Verde Michelin 2026. Chef Niederkofler.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -909,42 +921,42 @@
           <t>aimoenadia</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>12:00 (lun-ven), 19:00 (lun-sab)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>15:00 (lun-ven), 24:00</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Chef Negrini e Pisani.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -981,32 +993,32 @@
           <t>joiaaltacucinavegetariana</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Vegetariano. Nuovi chef Ricci e Minghini.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1043,32 +1055,32 @@
           <t>morellimilano</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Chef Giancarlo Morelli. Hotel Viu.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1105,32 +1117,32 @@
           <t>ristorantebertonmilano</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1155,24 +1167,26 @@
       <c r="D11" s="1" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr"/>
+      <c r="P11" s="1" t="inlineStr"/>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1209,32 +1223,32 @@
           <t>setaatmandarinoriental</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2 stelle Michelin 2026. Hotel Mandarin Oriental.</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1271,32 +1285,32 @@
           <t>sine_bydipinto</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026.</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1333,24 +1347,26 @@
           <t>versoristorante</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
-      <c r="I14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="O14" s="1" t="inlineStr"/>
+      <c r="P14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1387,52 +1403,52 @@
           <t>28posti</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Dom e Lun</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Si (Michelin 2026, Scatti di Gusto)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Michelin 2026.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -1469,52 +1485,52 @@
           <t>altatto_</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Solo sera lun-ven</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Sab e Dom</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Si (Michelin 2026, Gambero Rosso)</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Vegetariano/vegano. Trasferito ott 2025.</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -1541,22 +1557,22 @@
           <t>cucina__franca</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Presente su TheFork 2026</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
@@ -1593,32 +1609,32 @@
           <t>erbabrusca</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>12:00 (gio-dom), 20:00 (mer-dom)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>14:00, 22:30</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Confermato aperto feb 2026 (Yelp/sito)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
@@ -1655,22 +1671,22 @@
           <t>frangentemilano</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Listato tra migliori Milano 2026 (Gambero Rosso)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
@@ -1707,24 +1723,26 @@
           <t>insiemerestaurant</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1749,24 +1767,26 @@
       <c r="D21" s="1" t="inlineStr"/>
       <c r="E21" s="1" t="inlineStr"/>
       <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1799,24 +1819,26 @@
           <t>mannamilano</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P22" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr"/>
+      <c r="P22" s="1" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1849,24 +1871,26 @@
           <t>mater_bistrot</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1888,32 +1912,32 @@
           <t>02/36643680</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Cucina sperimentale.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1950,24 +1974,26 @@
           <t>motelombroso</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P25" s="1" t="inlineStr">
+      <c r="O25" s="1" t="inlineStr"/>
+      <c r="P25" s="1" t="inlineStr"/>
+      <c r="Q25" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R25" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2004,24 +2030,26 @@
           <t>nebbiamilano</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R26" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2053,32 +2081,32 @@
           <t>procaccinimilano</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026 (nuova). Chef Emir Hazizi.</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -2115,22 +2143,22 @@
           <t>remulass_milano</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Guida Michelin 2026 confermata</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
@@ -2163,24 +2191,26 @@
           <t>spore_ristorante</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P29" s="1" t="inlineStr">
+      <c r="O29" s="1" t="inlineStr"/>
+      <c r="P29" s="1" t="inlineStr"/>
+      <c r="Q29" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R29" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2217,52 +2247,52 @@
           <t>algarghet</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>19:30-22:30</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Lun; mar-ven pranzo</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Si (Yelp Apr 2026)</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Dal 1991. Cucina milanese tradizionale.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -2287,24 +2317,26 @@
       <c r="D31" s="1" t="inlineStr"/>
       <c r="E31" s="1" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
+      <c r="O31" s="1" t="inlineStr"/>
+      <c r="P31" s="1" t="inlineStr"/>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2329,24 +2361,26 @@
       <c r="D32" s="1" t="inlineStr"/>
       <c r="E32" s="1" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2383,24 +2417,26 @@
           <t>couscousrestaurant</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P33" s="1" t="inlineStr">
+      <c r="O33" s="1" t="inlineStr"/>
+      <c r="P33" s="1" t="inlineStr"/>
+      <c r="Q33" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2437,24 +2473,26 @@
           <t>gliortidelbelvedere</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P34" s="1" t="inlineStr">
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R34" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2491,24 +2529,26 @@
           <t>illibertymilano</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P35" s="1" t="inlineStr">
+      <c r="O35" s="1" t="inlineStr"/>
+      <c r="P35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R35" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2533,24 +2573,26 @@
       <c r="D36" s="1" t="inlineStr"/>
       <c r="E36" s="1" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P36" s="1" t="inlineStr">
+      <c r="O36" s="1" t="inlineStr"/>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R36" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2587,24 +2629,26 @@
           <t>locanda_del_menarost</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P37" s="1" t="inlineStr">
+      <c r="O37" s="1" t="inlineStr"/>
+      <c r="P37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R37" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2629,24 +2673,26 @@
       <c r="D38" s="1" t="inlineStr"/>
       <c r="E38" s="1" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2671,24 +2717,26 @@
       <c r="D39" s="1" t="inlineStr"/>
       <c r="E39" s="1" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="1" t="inlineStr"/>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2713,24 +2761,26 @@
       <c r="D40" s="1" t="inlineStr"/>
       <c r="E40" s="1" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="1" t="inlineStr"/>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2759,24 +2809,26 @@
           <t>osterialagrandissima</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P41" s="1" t="inlineStr">
+      <c r="O41" s="1" t="inlineStr"/>
+      <c r="P41" s="1" t="inlineStr"/>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R41" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2813,24 +2865,26 @@
           <t>particolaremilano</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="1" t="inlineStr"/>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2867,24 +2921,26 @@
           <t>pastamadre_milano</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="O43" s="1" t="inlineStr"/>
+      <c r="P43" s="1" t="inlineStr"/>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R43" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2921,24 +2977,26 @@
           <t>ristorante_ratana</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="O44" s="1" t="inlineStr"/>
+      <c r="P44" s="1" t="inlineStr"/>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R44" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2963,24 +3021,26 @@
       <c r="D45" s="1" t="inlineStr"/>
       <c r="E45" s="1" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P45" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr"/>
+      <c r="P45" s="1" t="inlineStr"/>
+      <c r="Q45" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3017,24 +3077,26 @@
           <t>sottobosco_milano</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P46" s="1" t="inlineStr">
+      <c r="O46" s="1" t="inlineStr"/>
+      <c r="P46" s="1" t="inlineStr"/>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R46" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3071,24 +3133,26 @@
           <t>trattoriadelnuovomacello</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P47" s="1" t="inlineStr">
+      <c r="O47" s="1" t="inlineStr"/>
+      <c r="P47" s="1" t="inlineStr"/>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R47" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3125,24 +3189,26 @@
           <t>unpostoamilano</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P48" s="1" t="inlineStr">
+      <c r="O48" s="1" t="inlineStr"/>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R48" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3179,24 +3245,26 @@
           <t>cizcantinaecucinamilano</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="inlineStr">
+      <c r="O49" s="1" t="inlineStr"/>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R49" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3221,24 +3289,26 @@
       <c r="D50" s="1" t="inlineStr"/>
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P50" s="1" t="inlineStr">
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R50" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3263,24 +3333,26 @@
       <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P51" s="1" t="inlineStr">
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3305,24 +3377,26 @@
       <c r="D52" s="1" t="inlineStr"/>
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P52" s="1" t="inlineStr">
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R52" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3347,24 +3421,26 @@
       <c r="D53" s="1" t="inlineStr"/>
       <c r="E53" s="1" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="inlineStr">
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R53" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3401,24 +3477,26 @@
           <t>giuliopaneeojo</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P54" s="1" t="inlineStr">
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R54" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3443,24 +3521,26 @@
       <c r="D55" s="1" t="inlineStr"/>
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P55" s="1" t="inlineStr">
+      <c r="O55" s="1" t="inlineStr"/>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R55" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3485,24 +3565,26 @@
       <c r="D56" s="1" t="inlineStr"/>
       <c r="E56" s="1" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P56" s="1" t="inlineStr">
+      <c r="O56" s="1" t="inlineStr"/>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3527,24 +3609,26 @@
       <c r="D57" s="1" t="inlineStr"/>
       <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="O57" s="1" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R57" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3581,24 +3665,26 @@
           <t>trattoriamasuelli</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P58" s="1" t="inlineStr">
+      <c r="O58" s="1" t="inlineStr"/>
+      <c r="P58" s="1" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R58" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3635,24 +3721,26 @@
           <t>trattoriamirta</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
+      <c r="O59" s="1" t="inlineStr"/>
+      <c r="P59" s="1" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3677,24 +3765,26 @@
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P60" s="1" t="inlineStr">
+      <c r="O60" s="1" t="inlineStr"/>
+      <c r="P60" s="1" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R60" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3719,24 +3809,26 @@
       <c r="D61" s="1" t="inlineStr"/>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P61" s="1" t="inlineStr">
+      <c r="O61" s="1" t="inlineStr"/>
+      <c r="P61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R61" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3773,24 +3865,26 @@
           <t>trippamilano</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P62" s="1" t="inlineStr">
+      <c r="O62" s="1" t="inlineStr"/>
+      <c r="P62" s="1" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3827,24 +3921,26 @@
           <t>ubarba</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P63" s="1" t="inlineStr">
+      <c r="O63" s="1" t="inlineStr"/>
+      <c r="P63" s="1" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R63" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3881,24 +3977,26 @@
           <t>alvelavevodetto</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P64" s="1" t="inlineStr">
+      <c r="O64" s="1" t="inlineStr"/>
+      <c r="P64" s="1" t="inlineStr"/>
+      <c r="Q64" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R64" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3935,52 +4033,52 @@
           <t>ba_restaurant</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Lun</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Si (Michelin 2026)</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Cucina cinese contemporanea.</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -4017,52 +4115,52 @@
           <t>bentotecamilano</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>19:00-22:30</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Lun; mar-gio pranzo</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Si (Michelin 2026, La Pecora Nera)</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Michelin 2026.</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -4099,24 +4197,26 @@
           <t>bussarakham_mi</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P67" s="1" t="inlineStr">
+      <c r="O67" s="1" t="inlineStr"/>
+      <c r="P67" s="1" t="inlineStr"/>
+      <c r="Q67" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R67" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4153,24 +4253,26 @@
           <t>casanori_</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P68" s="1" t="inlineStr">
+      <c r="O68" s="1" t="inlineStr"/>
+      <c r="P68" s="1" t="inlineStr"/>
+      <c r="Q68" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R68" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4207,24 +4309,26 @@
           <t>casaramen</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P69" s="1" t="inlineStr">
+      <c r="O69" s="1" t="inlineStr"/>
+      <c r="P69" s="1" t="inlineStr"/>
+      <c r="Q69" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R69" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4261,24 +4365,26 @@
           <t>gongmilano</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P70" s="1" t="inlineStr">
+      <c r="O70" s="1" t="inlineStr"/>
+      <c r="P70" s="1" t="inlineStr"/>
+      <c r="Q70" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R70" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4311,24 +4417,26 @@
           <t>ilgustodellanebbia_milano</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P71" s="1" t="inlineStr">
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R71" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4365,32 +4473,32 @@
           <t>iyo.restaurant</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Cucina giapponese.</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -4427,24 +4535,26 @@
           <t>kanpai_milano</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P73" s="1" t="inlineStr">
+      <c r="O73" s="1" t="inlineStr"/>
+      <c r="P73" s="1" t="inlineStr"/>
+      <c r="Q73" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R73" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4481,24 +4591,26 @@
           <t>Lenovescodelle</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P74" s="1" t="inlineStr">
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R74" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4535,24 +4647,26 @@
 maohunanrestaurant</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P75" s="1" t="inlineStr">
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R75" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4581,24 +4695,26 @@
           <t>ristorantemidomilano</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
+      <c r="O76" s="1" t="inlineStr"/>
+      <c r="P76" s="1" t="inlineStr"/>
+      <c r="Q76" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R76" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4635,24 +4751,26 @@
           <t>mudimsum</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P77" s="1" t="inlineStr">
+      <c r="O77" s="1" t="inlineStr"/>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R77" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4673,24 +4791,26 @@
       <c r="D78" s="1" t="inlineStr"/>
       <c r="E78" s="1" t="inlineStr"/>
       <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P78" s="1" t="inlineStr">
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R78" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4727,24 +4847,26 @@
           <t>tanishkaristo</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P79" s="1" t="inlineStr">
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4769,24 +4891,26 @@
       <c r="D80" s="1" t="inlineStr"/>
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4823,24 +4947,26 @@
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P81" s="1" t="inlineStr">
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R81" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4877,52 +5003,52 @@
           <t>berberepizzeria</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>12:30/19:00</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Si (Scatti di Gusto 2026)</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Pizza lievito madre.</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -4959,24 +5085,26 @@
           <t>confine_milano</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P83" s="1" t="inlineStr">
+      <c r="O83" s="1" t="inlineStr"/>
+      <c r="P83" s="1" t="inlineStr"/>
+      <c r="Q83" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R83" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5013,24 +5141,26 @@
           <t>crosta_milano</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P84" s="1" t="inlineStr">
+      <c r="O84" s="1" t="inlineStr"/>
+      <c r="P84" s="1" t="inlineStr"/>
+      <c r="Q84" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R84" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5067,24 +5197,26 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P85" s="1" t="inlineStr">
+      <c r="O85" s="1" t="inlineStr"/>
+      <c r="P85" s="1" t="inlineStr"/>
+      <c r="Q85" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R85" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5121,24 +5253,26 @@
           <t>denispizzadimontagna</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="O86" s="1" t="inlineStr"/>
+      <c r="P86" s="1" t="inlineStr"/>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5175,24 +5309,26 @@
           <t>drymilano</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="O87" s="1" t="inlineStr"/>
+      <c r="P87" s="1" t="inlineStr"/>
+      <c r="Q87" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5217,24 +5353,26 @@
       <c r="D88" s="1" t="inlineStr"/>
       <c r="E88" s="1" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P88" s="1" t="inlineStr">
+      <c r="O88" s="1" t="inlineStr"/>
+      <c r="P88" s="1" t="inlineStr"/>
+      <c r="Q88" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R88" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5271,24 +5409,26 @@
           <t>materia_milano</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P89" s="1" t="inlineStr">
+      <c r="O89" s="1" t="inlineStr"/>
+      <c r="P89" s="1" t="inlineStr"/>
+      <c r="Q89" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R89" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5325,24 +5465,26 @@
           <t>modus_milano</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P90" s="1" t="inlineStr">
+      <c r="O90" s="1" t="inlineStr"/>
+      <c r="P90" s="1" t="inlineStr"/>
+      <c r="Q90" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R90" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5379,52 +5521,52 @@
           <t>pasticceriaadolfostefanelli</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>07:30-20:00</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>Si (Gazzetta del Gusto)</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>2 sedi. Aperto tutti i giorni.</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -5449,24 +5591,26 @@
       <c r="D92" s="1" t="inlineStr"/>
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P92" s="1" t="inlineStr">
+      <c r="O92" s="1" t="inlineStr"/>
+      <c r="P92" s="1" t="inlineStr"/>
+      <c r="Q92" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R92" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5503,52 +5647,52 @@
           <t>bugancoffeelab</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>08:00-18:00</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>Si (Milano Events 2025)</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Specialty coffee. Aperto lug 2025.</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -5585,24 +5729,26 @@
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P94" s="1" t="inlineStr">
+      <c r="O94" s="1" t="inlineStr"/>
+      <c r="P94" s="1" t="inlineStr"/>
+      <c r="Q94" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5639,24 +5785,26 @@
           <t>pasticceriaclea</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr"/>
-      <c r="O95" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="O95" s="1" t="inlineStr"/>
+      <c r="P95" s="1" t="inlineStr"/>
+      <c r="Q95" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5681,24 +5829,26 @@
       <c r="D96" s="1" t="inlineStr"/>
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr"/>
-      <c r="O96" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P96" s="1" t="inlineStr">
+      <c r="O96" s="1" t="inlineStr"/>
+      <c r="P96" s="1" t="inlineStr"/>
+      <c r="Q96" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R96" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5735,24 +5885,26 @@
           <t>dittaartigianale</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P97" s="1" t="inlineStr">
+      <c r="O97" s="1" t="inlineStr"/>
+      <c r="P97" s="1" t="inlineStr"/>
+      <c r="Q97" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R97" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5789,24 +5941,26 @@
           <t>egalite_milano</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr"/>
+      <c r="P98" s="1" t="inlineStr"/>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5843,24 +5997,26 @@
           <t>fola.milano</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr"/>
+      <c r="I99" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr"/>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P99" s="1" t="inlineStr">
+      <c r="O99" s="1" t="inlineStr"/>
+      <c r="P99" s="1" t="inlineStr"/>
+      <c r="Q99" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5885,24 +6041,26 @@
       <c r="D100" s="1" t="inlineStr"/>
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr"/>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
-      <c r="I100" s="1" t="inlineStr"/>
+      <c r="I100" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr"/>
-      <c r="O100" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P100" s="1" t="inlineStr">
+      <c r="O100" s="1" t="inlineStr"/>
+      <c r="P100" s="1" t="inlineStr"/>
+      <c r="Q100" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R100" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5927,24 +6085,26 @@
       <c r="D101" s="1" t="inlineStr"/>
       <c r="E101" s="1" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr"/>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr"/>
+      <c r="I101" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr"/>
-      <c r="O101" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P101" s="1" t="inlineStr">
+      <c r="O101" s="1" t="inlineStr"/>
+      <c r="P101" s="1" t="inlineStr"/>
+      <c r="Q101" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R101" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5969,24 +6129,26 @@
       <c r="D102" s="1" t="inlineStr"/>
       <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr"/>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="1" t="inlineStr"/>
+      <c r="I102" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr"/>
-      <c r="O102" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr"/>
+      <c r="P102" s="1" t="inlineStr"/>
+      <c r="Q102" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6019,24 +6181,26 @@
           <t>lepolveri</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr"/>
+      <c r="I103" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J103" s="1" t="inlineStr"/>
       <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr"/>
-      <c r="O103" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr"/>
+      <c r="P103" s="1" t="inlineStr"/>
+      <c r="Q103" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6073,24 +6237,26 @@
           <t>iledoucemilano</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr"/>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr"/>
-      <c r="O104" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P104" s="1" t="inlineStr">
+      <c r="O104" s="1" t="inlineStr"/>
+      <c r="P104" s="1" t="inlineStr"/>
+      <c r="Q104" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R104" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6127,24 +6293,26 @@
           <t>lostecafemilano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr"/>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr"/>
-      <c r="O105" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P105" s="1" t="inlineStr">
+      <c r="O105" s="1" t="inlineStr"/>
+      <c r="P105" s="1" t="inlineStr"/>
+      <c r="Q105" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R105" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6181,24 +6349,26 @@
           <t>marlapasticceria</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr"/>
-      <c r="O106" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P106" s="1" t="inlineStr">
+      <c r="O106" s="1" t="inlineStr"/>
+      <c r="P106" s="1" t="inlineStr"/>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6231,24 +6401,26 @@
           <t>nowherecafe.milano</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="1" t="inlineStr"/>
+      <c r="I107" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr"/>
-      <c r="O107" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P107" s="1" t="inlineStr">
+      <c r="O107" s="1" t="inlineStr"/>
+      <c r="P107" s="1" t="inlineStr"/>
+      <c r="Q107" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6285,24 +6457,26 @@
           <t>orsonerocoffee</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr"/>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P108" s="1" t="inlineStr">
+      <c r="O108" s="1" t="inlineStr"/>
+      <c r="P108" s="1" t="inlineStr"/>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6339,24 +6513,26 @@
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr"/>
+      <c r="I109" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P109" s="1" t="inlineStr">
+      <c r="O109" s="1" t="inlineStr"/>
+      <c r="P109" s="1" t="inlineStr"/>
+      <c r="Q109" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R109" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6381,24 +6557,26 @@
       <c r="D110" s="1" t="inlineStr"/>
       <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr"/>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr"/>
-      <c r="O110" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P110" s="1" t="inlineStr">
+      <c r="O110" s="1" t="inlineStr"/>
+      <c r="P110" s="1" t="inlineStr"/>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6435,24 +6613,26 @@
           <t>signor_lievito</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr"/>
+      <c r="I111" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr"/>
-      <c r="O111" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P111" s="1" t="inlineStr">
+      <c r="O111" s="1" t="inlineStr"/>
+      <c r="P111" s="1" t="inlineStr"/>
+      <c r="Q111" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R111" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6489,24 +6669,26 @@
           <t>tiemi</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr"/>
+      <c r="I112" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P112" s="1" t="inlineStr">
+      <c r="O112" s="1" t="inlineStr"/>
+      <c r="P112" s="1" t="inlineStr"/>
+      <c r="Q112" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R112" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6539,24 +6721,26 @@
           <t>trechicchere</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P113" s="1" t="inlineStr">
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R113" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6593,24 +6777,26 @@
           <t>zivapasticceria</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr"/>
+      <c r="I114" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr"/>
-      <c r="O114" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P114" s="1" t="inlineStr">
+      <c r="O114" s="1" t="inlineStr"/>
+      <c r="P114" s="1" t="inlineStr"/>
+      <c r="Q114" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R114" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6642,52 +6828,52 @@
           <t>brolo.milano</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>08:00-01:00</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>Ortofrutta con cucina.</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="R115" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -6724,24 +6910,26 @@
           <t>gastronomiayamamoto</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G116" s="1" t="inlineStr"/>
       <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr"/>
+      <c r="I116" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J116" s="1" t="inlineStr"/>
       <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr"/>
-      <c r="O116" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P116" s="1" t="inlineStr">
+      <c r="O116" s="1" t="inlineStr"/>
+      <c r="P116" s="1" t="inlineStr"/>
+      <c r="Q116" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R116" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6766,24 +6954,26 @@
       <c r="D117" s="1" t="inlineStr"/>
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
-      <c r="I117" s="1" t="inlineStr"/>
+      <c r="I117" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J117" s="1" t="inlineStr"/>
       <c r="K117" s="1" t="inlineStr"/>
       <c r="L117" s="1" t="inlineStr"/>
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr"/>
-      <c r="O117" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P117" s="1" t="inlineStr">
+      <c r="O117" s="1" t="inlineStr"/>
+      <c r="P117" s="1" t="inlineStr"/>
+      <c r="Q117" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R117" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6812,24 +7002,26 @@
           <t>junecollectivemilano</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr"/>
+      <c r="I118" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J118" s="1" t="inlineStr"/>
       <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr"/>
-      <c r="O118" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P118" s="1" t="inlineStr">
+      <c r="O118" s="1" t="inlineStr"/>
+      <c r="P118" s="1" t="inlineStr"/>
+      <c r="Q118" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R118" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6866,24 +7058,26 @@
           <t>katsusanderia</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G119" s="1" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J119" s="1" t="inlineStr"/>
       <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P119" s="1" t="inlineStr">
+      <c r="O119" s="1" t="inlineStr"/>
+      <c r="P119" s="1" t="inlineStr"/>
+      <c r="Q119" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R119" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6920,24 +7114,26 @@
           <t>laravioleriasarpi</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J120" s="1" t="inlineStr"/>
       <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr"/>
-      <c r="O120" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P120" s="1" t="inlineStr">
+      <c r="O120" s="1" t="inlineStr"/>
+      <c r="P120" s="1" t="inlineStr"/>
+      <c r="Q120" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R120" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6974,24 +7170,26 @@
           <t>liseideli</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G121" s="1" t="inlineStr"/>
       <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr"/>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J121" s="1" t="inlineStr"/>
       <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr"/>
-      <c r="O121" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P121" s="1" t="inlineStr">
+      <c r="O121" s="1" t="inlineStr"/>
+      <c r="P121" s="1" t="inlineStr"/>
+      <c r="Q121" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R121" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7016,24 +7214,26 @@
       <c r="D122" s="1" t="inlineStr"/>
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr"/>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
-      <c r="I122" s="1" t="inlineStr"/>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J122" s="1" t="inlineStr"/>
       <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr"/>
-      <c r="O122" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P122" s="1" t="inlineStr">
+      <c r="O122" s="1" t="inlineStr"/>
+      <c r="P122" s="1" t="inlineStr"/>
+      <c r="Q122" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R122" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7066,24 +7266,26 @@
           <t>panmilano</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr"/>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J123" s="1" t="inlineStr"/>
       <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr"/>
-      <c r="O123" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P123" s="1" t="inlineStr">
+      <c r="O123" s="1" t="inlineStr"/>
+      <c r="P123" s="1" t="inlineStr"/>
+      <c r="Q123" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R123" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7108,24 +7310,26 @@
       <c r="D124" s="1" t="inlineStr"/>
       <c r="E124" s="1" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr"/>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J124" s="1" t="inlineStr"/>
       <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr"/>
-      <c r="O124" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P124" s="1" t="inlineStr">
+      <c r="O124" s="1" t="inlineStr"/>
+      <c r="P124" s="1" t="inlineStr"/>
+      <c r="Q124" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R124" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7154,24 +7358,26 @@
           <t>sandi_ristorante</t>
         </is>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J125" s="1" t="inlineStr"/>
       <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr"/>
-      <c r="O125" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P125" s="1" t="inlineStr">
+      <c r="O125" s="1" t="inlineStr"/>
+      <c r="P125" s="1" t="inlineStr"/>
+      <c r="Q125" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R125" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7204,24 +7410,26 @@
           <t>stadera_milano</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G126" s="1" t="inlineStr"/>
       <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J126" s="1" t="inlineStr"/>
       <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr"/>
-      <c r="O126" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P126" s="1" t="inlineStr">
+      <c r="O126" s="1" t="inlineStr"/>
+      <c r="P126" s="1" t="inlineStr"/>
+      <c r="Q126" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R126" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7254,24 +7462,26 @@
           <t>tone.milano</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J127" s="1" t="inlineStr"/>
       <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr"/>
-      <c r="O127" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P127" s="1" t="inlineStr">
+      <c r="O127" s="1" t="inlineStr"/>
+      <c r="P127" s="1" t="inlineStr"/>
+      <c r="Q127" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R127" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7304,24 +7514,26 @@
           <t>viastampa_milano</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
-      <c r="I128" s="1" t="inlineStr"/>
+      <c r="I128" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J128" s="1" t="inlineStr"/>
       <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr"/>
-      <c r="O128" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P128" s="1" t="inlineStr">
+      <c r="O128" s="1" t="inlineStr"/>
+      <c r="P128" s="1" t="inlineStr"/>
+      <c r="Q128" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R128" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7358,24 +7570,26 @@
           <t>zibocuochi</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J129" s="1" t="inlineStr"/>
       <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr"/>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P129" s="1" t="inlineStr">
+      <c r="O129" s="1" t="inlineStr"/>
+      <c r="P129" s="1" t="inlineStr"/>
+      <c r="Q129" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R129" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7412,24 +7626,26 @@
           <t>eastern.leaves</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J130" s="1" t="inlineStr"/>
       <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R130" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7466,24 +7682,26 @@
           <t>romanengo1780</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G131" s="1" t="inlineStr"/>
       <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J131" s="1" t="inlineStr"/>
       <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr"/>
-      <c r="O131" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P131" s="1" t="inlineStr">
+      <c r="O131" s="1" t="inlineStr"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R131" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7508,24 +7726,26 @@
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr"/>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G132" s="1" t="inlineStr"/>
       <c r="H132" s="1" t="inlineStr"/>
-      <c r="I132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J132" s="1" t="inlineStr"/>
       <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr"/>
-      <c r="O132" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P132" s="1" t="inlineStr">
+      <c r="O132" s="1" t="inlineStr"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R132" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7562,24 +7782,26 @@
           <t>la_teiera_eclettica</t>
         </is>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G133" s="1" t="inlineStr"/>
       <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J133" s="1" t="inlineStr"/>
       <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr"/>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
+      <c r="O133" s="1" t="inlineStr"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R133" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7604,24 +7826,26 @@
       <c r="D134" s="1" t="inlineStr"/>
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr"/>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G134" s="1" t="inlineStr"/>
       <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J134" s="1" t="inlineStr"/>
       <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr"/>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P134" s="1" t="inlineStr">
+      <c r="O134" s="1" t="inlineStr"/>
+      <c r="P134" s="1" t="inlineStr"/>
+      <c r="Q134" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R134" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7654,24 +7878,26 @@
           <t>pasticceriapasserini</t>
         </is>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G135" s="1" t="inlineStr"/>
       <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J135" s="1" t="inlineStr"/>
       <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr"/>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P135" s="1" t="inlineStr">
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R135" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7696,24 +7922,26 @@
       <c r="D136" s="1" t="inlineStr"/>
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr"/>
-      <c r="G136" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G136" s="1" t="inlineStr"/>
       <c r="H136" s="1" t="inlineStr"/>
-      <c r="I136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J136" s="1" t="inlineStr"/>
       <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr"/>
-      <c r="O136" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P136" s="1" t="inlineStr">
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R136" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7750,24 +7978,26 @@
           <t>cantine_isola</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G137" s="1" t="inlineStr"/>
       <c r="H137" s="1" t="inlineStr"/>
-      <c r="I137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J137" s="1" t="inlineStr"/>
       <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr"/>
-      <c r="O137" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P137" s="1" t="inlineStr">
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R137" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7804,24 +8034,26 @@
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G138" s="1" t="inlineStr"/>
       <c r="H138" s="1" t="inlineStr"/>
-      <c r="I138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J138" s="1" t="inlineStr"/>
       <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr"/>
-      <c r="O138" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P138" s="1" t="inlineStr">
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R138" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7858,24 +8090,26 @@
           <t>cru_milano</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G139" s="1" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J139" s="1" t="inlineStr"/>
       <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr"/>
-      <c r="O139" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P139" s="1" t="inlineStr">
+      <c r="O139" s="1" t="inlineStr"/>
+      <c r="P139" s="1" t="inlineStr"/>
+      <c r="Q139" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R139" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7912,24 +8146,26 @@
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G140" s="1" t="inlineStr"/>
       <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J140" s="1" t="inlineStr"/>
       <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr"/>
-      <c r="O140" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P140" s="1" t="inlineStr">
+      <c r="O140" s="1" t="inlineStr"/>
+      <c r="P140" s="1" t="inlineStr"/>
+      <c r="Q140" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R140" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7966,24 +8202,26 @@
           <t>florenoteca.milano</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G141" s="1" t="inlineStr"/>
       <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J141" s="1" t="inlineStr"/>
       <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr"/>
-      <c r="O141" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P141" s="1" t="inlineStr">
+      <c r="O141" s="1" t="inlineStr"/>
+      <c r="P141" s="1" t="inlineStr"/>
+      <c r="Q141" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R141" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8020,24 +8258,26 @@
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G142" s="1" t="inlineStr"/>
       <c r="H142" s="1" t="inlineStr"/>
-      <c r="I142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J142" s="1" t="inlineStr"/>
       <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr"/>
-      <c r="O142" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P142" s="1" t="inlineStr">
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R142" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8062,24 +8302,26 @@
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr"/>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G143" s="1" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J143" s="1" t="inlineStr"/>
       <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr"/>
-      <c r="O143" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P143" s="1" t="inlineStr">
+      <c r="O143" s="1" t="inlineStr"/>
+      <c r="P143" s="1" t="inlineStr"/>
+      <c r="Q143" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R143" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8116,24 +8358,26 @@
           <t>niks_co</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G144" s="1" t="inlineStr"/>
       <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J144" s="1" t="inlineStr"/>
       <c r="K144" s="1" t="inlineStr"/>
       <c r="L144" s="1" t="inlineStr"/>
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr"/>
-      <c r="O144" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P144" s="1" t="inlineStr">
+      <c r="O144" s="1" t="inlineStr"/>
+      <c r="P144" s="1" t="inlineStr"/>
+      <c r="Q144" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R144" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8158,24 +8402,26 @@
       <c r="D145" s="1" t="inlineStr"/>
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G145" s="1" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J145" s="1" t="inlineStr"/>
       <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr"/>
-      <c r="O145" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P145" s="1" t="inlineStr">
+      <c r="O145" s="1" t="inlineStr"/>
+      <c r="P145" s="1" t="inlineStr"/>
+      <c r="Q145" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R145" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8212,24 +8458,26 @@
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J146" s="1" t="inlineStr"/>
       <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr"/>
-      <c r="O146" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P146" s="1" t="inlineStr">
+      <c r="O146" s="1" t="inlineStr"/>
+      <c r="P146" s="1" t="inlineStr"/>
+      <c r="Q146" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R146" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8262,24 +8510,26 @@
           <t>vineriaeretica</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G147" s="1" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr"/>
+      <c r="I147" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J147" s="1" t="inlineStr"/>
       <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr"/>
-      <c r="O147" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P147" s="1" t="inlineStr">
+      <c r="O147" s="1" t="inlineStr"/>
+      <c r="P147" s="1" t="inlineStr"/>
+      <c r="Q147" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R147" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8304,24 +8554,26 @@
       <c r="D148" s="1" t="inlineStr"/>
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G148" s="1" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr"/>
+      <c r="I148" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J148" s="1" t="inlineStr"/>
       <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr"/>
-      <c r="O148" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P148" s="1" t="inlineStr">
+      <c r="O148" s="1" t="inlineStr"/>
+      <c r="P148" s="1" t="inlineStr"/>
+      <c r="Q148" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R148" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8346,24 +8598,26 @@
       <c r="D149" s="1" t="inlineStr"/>
       <c r="E149" s="1" t="inlineStr"/>
       <c r="F149" s="1" t="inlineStr"/>
-      <c r="G149" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G149" s="1" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J149" s="1" t="inlineStr"/>
       <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr"/>
-      <c r="O149" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P149" s="1" t="inlineStr">
+      <c r="O149" s="1" t="inlineStr"/>
+      <c r="P149" s="1" t="inlineStr"/>
+      <c r="Q149" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R149" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8388,24 +8642,26 @@
       <c r="D150" s="1" t="inlineStr"/>
       <c r="E150" s="1" t="inlineStr"/>
       <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G150" s="1" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J150" s="1" t="inlineStr"/>
       <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr"/>
-      <c r="O150" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P150" s="1" t="inlineStr">
+      <c r="O150" s="1" t="inlineStr"/>
+      <c r="P150" s="1" t="inlineStr"/>
+      <c r="Q150" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R150" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8442,24 +8698,26 @@
           <t>osteria_alla_concorrenza</t>
         </is>
       </c>
-      <c r="G151" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G151" s="1" t="inlineStr"/>
       <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J151" s="1" t="inlineStr"/>
       <c r="K151" s="1" t="inlineStr"/>
       <c r="L151" s="1" t="inlineStr"/>
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr"/>
-      <c r="O151" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P151" s="1" t="inlineStr">
+      <c r="O151" s="1" t="inlineStr"/>
+      <c r="P151" s="1" t="inlineStr"/>
+      <c r="Q151" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R151" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8492,24 +8750,26 @@
           <t>palinurobar</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G152" s="1" t="inlineStr"/>
       <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J152" s="1" t="inlineStr"/>
       <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr"/>
-      <c r="O152" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P152" s="1" t="inlineStr">
+      <c r="O152" s="1" t="inlineStr"/>
+      <c r="P152" s="1" t="inlineStr"/>
+      <c r="Q152" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R152" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8534,24 +8794,26 @@
       <c r="D153" s="1" t="inlineStr"/>
       <c r="E153" s="1" t="inlineStr"/>
       <c r="F153" s="1" t="inlineStr"/>
-      <c r="G153" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G153" s="1" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
-      <c r="I153" s="1" t="inlineStr"/>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J153" s="1" t="inlineStr"/>
       <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr"/>
-      <c r="O153" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P153" s="1" t="inlineStr">
+      <c r="O153" s="1" t="inlineStr"/>
+      <c r="P153" s="1" t="inlineStr"/>
+      <c r="Q153" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R153" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8580,24 +8842,26 @@
           <t>silvano_viniecibi</t>
         </is>
       </c>
-      <c r="G154" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G154" s="1" t="inlineStr"/>
       <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr"/>
+      <c r="I154" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J154" s="1" t="inlineStr"/>
       <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr"/>
-      <c r="O154" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P154" s="1" t="inlineStr">
+      <c r="O154" s="1" t="inlineStr"/>
+      <c r="P154" s="1" t="inlineStr"/>
+      <c r="Q154" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R154" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8630,24 +8894,26 @@
           <t>temp.enoteca</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G155" s="1" t="inlineStr"/>
       <c r="H155" s="1" t="inlineStr"/>
-      <c r="I155" s="1" t="inlineStr"/>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J155" s="1" t="inlineStr"/>
       <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr"/>
-      <c r="O155" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P155" s="1" t="inlineStr">
+      <c r="O155" s="1" t="inlineStr"/>
+      <c r="P155" s="1" t="inlineStr"/>
+      <c r="Q155" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R155" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8684,24 +8950,26 @@
           <t>kilburn_milano</t>
         </is>
       </c>
-      <c r="G156" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G156" s="1" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J156" s="1" t="inlineStr"/>
       <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr"/>
-      <c r="O156" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P156" s="1" t="inlineStr">
+      <c r="O156" s="1" t="inlineStr"/>
+      <c r="P156" s="1" t="inlineStr"/>
+      <c r="Q156" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R156" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8738,24 +9006,26 @@
           <t>lacerba.milano</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G157" s="1" t="inlineStr"/>
       <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr"/>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J157" s="1" t="inlineStr"/>
       <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr"/>
-      <c r="O157" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P157" s="1" t="inlineStr">
+      <c r="O157" s="1" t="inlineStr"/>
+      <c r="P157" s="1" t="inlineStr"/>
+      <c r="Q157" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R157" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8788,24 +9058,26 @@
           <t>magcafe</t>
         </is>
       </c>
-      <c r="G158" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G158" s="1" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr"/>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J158" s="1" t="inlineStr"/>
       <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr"/>
-      <c r="O158" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P158" s="1" t="inlineStr">
+      <c r="O158" s="1" t="inlineStr"/>
+      <c r="P158" s="1" t="inlineStr"/>
+      <c r="Q158" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R158" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8838,24 +9110,26 @@
           <t>norah_milano</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G159" s="1" t="inlineStr"/>
       <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr"/>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J159" s="1" t="inlineStr"/>
       <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr"/>
-      <c r="O159" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P159" s="1" t="inlineStr">
+      <c r="O159" s="1" t="inlineStr"/>
+      <c r="P159" s="1" t="inlineStr"/>
+      <c r="Q159" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R159" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8892,24 +9166,26 @@
           <t>ritacocktails</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G160" s="1" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr"/>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J160" s="1" t="inlineStr"/>
       <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P160" s="1" t="inlineStr">
+      <c r="O160" s="1" t="inlineStr"/>
+      <c r="P160" s="1" t="inlineStr"/>
+      <c r="Q160" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R160" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8934,24 +9210,26 @@
       <c r="D161" s="1" t="inlineStr"/>
       <c r="E161" s="1" t="inlineStr"/>
       <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G161" s="1" t="inlineStr"/>
       <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr"/>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J161" s="1" t="inlineStr"/>
       <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr"/>
-      <c r="O161" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P161" s="1" t="inlineStr">
+      <c r="O161" s="1" t="inlineStr"/>
+      <c r="P161" s="1" t="inlineStr"/>
+      <c r="Q161" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R161" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8984,24 +9262,26 @@
           <t>tripstillery</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G162" s="1" t="inlineStr"/>
       <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J162" s="1" t="inlineStr"/>
       <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr"/>
-      <c r="O162" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P162" s="1" t="inlineStr">
+      <c r="O162" s="1" t="inlineStr"/>
+      <c r="P162" s="1" t="inlineStr"/>
+      <c r="Q162" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R162" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9038,52 +9318,52 @@
           <t>alberto_marchetti_gelaterie</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t>12:00-23:00</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="N163" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
+      <c r="O163" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr">
+      <c r="P163" t="inlineStr">
         <is>
           <t>Si (Gambero Rosso, Flawless)</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="Q163" t="inlineStr">
         <is>
           <t>Gelateria artigianale.</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr">
+      <c r="R163" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -9108,24 +9388,26 @@
       <c r="D164" s="1" t="inlineStr"/>
       <c r="E164" s="1" t="inlineStr"/>
       <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J164" s="1" t="inlineStr"/>
       <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr"/>
-      <c r="O164" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P164" s="1" t="inlineStr">
+      <c r="O164" s="1" t="inlineStr"/>
+      <c r="P164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R164" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9162,24 +9444,26 @@
           <t>carmen_gelato</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G165" s="1" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J165" s="1" t="inlineStr"/>
       <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P165" s="1" t="inlineStr">
+      <c r="O165" s="1" t="inlineStr"/>
+      <c r="P165" s="1" t="inlineStr"/>
+      <c r="Q165" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R165" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9212,24 +9496,26 @@
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr"/>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G166" s="1" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J166" s="1" t="inlineStr"/>
       <c r="K166" s="1" t="inlineStr"/>
       <c r="L166" s="1" t="inlineStr"/>
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P166" s="1" t="inlineStr">
+      <c r="O166" s="1" t="inlineStr"/>
+      <c r="P166" s="1" t="inlineStr"/>
+      <c r="Q166" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R166" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9262,24 +9548,26 @@
           <t>latteneve</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G167" s="1" t="inlineStr"/>
       <c r="H167" s="1" t="inlineStr"/>
-      <c r="I167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J167" s="1" t="inlineStr"/>
       <c r="K167" s="1" t="inlineStr"/>
       <c r="L167" s="1" t="inlineStr"/>
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P167" s="1" t="inlineStr">
+      <c r="O167" s="1" t="inlineStr"/>
+      <c r="P167" s="1" t="inlineStr"/>
+      <c r="Q167" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R167" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9312,24 +9600,26 @@
           <t>gelateriapaganelli</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G168" s="1" t="inlineStr"/>
       <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J168" s="1" t="inlineStr"/>
       <c r="K168" s="1" t="inlineStr"/>
       <c r="L168" s="1" t="inlineStr"/>
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P168" s="1" t="inlineStr">
+      <c r="O168" s="1" t="inlineStr"/>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R168" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9366,24 +9656,26 @@
           <t>gelateria.prossima.fermata</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G169" s="1" t="inlineStr"/>
       <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr"/>
+      <c r="I169" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J169" s="1" t="inlineStr"/>
       <c r="K169" s="1" t="inlineStr"/>
       <c r="L169" s="1" t="inlineStr"/>
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P169" s="1" t="inlineStr">
+      <c r="O169" s="1" t="inlineStr"/>
+      <c r="P169" s="1" t="inlineStr"/>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R169" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9420,24 +9712,26 @@
           <t>gelatogiusto</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G170" s="1" t="inlineStr"/>
       <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr"/>
+      <c r="I170" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J170" s="1" t="inlineStr"/>
       <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P170" s="1" t="inlineStr">
+      <c r="O170" s="1" t="inlineStr"/>
+      <c r="P170" s="1" t="inlineStr"/>
+      <c r="Q170" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R170" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9474,24 +9768,26 @@
           <t>gnomogelato</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G171" s="1" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J171" s="1" t="inlineStr"/>
       <c r="K171" s="1" t="inlineStr"/>
       <c r="L171" s="1" t="inlineStr"/>
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P171" s="1" t="inlineStr">
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9528,24 +9824,26 @@
           <t>gusto17_ilgelato</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G172" s="1" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J172" s="1" t="inlineStr"/>
       <c r="K172" s="1" t="inlineStr"/>
       <c r="L172" s="1" t="inlineStr"/>
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P172" s="1" t="inlineStr">
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R172" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9582,24 +9880,26 @@
           <t>massimodelgelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G173" s="1" t="inlineStr"/>
       <c r="H173" s="1" t="inlineStr"/>
-      <c r="I173" s="1" t="inlineStr"/>
+      <c r="I173" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J173" s="1" t="inlineStr"/>
       <c r="K173" s="1" t="inlineStr"/>
       <c r="L173" s="1" t="inlineStr"/>
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P173" s="1" t="inlineStr">
+      <c r="O173" s="1" t="inlineStr"/>
+      <c r="P173" s="1" t="inlineStr"/>
+      <c r="Q173" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R173" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9636,24 +9936,26 @@
           <t>labottegadelgelatocardelli</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G174" s="1" t="inlineStr"/>
       <c r="H174" s="1" t="inlineStr"/>
-      <c r="I174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J174" s="1" t="inlineStr"/>
       <c r="K174" s="1" t="inlineStr"/>
       <c r="L174" s="1" t="inlineStr"/>
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P174" s="1" t="inlineStr">
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R174" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9690,24 +9992,26 @@
           <t>lagelateriadellamusica</t>
         </is>
       </c>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G175" s="1" t="inlineStr"/>
       <c r="H175" s="1" t="inlineStr"/>
-      <c r="I175" s="1" t="inlineStr"/>
+      <c r="I175" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J175" s="1" t="inlineStr"/>
       <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P175" s="1" t="inlineStr">
+      <c r="O175" s="1" t="inlineStr"/>
+      <c r="P175" s="1" t="inlineStr"/>
+      <c r="Q175" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R175" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9740,24 +10044,26 @@
           <t>noi_della_macelleriapopolare</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G176" s="1" t="inlineStr"/>
       <c r="H176" s="1" t="inlineStr"/>
-      <c r="I176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J176" s="1" t="inlineStr"/>
       <c r="K176" s="1" t="inlineStr"/>
       <c r="L176" s="1" t="inlineStr"/>
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P176" s="1" t="inlineStr">
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R176" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9782,24 +10088,26 @@
       <c r="D177" s="1" t="inlineStr"/>
       <c r="E177" s="1" t="inlineStr"/>
       <c r="F177" s="1" t="inlineStr"/>
-      <c r="G177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G177" s="1" t="inlineStr"/>
       <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J177" s="1" t="inlineStr"/>
       <c r="K177" s="1" t="inlineStr"/>
       <c r="L177" s="1" t="inlineStr"/>
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P177" s="1" t="inlineStr">
+      <c r="O177" s="1" t="inlineStr"/>
+      <c r="P177" s="1" t="inlineStr"/>
+      <c r="Q177" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R177" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9828,24 +10136,26 @@
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr"/>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G178" s="1" t="inlineStr"/>
       <c r="H178" s="1" t="inlineStr"/>
-      <c r="I178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J178" s="1" t="inlineStr"/>
       <c r="K178" s="1" t="inlineStr"/>
       <c r="L178" s="1" t="inlineStr"/>
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P178" s="1" t="inlineStr">
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R178" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9870,24 +10180,26 @@
       <c r="D179" s="1" t="inlineStr"/>
       <c r="E179" s="1" t="inlineStr"/>
       <c r="F179" s="1" t="inlineStr"/>
-      <c r="G179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G179" s="1" t="inlineStr"/>
       <c r="H179" s="1" t="inlineStr"/>
-      <c r="I179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J179" s="1" t="inlineStr"/>
       <c r="K179" s="1" t="inlineStr"/>
       <c r="L179" s="1" t="inlineStr"/>
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P179" s="1" t="inlineStr">
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R179" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9924,24 +10236,26 @@
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G180" s="1" t="inlineStr"/>
       <c r="H180" s="1" t="inlineStr"/>
-      <c r="I180" s="1" t="inlineStr"/>
+      <c r="I180" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J180" s="1" t="inlineStr"/>
       <c r="K180" s="1" t="inlineStr"/>
       <c r="L180" s="1" t="inlineStr"/>
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P180" s="1" t="inlineStr">
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R180" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9978,24 +10292,26 @@
           <t>gelateriarigoletto</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G181" s="1" t="inlineStr"/>
       <c r="H181" s="1" t="inlineStr"/>
-      <c r="I181" s="1" t="inlineStr"/>
+      <c r="I181" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J181" s="1" t="inlineStr"/>
       <c r="K181" s="1" t="inlineStr"/>
       <c r="L181" s="1" t="inlineStr"/>
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr"/>
-      <c r="O181" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P181" s="1" t="inlineStr">
+      <c r="O181" s="1" t="inlineStr"/>
+      <c r="P181" s="1" t="inlineStr"/>
+      <c r="Q181" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R181" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -10032,24 +10348,26 @@
           <t>terragelato</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G182" s="1" t="inlineStr"/>
       <c r="H182" s="1" t="inlineStr"/>
-      <c r="I182" s="1" t="inlineStr"/>
+      <c r="I182" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J182" s="1" t="inlineStr"/>
       <c r="K182" s="1" t="inlineStr"/>
       <c r="L182" s="1" t="inlineStr"/>
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr"/>
-      <c r="O182" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P182" s="1" t="inlineStr">
+      <c r="O182" s="1" t="inlineStr"/>
+      <c r="P182" s="1" t="inlineStr"/>
+      <c r="Q182" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R182" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -10074,24 +10392,26 @@
       <c r="D183" s="1" t="inlineStr"/>
       <c r="E183" s="1" t="inlineStr"/>
       <c r="F183" s="1" t="inlineStr"/>
-      <c r="G183" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G183" s="1" t="inlineStr"/>
       <c r="H183" s="1" t="inlineStr"/>
-      <c r="I183" s="1" t="inlineStr"/>
+      <c r="I183" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J183" s="1" t="inlineStr"/>
       <c r="K183" s="1" t="inlineStr"/>
       <c r="L183" s="1" t="inlineStr"/>
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr"/>
-      <c r="O183" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P183" s="1" t="inlineStr">
+      <c r="O183" s="1" t="inlineStr"/>
+      <c r="P183" s="1" t="inlineStr"/>
+      <c r="Q183" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R183" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -10128,24 +10448,26 @@
           <t>trapizzino</t>
         </is>
       </c>
-      <c r="G184" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G184" s="1" t="inlineStr"/>
       <c r="H184" s="1" t="inlineStr"/>
-      <c r="I184" s="1" t="inlineStr"/>
+      <c r="I184" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J184" s="1" t="inlineStr"/>
       <c r="K184" s="1" t="inlineStr"/>
       <c r="L184" s="1" t="inlineStr"/>
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P184" s="1" t="inlineStr">
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R184" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -561,6 +561,11 @@
           <t>andreaaprea_official</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -638,6 +643,11 @@
           <t>autem_milano</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -720,6 +730,16 @@
           <t>eugenio_boer</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -802,6 +822,16 @@
           <t>contrastemilano_</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -921,6 +951,16 @@
           <t>aimoenadia</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -993,6 +1033,16 @@
           <t>joiaaltacucinavegetariana</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1055,6 +1105,16 @@
           <t>morellimilano</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1115,6 +1175,16 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>ristorantebertonmilano</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1223,6 +1293,16 @@
           <t>setaatmandarinoriental</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1285,6 +1365,16 @@
           <t>sine_bydipinto</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1347,8 +1437,16 @@
           <t>versoristorante</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr"/>
-      <c r="H14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1403,6 +1501,16 @@
           <t>28posti</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1485,6 +1593,16 @@
           <t>altatto_</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1557,6 +1675,11 @@
           <t>cucina__franca</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1609,6 +1732,16 @@
           <t>erbabrusca</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1671,6 +1804,16 @@
           <t>frangentemilano</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1723,8 +1866,16 @@
           <t>insiemerestaurant</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1820,7 +1971,11 @@
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1872,7 +2027,11 @@
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1974,8 +2133,16 @@
           <t>motelombroso</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2030,8 +2197,16 @@
           <t>nebbiamilano</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2081,6 +2256,11 @@
           <t>procaccinimilano</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2143,6 +2323,16 @@
           <t>remulass_milano</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2192,7 +2382,11 @@
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2247,6 +2441,16 @@
           <t>algarghet</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2417,8 +2621,16 @@
           <t>couscousrestaurant</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2473,8 +2685,16 @@
           <t>gliortidelbelvedere</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2529,8 +2749,16 @@
           <t>illibertymilano</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2629,8 +2857,16 @@
           <t>locanda_del_menarost</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2810,7 +3046,11 @@
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2865,8 +3105,16 @@
           <t>particolaremilano</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2921,8 +3169,16 @@
           <t>pastamadre_milano</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2977,8 +3233,16 @@
           <t>ristorante_ratana</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3077,8 +3341,16 @@
           <t>sottobosco_milano</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>29/03/2026</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3133,8 +3405,16 @@
           <t>trattoriadelnuovomacello</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3189,8 +3469,16 @@
           <t>unpostoamilano</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3245,8 +3533,16 @@
           <t>cizcantinaecucinamilano</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3477,8 +3773,16 @@
           <t>giuliopaneeojo</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3665,8 +3969,16 @@
           <t>trattoriamasuelli</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3721,8 +4033,16 @@
           <t>trattoriamirta</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3865,8 +4185,16 @@
           <t>trippamilano</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3921,8 +4249,16 @@
           <t>ubarba</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3977,8 +4313,16 @@
           <t>alvelavevodetto</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4033,6 +4377,16 @@
           <t>ba_restaurant</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -4115,6 +4469,16 @@
           <t>bentotecamilano</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -4197,8 +4561,16 @@
           <t>bussarakham_mi</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4253,8 +4625,16 @@
           <t>casanori_</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4309,8 +4689,16 @@
           <t>casaramen</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4365,8 +4753,16 @@
           <t>gongmilano</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4417,8 +4813,16 @@
           <t>ilgustodellanebbia_milano</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4473,6 +4877,16 @@
           <t>iyo.restaurant</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -4535,8 +4949,16 @@
           <t>kanpai_milano</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4591,8 +5013,16 @@
           <t>Lenovescodelle</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4647,8 +5077,16 @@
 maohunanrestaurant</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1407,66 +1407,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Verso - Capitaneo</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Piazza Duomo, 21</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>02/89750929</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>www.ristoranteverso.com</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>versoristorante</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>versoristorante</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr"/>
-      <c r="L14" s="1" t="inlineStr"/>
-      <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr"/>
-      <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 15/04/2026</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1836,66 +1829,59 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Insieme</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Via Giovanni Rasori, 12</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>391/7182416</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>www.insieme.restaurant</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>insiemerestaurantmilano</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>insiemerestaurant</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 02/04/2026</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1925,7 @@
       </c>
       <c r="R21" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1981,7 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2037,7 @@
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2148,7 @@
       </c>
       <c r="R25" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2212,7 @@
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2392,7 @@
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2528,7 @@
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2572,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2636,7 @@
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2700,7 @@
       </c>
       <c r="R34" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2764,7 @@
       </c>
       <c r="R35" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2808,7 @@
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2872,7 @@
       </c>
       <c r="R37" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2916,7 @@
       </c>
       <c r="R38" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2960,7 @@
       </c>
       <c r="R39" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3004,7 @@
       </c>
       <c r="R40" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3056,7 @@
       </c>
       <c r="R41" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3120,7 @@
       </c>
       <c r="R42" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3198,71 +3184,64 @@
       </c>
       <c r="R43" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Ratanà</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Via Gaetano de Castillia, 28</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>02/87128855</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>www.ratana.it</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>RistoranteRatana</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>ristorante_ratana</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr"/>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R44" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3306,135 +3285,121 @@
       </c>
       <c r="R45" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Sottobosco</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Piazza San Luigi, 5</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>02/39289510</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>www.sottoboscomilano.com</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>sottobosco.milano</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>sottobosco_milano</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>29/03/2026</t>
         </is>
       </c>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr"/>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R46" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 29/03/2026</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Trattoria del Nuovo Macello</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Via Cesare Lombroso, 20</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>02/59902122</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>www.trattoriadelnuovomacello.it</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>trattoriadelnuovomacello</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>trattoriadelnuovomacello</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr"/>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3463,7 @@
       </c>
       <c r="R48" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3527,7 @@
       </c>
       <c r="R49" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3571,7 @@
       </c>
       <c r="R50" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3615,7 @@
       </c>
       <c r="R51" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3659,7 @@
       </c>
       <c r="R52" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3703,7 @@
       </c>
       <c r="R53" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3767,7 @@
       </c>
       <c r="R54" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3811,7 @@
       </c>
       <c r="R55" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3855,7 @@
       </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3899,7 @@
       </c>
       <c r="R57" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3963,7 @@
       </c>
       <c r="R58" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4027,7 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4071,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4150,71 +4115,64 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Trippa</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Via Giorgio Vasari, 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>327/6687908</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>www.trippamilano.it</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>TrippaMilano</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>trippamilano</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr"/>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 15/04/2026</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4236,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4300,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4531,130 +4489,116 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Bussarakham</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Via Felice Bellotti, 13</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>02/66661066</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>www.bussarakham.com</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>thairestaurantbussarakham</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>bussarakham_mi</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Casa Nori</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Via Antonio Pollaiuolo, 5</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>02/36742016</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>www.casanorimilano.it</t>
         </is>
       </c>
-      <c r="E68" s="1" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>profile.php?id=61567377507544</t>
         </is>
       </c>
-      <c r="F68" s="1" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>casanori_</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="H68" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr"/>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R68" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4662,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4726,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4786,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4922,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5042,7 +4986,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5050,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5078,11 @@
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5154,7 +5102,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5189,8 +5137,16 @@
           <t>mudimsum</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5210,7 +5166,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5250,63 +5206,64 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Tanishka</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Via Privata Antonio Meucci, 50</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>344/4236436</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>www.tanishkaristo.com</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>profile.php?id=100088513029290</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>tanishkaristo</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr"/>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R79" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 15/03/2026</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5307,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5385,8 +5342,16 @@
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5406,7 +5371,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5441,6 +5406,16 @@
           <t>berberepizzeria</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5523,8 +5498,16 @@
           <t>confine_milano</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5544,7 +5527,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5579,8 +5562,16 @@
           <t>crosta_milano</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5600,175 +5591,178 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Da Zero</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Oberdan, 12</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>02/47704656</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>www.dazero.org</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>dazeroaltredici</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr"/>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R85" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Denis - pizza di montagna</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Via Melzo, 16</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>375/5862098</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>www.denispizza.it</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>DenisPizzaDiMontagna</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>denispizzadimontagna</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr"/>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R86" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Dry</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Via Solferino, 33</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>02/63793414</t>
         </is>
       </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>www.drymilano.it</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Drymilano</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>drymilano</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr"/>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R87" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 09/04/2026</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5806,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5847,8 +5841,16 @@
           <t>materia_milano</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5868,63 +5870,64 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Modus</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Via Andrea Maffei, 12</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>02/82860006</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>www.modusmilano.it</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>profile.php?id=100083540587772</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>modus_milano</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>Modus</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>Via Andrea Maffei, 12</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>02/82860006</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>www.modusmilano.it</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>profile.php?id=100083540587772</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>modus_milano</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr"/>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R90" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5957,6 +5960,16 @@
       <c r="F91" t="inlineStr">
         <is>
           <t>pasticceriaadolfostefanelli</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6050,7 +6063,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6085,6 +6098,16 @@
           <t>bugancoffeelab</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -6137,58 +6160,59 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Cafezal Specialty Coffee</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Viale Premuda, 14</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>02/36579282</t>
         </is>
       </c>
-      <c r="D94" s="1" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>www.cafezal.it</t>
         </is>
       </c>
-      <c r="E94" s="1" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr"/>
-      <c r="L94" s="1" t="inlineStr"/>
-      <c r="M94" s="1" t="inlineStr"/>
-      <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr"/>
-      <c r="P94" s="1" t="inlineStr"/>
-      <c r="Q94" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R94" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6223,8 +6247,16 @@
           <t>pasticceriaclea</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6244,7 +6276,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6320,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6323,8 +6355,16 @@
           <t>dittaartigianale</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6344,63 +6384,64 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Égalité</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Via Melzo, 22</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>02/91763465</t>
         </is>
       </c>
-      <c r="D98" s="1" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>www.egalitemilano.it</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>egalitemilano</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>egalite_milano</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr"/>
-      <c r="L98" s="1" t="inlineStr"/>
-      <c r="M98" s="1" t="inlineStr"/>
-      <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr"/>
-      <c r="P98" s="1" t="inlineStr"/>
-      <c r="Q98" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R98" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6435,8 +6476,16 @@
           <t>fola.milano</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6456,7 +6505,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6549,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6593,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6637,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6669,11 @@
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6640,7 +6693,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6675,8 +6728,16 @@
           <t>iledoucemilano</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6696,7 +6757,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6731,8 +6792,16 @@
           <t>lostecafemilano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6752,63 +6821,64 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Marlà</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Corso Lodi, 15</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>02/36536410</t>
         </is>
       </c>
-      <c r="D106" s="1" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>www.marlapasticceria.it</t>
         </is>
       </c>
-      <c r="E106" s="1" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>creiamodolcienonsolo</t>
         </is>
       </c>
-      <c r="F106" s="1" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>marlapasticceria</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="inlineStr"/>
-      <c r="K106" s="1" t="inlineStr"/>
-      <c r="L106" s="1" t="inlineStr"/>
-      <c r="M106" s="1" t="inlineStr"/>
-      <c r="N106" s="1" t="inlineStr"/>
-      <c r="O106" s="1" t="inlineStr"/>
-      <c r="P106" s="1" t="inlineStr"/>
-      <c r="Q106" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R106" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6839,8 +6909,16 @@
           <t>nowherecafe.milano</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6860,7 +6938,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6895,8 +6973,16 @@
           <t>orsonerocoffee</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I108" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6916,7 +7002,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6951,8 +7037,16 @@
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I109" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6972,7 +7066,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7110,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7051,8 +7145,16 @@
           <t>signor_lievito</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7072,115 +7174,116 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tiemì</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Via Tiziano, 13</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>02/82874844</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>www.tiemipasticceria.it</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>tiemipasticceria</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>tiemi</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>Tiemì</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>Via Tiziano, 13</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>02/82874844</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>www.tiemipasticceria.it</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>tiemipasticceria</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>tiemi</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr"/>
-      <c r="L112" s="1" t="inlineStr"/>
-      <c r="M112" s="1" t="inlineStr"/>
-      <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr"/>
-      <c r="P112" s="1" t="inlineStr"/>
-      <c r="Q112" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R112" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Tre Chicchere</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Via Gian Antonio Boltraffio, 12</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>02/69007248</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>Trechicchere</t>
         </is>
       </c>
-      <c r="F113" s="1" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>trechicchere</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr"/>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
-      <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr"/>
-      <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R113" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 19/04/2026</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7215,8 +7318,16 @@
           <t>zivapasticceria</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7236,7 +7347,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7266,6 +7377,16 @@
           <t>brolo.milano</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7348,8 +7469,16 @@
           <t>gastronomiayamamoto</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7369,7 +7498,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7542,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7570,11 @@
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7461,7 +7594,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7496,8 +7629,16 @@
           <t>katsusanderia</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I119" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7517,7 +7658,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7552,8 +7693,16 @@
           <t>laravioleriasarpi</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7573,7 +7722,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7608,8 +7757,16 @@
           <t>liseideli</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7629,7 +7786,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7830,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7862,11 @@
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7725,7 +7886,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7930,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7958,11 @@
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr"/>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7817,7 +7982,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7848,8 +8013,16 @@
           <t>stadera_milano</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7869,7 +8042,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7900,8 +8073,16 @@
           <t>tone.milano</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7921,7 +8102,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7953,7 +8134,11 @@
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr"/>
-      <c r="H128" s="1" t="inlineStr"/>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7973,7 +8158,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8008,8 +8193,16 @@
           <t>zibocuochi</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr"/>
-      <c r="H129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8029,63 +8222,64 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Eastern Leaves</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Via Macedonio Melloni, 32</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>02/36706513</t>
         </is>
       </c>
-      <c r="D130" s="1" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>www.easternleaves.com</t>
         </is>
       </c>
-      <c r="E130" s="1" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>easternleavesfineteas</t>
         </is>
       </c>
-      <c r="F130" s="1" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>eastern.leaves</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr"/>
-      <c r="K130" s="1" t="inlineStr"/>
-      <c r="L130" s="1" t="inlineStr"/>
-      <c r="M130" s="1" t="inlineStr"/>
-      <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr"/>
-      <c r="P130" s="1" t="inlineStr"/>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 30/03/2026</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8120,8 +8314,16 @@
           <t>romanengo1780</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8141,7 +8343,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8387,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8220,8 +8422,16 @@
           <t>la_teiera_eclettica</t>
         </is>
       </c>
-      <c r="G133" s="1" t="inlineStr"/>
-      <c r="H133" s="1" t="inlineStr"/>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8241,7 +8451,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8495,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8527,11 @@
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8337,7 +8551,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8595,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8416,8 +8630,16 @@
           <t>cantine_isola</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr"/>
-      <c r="H137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8437,7 +8659,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8472,8 +8694,16 @@
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8493,7 +8723,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8528,8 +8758,16 @@
           <t>cru_milano</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr"/>
-      <c r="H139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8549,7 +8787,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8584,8 +8822,16 @@
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr"/>
-      <c r="H140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8605,7 +8851,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8640,8 +8886,16 @@
           <t>florenoteca.milano</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" s="1" t="inlineStr"/>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8661,7 +8915,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8696,8 +8950,16 @@
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8717,7 +8979,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8761,7 +9023,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8796,8 +9058,16 @@
           <t>niks_co</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H144" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8817,7 +9087,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8861,7 +9131,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9166,11 @@
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
@@ -8917,7 +9191,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8969,7 +9243,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9287,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9331,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9375,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9431,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9483,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9527,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9575,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9627,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9683,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9739,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9791,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9843,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9899,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9943,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9995,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9847,7 +10121,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9903,7 +10177,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9955,7 +10229,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10281,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10333,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10389,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10445,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10501,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10557,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10613,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10669,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10725,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10777,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10821,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10869,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10913,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10969,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10751,7 +11025,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10807,7 +11081,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10851,7 +11125,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10907,7 +11181,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -1219,46 +1219,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Ristorante D'O</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Piazza della Chiesa, 14</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>02/9362209</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr"/>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr"/>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GBP aperto, 2 stelle Michelin 2026, nessuna chiusura rilevata</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1452,14 +1445,19 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 15/04/2026</t>
+          <t>GBP aperto, 2 stelle Michelin 2026, recensione TripAdvisor gen 2026</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1874,170 +1872,160 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 02/04/2026</t>
+          <t>GBP aperto, sito e Instagram attivi 2026</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>La Cucina dei Frigoriferi Milanesi</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Via Giovanni Battista Piranesi, 10</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>02/39666784</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp aggiornato mar 2026, orari disponibili</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Manna</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Piazzale Governo Provvisorio, 6</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>02/26809153</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>www.mannamilano.it</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>mannamilano</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R22" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, riaperto dic 2023 in nuovo spazio</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Mater Bistrot</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Via Pasquale Sottocorno, 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>02/91321602</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>www.materbistrot.it</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>mater_bistrot</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr"/>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, Instagram @mater_bistrot attivo</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2089,130 +2077,126 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Motelombroso</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Alzaia Naviglio Pavese, 256</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>333/1855267</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>www.motelombroso.it</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>motelombroso</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>motelombroso</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GBP aperto, Ristoratore Anno Gambero Rosso 2026, sito attivo</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Nebbia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Via Evangelista Torricelli, 15</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>02/82781557</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>www.nebbiamilano.com</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Nebbia</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>nebbiamilano</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R26" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito attivo, orari confermati 2026</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2341,58 +2325,54 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Spore</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Via Passo Buole, 4</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>389/9191929</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>www.sporeristorante.it</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>spore_ristorante</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr"/>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GBP aperto, aggiornato gen 2026, prenotazioni attive</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2489,702 +2469,643 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Antica Osteria Magenes</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Via Cavour, 7 - fraz. Barate</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>02/9085125</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr"/>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R31" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, sito osteriamagenes.com con orari</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Antica Trattoria Monluè</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Via Monluè, 75</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>02/7610246</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr"/>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp apr 2026, sito trattoriamonlue.it attivo</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Cous-Cous</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Via Adige, 9</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>02/83967642</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>www.cous-cous.com</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>couscousrestaurant</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>couscousrestaurant</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito cous-cous.com con orari 2026, OpenTable attivo</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Gli Orti del Belvedere</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Via Orti, 10</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>02/49781425</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>www.gliortidelbelvedere.it</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>gliortidelbelvedere</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>gliortidelbelvedere</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork menù 2026, Yelp feb 2026</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Il Liberty</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Viale Monte Grappa, 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>02/29011439</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>www.il-liberty.it</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>IllibertyMilano</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>illibertymilano</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R35" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, TheFork disponibile, sito attivo</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Il Lughino</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Via Solferino, 12</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>02/6598972</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr"/>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R36" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork disponibile, sito lughino.it attivo</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Locanda del Menarost</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Via Giuseppe Compagnoni, 24</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>02/73951036</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>www.menarost.it</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>LocandaDelMenarost</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>locanda_del_menarost</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr"/>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp mar 2026, orari confermati</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Mezzolitro Vini e Cucina</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Via Pomè, 10</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>02/91327868</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr"/>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R38" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>GBP aperto, TripAdvisor mar 2026 tra i migliori di Rho, Michelin BibGourmand</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Mìbabbo</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Corso Lodi, 19, ang. Via Lazzaro Papi</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>02/45488997</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr"/>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R39" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, TheFork attivo, sito mibabbo.it</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Osteria Conchetta</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Via Conchetta, 8</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>02/8372917</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr"/>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp mar 2026, TheFork attivo, sito attivo</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Osteria Lagrandissima</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Via Ponte Nuovo, 25</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>342/5593532</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>osterialagrandissima</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr"/>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>GBP aperto, menù 2026 aggiornato Wheree, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Particolare Milano</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Via Gerolamo Tiraboschi, 5</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>02/47755016</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>www.particolaremilano.com</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>particolaremilano</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>particolaremilano</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr"/>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R42" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork recensione 9 gen 2026; valutazione 9.3/10 attiva</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Pastamadre</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Via Bernardino Corio, 8</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>02/55190020</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>www.pastamadremilano.it</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>team.pastamadre</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>pastamadre_milano</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr"/>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R43" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated January 2026; sito attivo</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3142,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3234,58 +3155,56 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+          <t>GBP aperto; Yelp Updated April 2026; Michelin 2026</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Ricci Osteria</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Via Pasquale Sottocorno, 27</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>02/49705612</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr"/>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensioni 2026 positive; 439 rec. RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3241,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3335,14 +3254,19 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 29/03/2026</t>
+          <t>GBP aperto; sito attivo; 512 rec. RestaurantGuru</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3303,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3392,730 +3316,662 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+          <t>GBP aperto; Yelp Updated March 2026; Michelin attivo</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Un posto a Milano</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Via Cuccagna, 2</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>02/5457785</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>www.unpostoamilano.it</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>unpostoamilano</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>unpostoamilano</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr"/>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated April 2026; TheFork menu 2026</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>CIZ - cantina e cucina</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Viale Premuda, 44</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>02/23189915</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>www.cizcantinaecucina.it</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>CizCantinaeCucina</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>cizcantinaecucinamilano</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr"/>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>GBP aperto; OpenTable Updated 2026; sito attivo</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>O|Nest</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Via Gerolamo Turroni, 2</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>351/8578998</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr"/>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R50" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensioni 2026; 821 rec. RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Antica Trattoria del Gallo</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Via Privata Gerli, 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>02/9085276</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr"/>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensioni 3-6 aprile 2026</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Ba' Ghetto</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Via Sardegna, 45</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>02/4694643</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr"/>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R52" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated March 2026; TheFork Recensioni 2026</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Felice a Testaccio</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Via del Torchio, 4</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>02/80506690</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr"/>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R53" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensioni 2026 positive; sito attivo</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Giulio Pane e Ojo</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Via Lodovico Muratori, 10</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>02/5456189 - 340/5806641</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>www.giuliopaneojo.com</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>dagiuliopaneojo</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>giuliopaneeojo</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr"/>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R54" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork Recensioni Verificate 2026</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Nonna Maria Osteria Romana</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Via Macedonio Melloni, 9</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>02/49436609</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr"/>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R55" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated February 2026; Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Osteria del Biliardo</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Via Enrico Cialdini, 107</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>02/36756256</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr"/>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>GBP aperto; Wheree Updated January 2026</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Osteria della Stazione</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Via Popoli Uniti, 26</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>02/28381700</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr"/>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R57" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; 1852 rec. RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Trattoria Masuelli San Marco</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Viale Umbria, 80</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>02/55184138</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>www.masuellitrattoria.com</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>TrattoriaMasuelli</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>trattoriamasuelli</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr"/>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R58" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>GBP aperto; 804 rec. TripAdvisor; attiva dal 1921</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Trattoria Mirta</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Piazza San Materno, 12</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>338/6251114</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>www.trattoriamirta.it</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>trattoriamirta</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>trattoriamirta</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr"/>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated February 2026</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Trattoria Sabbioneda</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Via Alessandro Tadino, 32</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>02/29521014</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr"/>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated January 2026</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Trattoria Sincera</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Via Antonio Porpora, 154</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>389/8741577</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr"/>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; recensioni 2026</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4193,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4489,57 +4345,64 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t>Bussarakham</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>Via Felice Bellotti, 13</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>02/66661066</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>www.bussarakham.com</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>thairestaurantbussarakham</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="1" t="inlineStr">
         <is>
           <t>bussarakham_mi</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
+      <c r="L67" s="1" t="inlineStr"/>
+      <c r="M67" s="1" t="inlineStr"/>
+      <c r="N67" s="1" t="inlineStr"/>
+      <c r="O67" s="1" t="inlineStr"/>
+      <c r="P67" s="1" t="inlineStr"/>
+      <c r="Q67" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R67" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -4578,7 +4441,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4593,7 +4456,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5078,11 +4941,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5137,16 +4996,8 @@
           <t>mudimsum</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5211,57 +5062,56 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>Tanishka</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>Via Privata Antonio Meucci, 50</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>344/4236436</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="1" t="inlineStr">
         <is>
           <t>www.tanishkaristo.com</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="1" t="inlineStr">
         <is>
           <t>profile.php?id=100088513029290</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="1" t="inlineStr">
         <is>
           <t>tanishkaristo</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 15/03/2026</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="inlineStr"/>
+      <c r="M79" s="1" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr"/>
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -5342,16 +5192,8 @@
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5406,16 +5248,6 @@
           <t>berberepizzeria</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5498,16 +5330,8 @@
           <t>confine_milano</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G83" s="1" t="inlineStr"/>
+      <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5562,16 +5386,8 @@
           <t>crosta_milano</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G84" s="1" t="inlineStr"/>
+      <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5596,171 +5412,168 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>Da Zero</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="1" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Oberdan, 12</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>02/47704656</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="1" t="inlineStr">
         <is>
           <t>www.dazero.org</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="1" t="inlineStr">
         <is>
           <t>dazeroaltredici</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="1" t="inlineStr">
         <is>
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="G85" s="1" t="inlineStr"/>
+      <c r="H85" s="1" t="inlineStr"/>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="inlineStr"/>
+      <c r="K85" s="1" t="inlineStr"/>
+      <c r="L85" s="1" t="inlineStr"/>
+      <c r="M85" s="1" t="inlineStr"/>
+      <c r="N85" s="1" t="inlineStr"/>
+      <c r="O85" s="1" t="inlineStr"/>
+      <c r="P85" s="1" t="inlineStr"/>
+      <c r="Q85" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R85" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>Denis - pizza di montagna</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>Via Melzo, 16</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>375/5862098</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="1" t="inlineStr">
         <is>
           <t>www.denispizza.it</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="1" t="inlineStr">
         <is>
           <t>DenisPizzaDiMontagna</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>denispizzadimontagna</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr"/>
+      <c r="H86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr"/>
+      <c r="K86" s="1" t="inlineStr"/>
+      <c r="L86" s="1" t="inlineStr"/>
+      <c r="M86" s="1" t="inlineStr"/>
+      <c r="N86" s="1" t="inlineStr"/>
+      <c r="O86" s="1" t="inlineStr"/>
+      <c r="P86" s="1" t="inlineStr"/>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
         <is>
           <t>Dry</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>Via Solferino, 33</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>02/63793414</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="1" t="inlineStr">
         <is>
           <t>www.drymilano.it</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="1" t="inlineStr">
         <is>
           <t>Drymilano</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="1" t="inlineStr">
         <is>
           <t>drymilano</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 09/04/2026</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr"/>
+      <c r="H87" s="1" t="inlineStr"/>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr"/>
+      <c r="K87" s="1" t="inlineStr"/>
+      <c r="L87" s="1" t="inlineStr"/>
+      <c r="M87" s="1" t="inlineStr"/>
+      <c r="N87" s="1" t="inlineStr"/>
+      <c r="O87" s="1" t="inlineStr"/>
+      <c r="P87" s="1" t="inlineStr"/>
+      <c r="Q87" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -5841,16 +5654,8 @@
           <t>materia_milano</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G89" s="1" t="inlineStr"/>
+      <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5875,57 +5680,56 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>Modus</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="1" t="inlineStr">
         <is>
           <t>Via Andrea Maffei, 12</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>02/82860006</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="1" t="inlineStr">
         <is>
           <t>www.modusmilano.it</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="1" t="inlineStr">
         <is>
           <t>profile.php?id=100083540587772</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="1" t="inlineStr">
         <is>
           <t>modus_milano</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="G90" s="1" t="inlineStr"/>
+      <c r="H90" s="1" t="inlineStr"/>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr"/>
+      <c r="K90" s="1" t="inlineStr"/>
+      <c r="L90" s="1" t="inlineStr"/>
+      <c r="M90" s="1" t="inlineStr"/>
+      <c r="N90" s="1" t="inlineStr"/>
+      <c r="O90" s="1" t="inlineStr"/>
+      <c r="P90" s="1" t="inlineStr"/>
+      <c r="Q90" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R90" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -5960,16 +5764,6 @@
       <c r="F91" t="inlineStr">
         <is>
           <t>pasticceriaadolfostefanelli</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>N/D</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6098,16 +5892,6 @@
           <t>bugancoffeelab</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -6160,57 +5944,56 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>Cafezal Specialty Coffee</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="1" t="inlineStr">
         <is>
           <t>Viale Premuda, 14</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>02/36579282</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="1" t="inlineStr">
         <is>
           <t>www.cafezal.it</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="1" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="1" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr"/>
+      <c r="H94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="inlineStr"/>
+      <c r="K94" s="1" t="inlineStr"/>
+      <c r="L94" s="1" t="inlineStr"/>
+      <c r="M94" s="1" t="inlineStr"/>
+      <c r="N94" s="1" t="inlineStr"/>
+      <c r="O94" s="1" t="inlineStr"/>
+      <c r="P94" s="1" t="inlineStr"/>
+      <c r="Q94" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -6247,16 +6030,8 @@
           <t>pasticceriaclea</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H95" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G95" s="1" t="inlineStr"/>
+      <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6355,16 +6130,8 @@
           <t>dittaartigianale</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G97" s="1" t="inlineStr"/>
+      <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6389,57 +6156,56 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>Égalité</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="1" t="inlineStr">
         <is>
           <t>Via Melzo, 22</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>02/91763465</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="1" t="inlineStr">
         <is>
           <t>www.egalitemilano.it</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="1" t="inlineStr">
         <is>
           <t>egalitemilano</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="1" t="inlineStr">
         <is>
           <t>egalite_milano</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr"/>
+      <c r="H98" s="1" t="inlineStr"/>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr"/>
+      <c r="K98" s="1" t="inlineStr"/>
+      <c r="L98" s="1" t="inlineStr"/>
+      <c r="M98" s="1" t="inlineStr"/>
+      <c r="N98" s="1" t="inlineStr"/>
+      <c r="O98" s="1" t="inlineStr"/>
+      <c r="P98" s="1" t="inlineStr"/>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -6476,16 +6242,8 @@
           <t>fola.milano</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G99" s="1" t="inlineStr"/>
+      <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6669,11 +6427,7 @@
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6728,16 +6482,8 @@
           <t>iledoucemilano</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G104" s="1" t="inlineStr"/>
+      <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6792,16 +6538,8 @@
           <t>lostecafemilano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G105" s="1" t="inlineStr"/>
+      <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6826,57 +6564,56 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>Marlà</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t>Corso Lodi, 15</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>02/36536410</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="1" t="inlineStr">
         <is>
           <t>www.marlapasticceria.it</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="1" t="inlineStr">
         <is>
           <t>creiamodolcienonsolo</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="1" t="inlineStr">
         <is>
           <t>marlapasticceria</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr"/>
+      <c r="H106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
+      <c r="L106" s="1" t="inlineStr"/>
+      <c r="M106" s="1" t="inlineStr"/>
+      <c r="N106" s="1" t="inlineStr"/>
+      <c r="O106" s="1" t="inlineStr"/>
+      <c r="P106" s="1" t="inlineStr"/>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -6909,16 +6646,8 @@
           <t>nowherecafe.milano</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G107" s="1" t="inlineStr"/>
+      <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6973,16 +6702,8 @@
           <t>orsonerocoffee</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G108" s="1" t="inlineStr"/>
+      <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7037,16 +6758,8 @@
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G109" s="1" t="inlineStr"/>
+      <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7145,16 +6858,8 @@
           <t>signor_lievito</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G111" s="1" t="inlineStr"/>
+      <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7179,109 +6884,108 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>Tiemì</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>Via Tiziano, 13</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>02/82874844</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="1" t="inlineStr">
         <is>
           <t>www.tiemipasticceria.it</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="1" t="inlineStr">
         <is>
           <t>tiemipasticceria</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="1" t="inlineStr">
         <is>
           <t>tiemi</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
+      <c r="G112" s="1" t="inlineStr"/>
+      <c r="H112" s="1" t="inlineStr"/>
+      <c r="I112" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J112" s="1" t="inlineStr"/>
+      <c r="K112" s="1" t="inlineStr"/>
+      <c r="L112" s="1" t="inlineStr"/>
+      <c r="M112" s="1" t="inlineStr"/>
+      <c r="N112" s="1" t="inlineStr"/>
+      <c r="O112" s="1" t="inlineStr"/>
+      <c r="P112" s="1" t="inlineStr"/>
+      <c r="Q112" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R112" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
         <is>
           <t>Tre Chicchere</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>Via Gian Antonio Boltraffio, 12</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>02/69007248</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="D113" s="1" t="inlineStr"/>
+      <c r="E113" s="1" t="inlineStr">
         <is>
           <t>Trechicchere</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="1" t="inlineStr">
         <is>
           <t>trechicchere</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 19/04/2026</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr"/>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
+      <c r="L113" s="1" t="inlineStr"/>
+      <c r="M113" s="1" t="inlineStr"/>
+      <c r="N113" s="1" t="inlineStr"/>
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R113" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -7318,16 +7022,8 @@
           <t>zivapasticceria</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G114" s="1" t="inlineStr"/>
+      <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7377,16 +7073,6 @@
           <t>brolo.milano</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7469,16 +7155,8 @@
           <t>gastronomiayamamoto</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G116" s="1" t="inlineStr"/>
+      <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7570,11 +7248,7 @@
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7629,16 +7303,8 @@
           <t>katsusanderia</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G119" s="1" t="inlineStr"/>
+      <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7693,16 +7359,8 @@
           <t>laravioleriasarpi</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G120" s="1" t="inlineStr"/>
+      <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7757,16 +7415,8 @@
           <t>liseideli</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G121" s="1" t="inlineStr"/>
+      <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7862,11 +7512,7 @@
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7958,11 +7604,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8013,16 +7655,8 @@
           <t>stadera_milano</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G126" s="1" t="inlineStr"/>
+      <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8073,16 +7707,8 @@
           <t>tone.milano</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H127" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8134,11 +7760,7 @@
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr"/>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8193,16 +7815,8 @@
           <t>zibocuochi</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G129" s="1" t="inlineStr"/>
+      <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8227,57 +7841,56 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="1" t="inlineStr">
         <is>
           <t>Eastern Leaves</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="1" t="inlineStr">
         <is>
           <t>Via Macedonio Melloni, 32</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>02/36706513</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="1" t="inlineStr">
         <is>
           <t>www.easternleaves.com</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="1" t="inlineStr">
         <is>
           <t>easternleavesfineteas</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="1" t="inlineStr">
         <is>
           <t>eastern.leaves</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 30/03/2026</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr">
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
+      <c r="L130" s="1" t="inlineStr"/>
+      <c r="M130" s="1" t="inlineStr"/>
+      <c r="N130" s="1" t="inlineStr"/>
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R130" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -8314,16 +7927,8 @@
           <t>romanengo1780</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8422,16 +8027,8 @@
           <t>la_teiera_eclettica</t>
         </is>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G133" s="1" t="inlineStr"/>
+      <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8527,11 +8124,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8630,16 +8223,8 @@
           <t>cantine_isola</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H137" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8694,16 +8279,8 @@
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H138" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8758,16 +8335,8 @@
           <t>cru_milano</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G139" s="1" t="inlineStr"/>
+      <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8822,16 +8391,8 @@
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G140" s="1" t="inlineStr"/>
+      <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8886,16 +8447,8 @@
           <t>florenoteca.milano</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G141" s="1" t="inlineStr"/>
+      <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8950,16 +8503,8 @@
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G142" s="1" t="inlineStr"/>
+      <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9058,16 +8603,8 @@
           <t>niks_co</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H144" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G144" s="1" t="inlineStr"/>
+      <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9166,11 +8703,7 @@
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,11 @@
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4961,7 +4965,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4996,8 +5000,16 @@
           <t>mudimsum</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5017,7 +5029,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5057,63 +5069,64 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Tanishka</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Via Privata Antonio Meucci, 50</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>344/4236436</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>www.tanishkaristo.com</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>profile.php?id=100088513029290</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>tanishkaristo</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr"/>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R79" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 15/03/2026</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5170,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5192,8 +5205,16 @@
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5213,7 +5234,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5248,6 +5269,16 @@
           <t>berberepizzeria</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5330,8 +5361,16 @@
           <t>confine_milano</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5351,7 +5390,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5386,8 +5425,16 @@
           <t>crosta_milano</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5407,7 +5454,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5442,8 +5489,16 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5463,119 +5518,121 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Denis - pizza di montagna</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Via Melzo, 16</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>375/5862098</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>www.denispizza.it</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>DenisPizzaDiMontagna</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>denispizzadimontagna</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr"/>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R86" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Dry</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Via Solferino, 33</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>02/63793414</t>
         </is>
       </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>www.drymilano.it</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Drymilano</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>drymilano</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr"/>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R87" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 09/04/2026</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5619,119 +5676,121 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Materia</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Via del Torchio, 1</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>02/49714985</t>
         </is>
       </c>
-      <c r="D89" s="1" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>www.materiapizzeria.com</t>
         </is>
       </c>
-      <c r="E89" s="1" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>materiapizza</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>materia_milano</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr"/>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R89" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 23/04/2026</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Modus</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Via Andrea Maffei, 12</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>02/82860006</t>
         </is>
       </c>
-      <c r="D90" s="1" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>www.modusmilano.it</t>
         </is>
       </c>
-      <c r="E90" s="1" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>profile.php?id=100083540587772</t>
         </is>
       </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>modus_milano</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr"/>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R90" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5764,6 +5823,16 @@
       <c r="F91" t="inlineStr">
         <is>
           <t>pasticceriaadolfostefanelli</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5857,7 +5926,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5892,6 +5961,16 @@
           <t>bugancoffeelab</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5974,8 +6053,16 @@
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5995,7 +6082,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6030,8 +6117,16 @@
           <t>pasticceriaclea</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6051,7 +6146,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6095,63 +6190,64 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Ditta Artigianale</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Corso Magenta, 31</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>02/99250284</t>
         </is>
       </c>
-      <c r="D97" s="1" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>www.dittaartigianale.com</t>
         </is>
       </c>
-      <c r="E97" s="1" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>dittaartigianale</t>
         </is>
       </c>
-      <c r="F97" s="1" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>dittaartigianale</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr"/>
-      <c r="L97" s="1" t="inlineStr"/>
-      <c r="M97" s="1" t="inlineStr"/>
-      <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr"/>
-      <c r="P97" s="1" t="inlineStr"/>
-      <c r="Q97" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R97" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 21/04/2026</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6186,8 +6282,16 @@
           <t>egalite_milano</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6207,7 +6311,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6242,8 +6346,16 @@
           <t>fola.milano</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6263,7 +6375,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6419,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6463,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6507,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6539,11 @@
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6447,7 +6563,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6482,8 +6598,16 @@
           <t>iledoucemilano</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6503,7 +6627,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6538,8 +6662,16 @@
           <t>lostecafemilano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6559,7 +6691,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6594,8 +6726,16 @@
           <t>marlapasticceria</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6615,7 +6755,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6646,8 +6786,16 @@
           <t>nowherecafe.milano</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6667,7 +6815,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6702,8 +6850,16 @@
           <t>orsonerocoffee</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I108" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6723,63 +6879,64 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Pavè</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Via della Commenda, 25</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>02/83630074</t>
         </is>
       </c>
-      <c r="D109" s="1" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>www.pavemilano.com</t>
         </is>
       </c>
-      <c r="E109" s="1" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="F109" s="1" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr"/>
-      <c r="K109" s="1" t="inlineStr"/>
-      <c r="L109" s="1" t="inlineStr"/>
-      <c r="M109" s="1" t="inlineStr"/>
-      <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr"/>
-      <c r="P109" s="1" t="inlineStr"/>
-      <c r="Q109" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R109" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6980,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6858,8 +7015,16 @@
           <t>signor_lievito</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6879,63 +7044,64 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>Tiemì</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Via Tiziano, 13</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>02/82874844</t>
         </is>
       </c>
-      <c r="D112" s="1" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>www.tiemipasticceria.it</t>
         </is>
       </c>
-      <c r="E112" s="1" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>tiemipasticceria</t>
         </is>
       </c>
-      <c r="F112" s="1" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>tiemi</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr"/>
-      <c r="L112" s="1" t="inlineStr"/>
-      <c r="M112" s="1" t="inlineStr"/>
-      <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr"/>
-      <c r="P112" s="1" t="inlineStr"/>
-      <c r="Q112" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R112" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6966,8 +7132,16 @@
           <t>trechicchere</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H113" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I113" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6987,7 +7161,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7022,8 +7196,16 @@
           <t>zivapasticceria</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7043,7 +7225,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7073,6 +7255,16 @@
           <t>brolo.milano</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7155,8 +7347,16 @@
           <t>gastronomiayamamoto</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7176,7 +7376,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7420,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7448,11 @@
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7268,7 +7472,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7303,8 +7507,16 @@
           <t>katsusanderia</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I119" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7324,7 +7536,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7359,8 +7571,16 @@
           <t>laravioleriasarpi</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7380,7 +7600,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7415,8 +7635,16 @@
           <t>liseideli</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7436,7 +7664,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7708,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7740,11 @@
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7532,7 +7764,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7808,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7836,11 @@
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr"/>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7624,7 +7860,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7655,8 +7891,16 @@
           <t>stadera_milano</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7676,7 +7920,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7707,8 +7951,16 @@
           <t>tone.milano</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7728,7 +7980,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7760,7 +8012,11 @@
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr"/>
-      <c r="H128" s="1" t="inlineStr"/>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7780,7 +8036,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7815,8 +8071,16 @@
           <t>zibocuochi</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr"/>
-      <c r="H129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7836,119 +8100,121 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Eastern Leaves</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Via Macedonio Melloni, 32</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>02/36706513</t>
         </is>
       </c>
-      <c r="D130" s="1" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>www.easternleaves.com</t>
         </is>
       </c>
-      <c r="E130" s="1" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>easternleavesfineteas</t>
         </is>
       </c>
-      <c r="F130" s="1" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>eastern.leaves</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr"/>
-      <c r="K130" s="1" t="inlineStr"/>
-      <c r="L130" s="1" t="inlineStr"/>
-      <c r="M130" s="1" t="inlineStr"/>
-      <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr"/>
-      <c r="P130" s="1" t="inlineStr"/>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 30/03/2026</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>La Corte - Romanengo 1780</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Via Manzoni, 5</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>2799979385</t>
         </is>
       </c>
-      <c r="D131" s="1" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>www.romanengo.com</t>
         </is>
       </c>
-      <c r="E131" s="1" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>romanengo1780</t>
         </is>
       </c>
-      <c r="F131" s="1" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>romanengo1780</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr"/>
-      <c r="K131" s="1" t="inlineStr"/>
-      <c r="L131" s="1" t="inlineStr"/>
-      <c r="M131" s="1" t="inlineStr"/>
-      <c r="N131" s="1" t="inlineStr"/>
-      <c r="O131" s="1" t="inlineStr"/>
-      <c r="P131" s="1" t="inlineStr"/>
-      <c r="Q131" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R131" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7992,7 +8258,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8027,8 +8293,16 @@
           <t>la_teiera_eclettica</t>
         </is>
       </c>
-      <c r="G133" s="1" t="inlineStr"/>
-      <c r="H133" s="1" t="inlineStr"/>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8048,7 +8322,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8366,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8398,11 @@
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8144,7 +8422,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8466,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8223,8 +8501,16 @@
           <t>cantine_isola</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr"/>
-      <c r="H137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8244,7 +8530,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8279,8 +8565,16 @@
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8300,7 +8594,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8335,8 +8629,16 @@
           <t>cru_milano</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr"/>
-      <c r="H139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8356,7 +8658,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8391,8 +8693,16 @@
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr"/>
-      <c r="H140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8412,7 +8722,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8447,8 +8757,16 @@
           <t>florenoteca.milano</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" s="1" t="inlineStr"/>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8468,7 +8786,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8503,8 +8821,16 @@
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8524,7 +8850,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8894,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8603,8 +8929,16 @@
           <t>niks_co</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="H144" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8624,7 +8958,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8668,7 +9002,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8703,7 +9037,11 @@
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
@@ -8724,7 +9062,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8776,7 +9114,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8820,7 +9158,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8864,7 +9202,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8908,7 +9246,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9302,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9354,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9398,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9446,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9498,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9554,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9610,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9662,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9714,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9770,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9814,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9866,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9992,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9710,7 +10048,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9762,7 +10100,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9814,7 +10152,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9866,7 +10204,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9922,7 +10260,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9978,7 +10316,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10372,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10428,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10484,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10540,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10596,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10648,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10692,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10740,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10784,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10840,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10896,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10952,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10996,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10714,7 +11052,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H146" s="1" t="inlineStr"/>
+      <c r="H146" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I146" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9062,7 +9066,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9098,11 @@
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9114,7 +9122,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9166,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9210,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9254,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9281,8 +9289,16 @@
           <t>osteria_alla_concorrenza</t>
         </is>
       </c>
-      <c r="G151" s="1" t="inlineStr"/>
-      <c r="H151" s="1" t="inlineStr"/>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9302,7 +9318,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9350,11 @@
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr"/>
-      <c r="H152" s="1" t="inlineStr"/>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9354,7 +9374,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9418,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9446,11 @@
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
+      <c r="H154" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9446,7 +9470,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9502,11 @@
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr"/>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9498,7 +9526,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9533,8 +9561,16 @@
           <t>kilburn_milano</t>
         </is>
       </c>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr"/>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9554,7 +9590,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9589,8 +9625,16 @@
           <t>lacerba.milano</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9610,7 +9654,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9641,8 +9685,16 @@
           <t>magcafe</t>
         </is>
       </c>
-      <c r="G158" s="1" t="inlineStr"/>
-      <c r="H158" s="1" t="inlineStr"/>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9662,7 +9714,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9693,8 +9745,16 @@
           <t>norah_milano</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" s="1" t="inlineStr"/>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9714,7 +9774,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9749,8 +9809,16 @@
           <t>ritacocktails</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr"/>
-      <c r="H160" s="1" t="inlineStr"/>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9770,7 +9838,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9882,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9845,8 +9913,16 @@
           <t>tripstillery</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9866,7 +9942,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9899,6 +9975,16 @@
       <c r="F163" t="inlineStr">
         <is>
           <t>alberto_marchetti_gelaterie</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9992,7 +10078,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10027,8 +10113,16 @@
           <t>carmen_gelato</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10048,7 +10142,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10173,11 @@
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr"/>
-      <c r="G166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr">
         <is>
@@ -10100,7 +10198,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10131,8 +10229,16 @@
           <t>latteneve</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr"/>
-      <c r="H167" s="1" t="inlineStr"/>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I167" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10152,7 +10258,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10183,8 +10289,16 @@
           <t>gelateriapaganelli</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr"/>
-      <c r="H168" s="1" t="inlineStr"/>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10204,7 +10318,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10239,8 +10353,16 @@
           <t>gelateria.prossima.fermata</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr"/>
-      <c r="H169" s="1" t="inlineStr"/>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I169" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10260,7 +10382,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10295,8 +10417,16 @@
           <t>gelatogiusto</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10316,7 +10446,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10351,8 +10481,16 @@
           <t>gnomogelato</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10372,7 +10510,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10407,8 +10545,16 @@
           <t>gusto17_ilgelato</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10428,7 +10574,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10463,8 +10609,16 @@
           <t>massimodelgelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10484,7 +10638,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10519,8 +10673,16 @@
           <t>labottegadelgelatocardelli</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr"/>
-      <c r="H174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I174" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10540,7 +10702,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10575,8 +10737,16 @@
           <t>lagelateriadellamusica</t>
         </is>
       </c>
-      <c r="G175" s="1" t="inlineStr"/>
-      <c r="H175" s="1" t="inlineStr"/>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I175" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10596,7 +10766,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10627,8 +10797,16 @@
           <t>noi_della_macelleriapopolare</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr"/>
-      <c r="H176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I176" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10648,7 +10826,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10870,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10897,11 @@
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr"/>
-      <c r="G178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
@@ -10740,7 +10922,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10966,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10819,8 +11001,16 @@
           <t>pavemilano</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr"/>
-      <c r="H180" s="1" t="inlineStr"/>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I180" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10840,7 +11030,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10875,8 +11065,16 @@
           <t>gelateriarigoletto</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr"/>
-      <c r="H181" s="1" t="inlineStr"/>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I181" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10896,7 +11094,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10931,8 +11129,16 @@
           <t>terragelato</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr"/>
-      <c r="H182" s="1" t="inlineStr"/>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I182" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10952,7 +11158,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11202,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11031,8 +11237,16 @@
           <t>trapizzino</t>
         </is>
       </c>
-      <c r="G184" s="1" t="inlineStr"/>
-      <c r="H184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I184" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11052,7 +11266,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -4033,128 +4033,124 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>U Barba - osteria genovese</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Via Pier Candido Decembrio, 33</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>02/45487032</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>www.ubarba.it</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>ubarba</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>ubarba</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R63" s="1" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Restaurant Guru 4.3 con 3474 recensioni, attivo 2026</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Velavevodetto</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Via Festa del Perdono, 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>02/92863557</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>www.ristorantevelavevodetto.it</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>velavevodetto</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>alvelavevodetto</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H64" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr"/>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 8.8/10 feb 2026, 654 recensioni</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4345,64 +4341,62 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Bussarakham</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Via Felice Bellotti, 13</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>02/66661066</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>www.bussarakham.com</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>thairestaurantbussarakham</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>bussarakham_mi</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated February 2026', TheFork attivo</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4466,188 +4460,181 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Casa Ramen Super</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Via Ugo Bassi, 26</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>02/83529210</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>www.casaramensuper.com</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>casaramensuper</t>
         </is>
       </c>
-      <c r="F69" s="1" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>casaramen</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H69" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr"/>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R69" s="1" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, presenza Facebook attiva, riferimenti 2026</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Gong - Oriental Attitude</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Corso Concordia, 8</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>02/76023873</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>www.gongmilano.it</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>GongRistorante</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>gongmilano</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H70" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr"/>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R70" s="1" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito attivo, prenotazioni online aperte 2026</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Il Gusto della Nebbia</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Via Privata Nino Bonnet, 11</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>351/9866676</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>ilgustodellanebbia</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>ilgustodellanebbia_milano</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr"/>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R71" s="1" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, info Yelp aggiornate gennaio 2026, dettagli orari aggiornati 7/3/2026</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4726,156 +4713,151 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Kanpai</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Via Melzo, 12</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>02/38269862 - 347/5188347</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>www.kanpaimilano.it</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>kanpairestaurantmilano</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>kanpai_milano</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr"/>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R73" s="1" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Wheree menu Updated 2026, sito attivo</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Le Nove Scodelle</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Viale Monza, 4</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>331/8001116</t>
         </is>
       </c>
-      <c r="D74" s="1" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>www.lenovescodelle.com</t>
         </is>
       </c>
-      <c r="E74" s="1" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>lenovescodelle</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Lenovescodelle</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H74" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr"/>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R74" s="1" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Restaurant Guru 4.2 con 2386 recensioni, recensioni 2025-2026</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Mao Hunan</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Via Nicola Antonio Porpora, 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>02/49787361</t>
         </is>
       </c>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>ristorantemao</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>maohunanrestaurant_x000d_
 maohunanrestaurant_x000d_
@@ -4884,190 +4866,173 @@
 maohunanrestaurant</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr"/>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R75" s="1" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026'</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Mido</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Via Pietro Custodi, 4</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>02/8375249</t>
         </is>
       </c>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>ristorantemidomilano</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr"/>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.1/10 con offerta sconto 30% attiva</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Mu dimsum</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Via Aminto Caretto, 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>338/3582658</t>
         </is>
       </c>
-      <c r="D77" s="1" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>www.mudimsum.it</t>
         </is>
       </c>
-      <c r="E77" s="1" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>MUDimSumMilano</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>mudimsum</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr"/>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R77" s="1" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026', 1712 recensioni</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Sakeya</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Via Cesare da Sesto, 1</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr"/>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R78" s="1" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito attivo, premio Gambero Rosso 2025</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5131,108 +5096,99 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Wicky’s Innovative Japanese Cuisine</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Corso Italia, 6</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>02/89093781</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr"/>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Michelin guide attiva, sito booking attivo</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Zazà Ramen</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Via Solferino, 48</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>02/36799000</t>
         </is>
       </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>www.zazaramen.it</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>zazaramen</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I81" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr"/>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R81" s="1" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated March 2026', TheFork 9.1/10 con 152 recensioni verificate</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5331,192 +5287,186 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Confine - Pizza e Cantina</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Massaia</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>375/5426086</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>www.confinemilano.it</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>profile.php?id=100075827156405</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>confine_milano</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr"/>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R83" s="1" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Wheree 'Updated March 2026', 50 Top Pizza #2 Italia</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Crosta</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Via Bellotti, 13</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>02/38248570</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>www.crosta.eu</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>crosta.milano</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>crosta_milano</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I84" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr"/>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R84" s="1" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Sluurpy aggiornato 24/01/2026, Google 4.2</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Da Zero</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Oberdan, 12</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>02/47704656</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>www.dazero.org</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>dazeroaltredici</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I85" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr"/>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R85" s="1" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated February 2026', nuova apertura Oberdan</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5637,44 +5587,37 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Due Forni</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Viale Monte Nero, 23</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>02/09978710</t>
         </is>
       </c>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr"/>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R88" s="1" t="inlineStr">
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026', citato in nuove aperture aprile 2026</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5887,44 +5830,37 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Bar Affori</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Via Alessandro Astesani, 15</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>02/66203236</t>
         </is>
       </c>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr"/>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R92" s="1" t="inlineStr">
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, articolo Gambero Rosso e blog Urbanfile gennaio 2026</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -6023,64 +5959,62 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Cafezal Specialty Coffee</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Viale Premuda, 14</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>02/36579282</t>
         </is>
       </c>
-      <c r="D94" s="1" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>www.cafezal.it</t>
         </is>
       </c>
-      <c r="E94" s="1" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>cafezal.milano</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H94" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I94" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr"/>
-      <c r="L94" s="1" t="inlineStr"/>
-      <c r="M94" s="1" t="inlineStr"/>
-      <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr"/>
-      <c r="P94" s="1" t="inlineStr"/>
-      <c r="Q94" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R94" s="1" t="inlineStr">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, premio Gambero Rosso 'Best Roaster 2026'</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -6146,7 +6080,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6124,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6245,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6309,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6353,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6397,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6441,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6497,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6561,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6625,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6689,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6749,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6813,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6914,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7044,7 +6978,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7095,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7159,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7310,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7354,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7406,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7470,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7534,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7598,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7642,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7698,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7742,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7794,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7854,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7914,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8036,7 +7970,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8034,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8192,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8256,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8300,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8356,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8400,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8464,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8528,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8592,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8656,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8720,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8784,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8828,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8892,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9002,7 +8936,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9000,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9056,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9100,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9144,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9188,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9252,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9308,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9352,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9404,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9460,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9524,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9588,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9648,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9708,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9772,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9816,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9876,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10012,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10076,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10132,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10192,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10252,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10316,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10380,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10444,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10508,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10572,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10636,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10700,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10760,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10804,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10856,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10900,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11030,7 +10964,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11028,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11092,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11136,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11200,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -6080,7 +6080,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -6080,7 +6080,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -6080,7 +6080,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -6080,7 +6080,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,18 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -47,7 +40,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,34 +48,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -469,92 +444,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nome Ristorante</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Indirizzo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Telefono</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ultimo post Facebook</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ultimo post Instagram</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Ultima revisione Google</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ultima revisione The Fork</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Ultima revisione Tripadvisor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Orari apertura</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Orari chiusura</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Social attivo?</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Menzioni notizie</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Note aggiuntive</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Data verifica</t>
         </is>
@@ -6510,4726 +6485,4829 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Clèa Pasticceria Culinaria</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Via Giacomo Boni, 25</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>02/83555166</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>www.pasticceriaclea.it</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>pasticceriaClea</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>pasticceriaclea</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '07:30', 'closes': '13'}, 'martedì': {'opens': '07:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (pasticceriaClea) | IG: trovato (pasticceriaclea)</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Coffee Studio 7gr.</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>Corso Venezia, 31</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>02/38238682</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr"/>
+      <c r="E103" s="1" t="inlineStr"/>
+      <c r="F103" s="1" t="inlineStr"/>
+      <c r="G103" s="1" t="inlineStr"/>
+      <c r="H103" s="1" t="inlineStr"/>
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="n"/>
-      <c r="L102" s="2" t="n"/>
-      <c r="M102" s="2" t="n"/>
-      <c r="N102" s="2" t="n"/>
-      <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="n"/>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>Err:HTTPSConnectionPool(host='serpapi.com',  | TF err:HTTPSConnectionPool( | FB err:HTTPSConnectionPool( | IG err:HTTPSConnectionPool(</t>
-        </is>
-      </c>
-      <c r="R102" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Coffee Studio 7gr.</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Corso Venezia, 31</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>02/38238682</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr"/>
+      <c r="K103" s="1" t="inlineStr"/>
+      <c r="L103" s="1" t="inlineStr"/>
+      <c r="M103" s="1" t="inlineStr"/>
+      <c r="N103" s="1" t="inlineStr"/>
+      <c r="O103" s="1" t="inlineStr"/>
+      <c r="P103" s="1" t="inlineStr"/>
+      <c r="Q103" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R103" s="1" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Égalité</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Via Melzo, 22</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>02/91763465</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>www.egalitemilano.it</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>egalitemilano</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>egalite_milano</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (egalitemilano) | IG: trovato (egalite_milano)</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Fòla</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Via Luigi Varanini, 12</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>02/49713413</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>www.folamilano.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>fola.milano.nolo</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>fola.milano</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '18'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (fola.milano.nolo) | IG: trovato (fola.milano)</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>I Dolci Namura</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Via Lodovico Castelvetro, 16</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>02/34534176</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07:30', 'closes': '20'}, '</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>La Bruma</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Piazza Vetra, 21</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '19'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>La Mary</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Via Marcona, 70</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>02/36599229</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07', 'closes': '20'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Le Polveri - panificio diurno</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Via Vespri Siciliani, 16</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>www.lepolveri.com</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>lepolveri</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '18:30'}, '</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (lepolveri)</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L'ile Douce</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Via Luigi Porro Lambertenghi, 15</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>02/49780658</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>www.iledoucemilano.it</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>iledoucemilano</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>iledoucemilano</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (iledoucemilano) | IG: trovato (iledoucemilano)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Loste Cafè</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Via Francesco Guicciardini, 3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>02/45375475</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>www.lostecafe.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>lostecafemilano</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>lostecafemilano</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lostecafemilano) | IG: trovato (lostecafemilano)</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Marlà</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Corso Lodi, 15</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>02/36536410</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>www.marlapasticceria.it</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>creiamodolcienonsolo</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>marlapasticceria</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '19'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (creiamodolcienonsolo) | IG: trovato (marlapasticceria)</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Nowhere - Coffee &amp; Community</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Via Vetere, 14</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>389/1078092</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>nowherecafe.it</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>nowherecafe.milano</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08:30', 'closes': '16'}, '</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (nowherecafe.it) | IG: trovato (nowherecafe.milano)</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Orsonero Coffee</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Broggi, 15</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>366/5477441</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>www.orsonerocoffee.it</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>orsonerocoffee</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>orsonerocoffee</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '17'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (orsonerocoffee) | IG: trovato (orsonerocoffee)</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sfoglia Pastry Lab</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Via Nicola Piccinni, 3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>345/1662856</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '21'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Signor Lievito</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Via Maestri Campionesi, 26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>02/91678209</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>www.signor-lievito.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>signorlievito</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>signor_lievito</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '16'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (signorlievito) | IG: trovato (signor_lievito)</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tre Chicchere</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Via Gian Antonio Boltraffio, 12</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>02/69007248</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Trechicchere</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>trechicchere</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '13'}, 'martedì': {'opens': '08, 13:30', 'c</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (Trechicchere) | IG: trovato (trechicchere)</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ziva</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Via Federico Faruffini, 2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>02/99266436</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>www.zivapasticceria.it</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>zivapasticceria</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>zivapasticceria</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (zivapasticceria) | IG: trovato (zivapasticceria)</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gastronomia Yamamoto</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Via Amedei, 5</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>02/36741426</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>www.gastronomiayamamoto.it</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>gastronomiayamamoto</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>gastronomiayamamoto</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gastronomiayamamoto) | IG: trovato (gastronomiayamamoto)</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Sapeto, 3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>June Collective</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Via Varesina, 162 c/o Certosa District</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>junecollectivemilano</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '09:30', 'closes': '15'}, 'martedì': {'opens': '09:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (junecollectivemilano)</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Katsusanderia</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Via Bonvesin de la Riva, 3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>www.katsusanderia.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>profile.php?id=100083562601123</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>katsusanderia</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19', 'closes': '15, 23</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100083562601123) | IG: trovato (katsusanderia)</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>La Ravioleria Sarpi</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Via Paolo Sarpi, 27</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>331/8870596</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>www.laravioleriasarpi.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ravioleriasarpi</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>laravioleriasarpi</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10:30, 16', 'closes': '15, 22', 'break': '15–16'}, 'marted</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ravioleriasarpi) | IG: trovato (laravioleriasarpi)</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Li - Sei Deli</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Via Vigevano, 9</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>02/49775083</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>www.lisei.it</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Li-Sei Deli</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>liseideli</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Li-Sei Deli) | IG: trovato (liseideli)</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Lile in cucina</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Piazza Carlo Maciachini, 18</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>02/36735997</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08:30', 'closes': '19'}, 'martedì': {'opens': '08:30', 'cl</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Via Leopoldo Cicognara, 19</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>340/8551831</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>www.panmilano.com</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>panmilano</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '17'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (panmilano)</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Rito</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Porta Venezia</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>02/38241909</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '16'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sandì</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Via Francesco Hayez, 13</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>02/82046200</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>sandi_ristorante</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '15'}, 'martedì': {'opens': 'Chiuso'}, '</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (sandi_ristorante)</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Stadera - gastronomia contemporanea</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Largo della Crocetta, 1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>340/6056240</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>staderamilano</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>stadera_milano</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '11:30, 18', 'closes': '15,</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (staderamilano) | IG: trovato (stadera_milano)</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Tone - Bread Lab.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Via Donatello, 22</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>351/8731109</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>tone.milano.breadlab</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>tone.milano</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (tone.milano.breadlab) | IG: trovato (tone.milano)</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Via Stampa</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Via Stampa, 8</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>02/30554088</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>www.viastampa.it</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>viastampa_milano</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (viastampa_milano)</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zibo - campo base</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Via Caminadella, 21</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>02/35999463</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>www.zibocuochiitineranti.it</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>zibocuochi</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>zibocuochi</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (zibocuochi) | IG: trovato (zibocuochi)</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>La Medina</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Via Tolentino, 1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>388/7940829</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>La Teiera Eclettica</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Via Melzo, 30</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>02/29419101</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>www.teieraeclettica.it</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LaTeieraEclettica</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>la_teiera_eclettica</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10, 14:45', 'closes': '13:</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (LaTeieraEclettica) | IG: trovato (la_teiera_eclettica)</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Momenteeria</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Via Giosuè Carducci, 38</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>02/36532185</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '20'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>Pasticceria Passerini dal 1919</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>Via Victor Hugo, 4</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>02/8693614</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>www.passerinilecco.it</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>pasticceriapasserini</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I136" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="n"/>
-      <c r="L103" s="2" t="n"/>
-      <c r="M103" s="2" t="n"/>
-      <c r="N103" s="2" t="n"/>
-      <c r="O103" s="2" t="n"/>
-      <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>Err:HTTPSConnectionPool(host='serpapi.com',  | TF err:HTTPSConnectionPool( | FB: no handle | IG: no handle</t>
-        </is>
-      </c>
-      <c r="R103" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Égalité</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Via Melzo, 22</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>02/91763465</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>www.egalitemilano.it</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>egalitemilano</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>egalite_milano</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
+      <c r="L136" s="1" t="inlineStr"/>
+      <c r="M136" s="1" t="inlineStr"/>
+      <c r="N136" s="1" t="inlineStr"/>
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R136" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>Brylla</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>Via Giovanni Rasori, 12</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>02/64089167</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="n"/>
-      <c r="L104" s="2" t="n"/>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="inlineStr">
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
+      <c r="L137" s="1" t="inlineStr"/>
+      <c r="M137" s="1" t="inlineStr"/>
+      <c r="N137" s="1" t="inlineStr"/>
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R104" s="2" t="inlineStr">
+      <c r="R137" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Fòla</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Via Luigi Varanini, 12</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>02/49713413</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>www.folamilano.com</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>fola.milano.nolo</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>fola.milano</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>Cantine Isola</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>Via Paolo Sarpi, 30</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>02/3315249</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>www.cantineisola.com</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>cantineisola</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>cantine_isola</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="n"/>
-      <c r="L105" s="2" t="n"/>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
-      <c r="Q105" s="2" t="inlineStr">
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
+      <c r="L138" s="1" t="inlineStr"/>
+      <c r="M138" s="1" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr"/>
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R105" s="2" t="inlineStr">
+      <c r="R138" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>I Dolci Namura</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Via Lodovico Castelvetro, 16</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>02/34534176</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>Ceresio 7</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>Via Ceresio, 7</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>02/31039221</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>www.ceresio7.com</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t>ceresio7</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>ceresio7</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I139" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="n"/>
-      <c r="L106" s="2" t="n"/>
-      <c r="M106" s="2" t="n"/>
-      <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
-      <c r="Q106" s="2" t="inlineStr">
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
+      <c r="L139" s="1" t="inlineStr"/>
+      <c r="M139" s="1" t="inlineStr"/>
+      <c r="N139" s="1" t="inlineStr"/>
+      <c r="O139" s="1" t="inlineStr"/>
+      <c r="P139" s="1" t="inlineStr"/>
+      <c r="Q139" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr">
+      <c r="R139" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>La Bruma</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Vetra, 21</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>Cru</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Sempione, 6</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>342/3040081</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>www.crumilano.com</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>crumilanowinebar</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>cru_milano</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I140" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
+      <c r="L140" s="1" t="inlineStr"/>
+      <c r="M140" s="1" t="inlineStr"/>
+      <c r="N140" s="1" t="inlineStr"/>
+      <c r="O140" s="1" t="inlineStr"/>
+      <c r="P140" s="1" t="inlineStr"/>
+      <c r="Q140" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R140" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>Enoteca Naturale</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>Via Santa Croce, 19/A</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>02/82770589</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>www.enotecanaturale.it</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="inlineStr">
+        <is>
+          <t>enotecanaturale</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>enotecanaturale</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I141" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
+      <c r="L141" s="1" t="inlineStr"/>
+      <c r="M141" s="1" t="inlineStr"/>
+      <c r="N141" s="1" t="inlineStr"/>
+      <c r="O141" s="1" t="inlineStr"/>
+      <c r="P141" s="1" t="inlineStr"/>
+      <c r="Q141" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R141" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>Flor. | born to be wine</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>Via Vigevano, 6</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>340/8587572</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>www.florwine.com</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
+        <is>
+          <t>milanoflor</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
+          <t>florenoteca.milano</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I142" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
+      <c r="L142" s="1" t="inlineStr"/>
+      <c r="M142" s="1" t="inlineStr"/>
+      <c r="N142" s="1" t="inlineStr"/>
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R142" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>Mesté - vino e fornelli</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>Via Corrado II il Salico, 12</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>346/8061538</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>www.meste.it</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
+        <is>
+          <t>mestemilano</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t>mestemilano</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H143" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
+      <c r="L143" s="1" t="inlineStr"/>
+      <c r="M143" s="1" t="inlineStr"/>
+      <c r="N143" s="1" t="inlineStr"/>
+      <c r="O143" s="1" t="inlineStr"/>
+      <c r="P143" s="1" t="inlineStr"/>
+      <c r="Q143" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R143" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Millésime 1990 - sorsi di Francia</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>Via Raffaello Sanzio, 4</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>02/36534945</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr"/>
+      <c r="E144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr"/>
+      <c r="H144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
+      <c r="L144" s="1" t="inlineStr"/>
+      <c r="M144" s="1" t="inlineStr"/>
+      <c r="N144" s="1" t="inlineStr"/>
+      <c r="O144" s="1" t="inlineStr"/>
+      <c r="P144" s="1" t="inlineStr"/>
+      <c r="Q144" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R144" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>Nik’s &amp; Co</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>Via Giovanni Schiaparelli, 14</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>02/91571797</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>www.niksandco.it</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
+        <is>
+          <t>niksandco</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>niks_co</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="H145" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I145" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
+      <c r="L145" s="1" t="inlineStr"/>
+      <c r="M145" s="1" t="inlineStr"/>
+      <c r="N145" s="1" t="inlineStr"/>
+      <c r="O145" s="1" t="inlineStr"/>
+      <c r="P145" s="1" t="inlineStr"/>
+      <c r="Q145" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R145" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>Shiua</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>Via Solari, 43</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>345/0229180</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="inlineStr"/>
+      <c r="E146" s="1" t="inlineStr"/>
+      <c r="F146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr"/>
+      <c r="H146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J146" s="1" t="inlineStr"/>
+      <c r="K146" s="1" t="inlineStr"/>
+      <c r="L146" s="1" t="inlineStr"/>
+      <c r="M146" s="1" t="inlineStr"/>
+      <c r="N146" s="1" t="inlineStr"/>
+      <c r="O146" s="1" t="inlineStr"/>
+      <c r="P146" s="1" t="inlineStr"/>
+      <c r="Q146" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R146" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>Tipografia Alimentare</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>Via Dolomiti, 1</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>02/83537868</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>www.tipografiaalimentare.it</t>
+        </is>
+      </c>
+      <c r="E147" s="1" t="inlineStr">
+        <is>
+          <t>tipografiaalimentare</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>tipografiaalimentare</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I147" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J147" s="1" t="inlineStr"/>
+      <c r="K147" s="1" t="inlineStr"/>
+      <c r="L147" s="1" t="inlineStr"/>
+      <c r="M147" s="1" t="inlineStr"/>
+      <c r="N147" s="1" t="inlineStr"/>
+      <c r="O147" s="1" t="inlineStr"/>
+      <c r="P147" s="1" t="inlineStr"/>
+      <c r="Q147" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R147" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Vineria Eretica</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>Via Rosolino Pilo, 14</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>02/45942171</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>www.vineriaeretica.it</t>
+        </is>
+      </c>
+      <c r="E148" s="1" t="inlineStr"/>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>vineriaeretica</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="inlineStr"/>
+      <c r="H148" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I148" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J148" s="1" t="inlineStr"/>
+      <c r="K148" s="1" t="inlineStr"/>
+      <c r="L148" s="1" t="inlineStr"/>
+      <c r="M148" s="1" t="inlineStr"/>
+      <c r="N148" s="1" t="inlineStr"/>
+      <c r="O148" s="1" t="inlineStr"/>
+      <c r="P148" s="1" t="inlineStr"/>
+      <c r="Q148" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R148" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Vinodromo</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>Via Salasco, 21</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>02/32960708</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr"/>
+      <c r="E149" s="1" t="inlineStr"/>
+      <c r="F149" s="1" t="inlineStr"/>
+      <c r="G149" s="1" t="inlineStr"/>
+      <c r="H149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J149" s="1" t="inlineStr"/>
+      <c r="K149" s="1" t="inlineStr"/>
+      <c r="L149" s="1" t="inlineStr"/>
+      <c r="M149" s="1" t="inlineStr"/>
+      <c r="N149" s="1" t="inlineStr"/>
+      <c r="O149" s="1" t="inlineStr"/>
+      <c r="P149" s="1" t="inlineStr"/>
+      <c r="Q149" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R149" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Wineria</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Carlo Caneva, 4</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>02/39464196</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr"/>
+      <c r="E150" s="1" t="inlineStr"/>
+      <c r="F150" s="1" t="inlineStr"/>
+      <c r="G150" s="1" t="inlineStr"/>
+      <c r="H150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J150" s="1" t="inlineStr"/>
+      <c r="K150" s="1" t="inlineStr"/>
+      <c r="L150" s="1" t="inlineStr"/>
+      <c r="M150" s="1" t="inlineStr"/>
+      <c r="N150" s="1" t="inlineStr"/>
+      <c r="O150" s="1" t="inlineStr"/>
+      <c r="P150" s="1" t="inlineStr"/>
+      <c r="Q150" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R150" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>Barba</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 40</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>02/36515846</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr"/>
+      <c r="E151" s="1" t="inlineStr"/>
+      <c r="F151" s="1" t="inlineStr"/>
+      <c r="G151" s="1" t="inlineStr"/>
+      <c r="H151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J151" s="1" t="inlineStr"/>
+      <c r="K151" s="1" t="inlineStr"/>
+      <c r="L151" s="1" t="inlineStr"/>
+      <c r="M151" s="1" t="inlineStr"/>
+      <c r="N151" s="1" t="inlineStr"/>
+      <c r="O151" s="1" t="inlineStr"/>
+      <c r="P151" s="1" t="inlineStr"/>
+      <c r="Q151" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R151" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>Osteria alla Concorrenza</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>Via Melzo, 12</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>02/91672012</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>www.osteriaallaconcorrenza.superbexperience.com</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t>osteriaallaconcorrenza</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="inlineStr">
+        <is>
+          <t>osteria_alla_concorrenza</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="inlineStr"/>
+      <c r="K152" s="1" t="inlineStr"/>
+      <c r="L152" s="1" t="inlineStr"/>
+      <c r="M152" s="1" t="inlineStr"/>
+      <c r="N152" s="1" t="inlineStr"/>
+      <c r="O152" s="1" t="inlineStr"/>
+      <c r="P152" s="1" t="inlineStr"/>
+      <c r="Q152" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R152" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Palinurobar</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>Via Giovanni Paisello, 28</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>www.palinurobar.it</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr"/>
+      <c r="F153" s="1" t="inlineStr">
+        <is>
+          <t>palinurobar</t>
+        </is>
+      </c>
+      <c r="G153" s="1" t="inlineStr"/>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I153" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="n"/>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="2" t="n"/>
-      <c r="N107" s="2" t="n"/>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="inlineStr">
+      <c r="J153" s="1" t="inlineStr"/>
+      <c r="K153" s="1" t="inlineStr"/>
+      <c r="L153" s="1" t="inlineStr"/>
+      <c r="M153" s="1" t="inlineStr"/>
+      <c r="N153" s="1" t="inlineStr"/>
+      <c r="O153" s="1" t="inlineStr"/>
+      <c r="P153" s="1" t="inlineStr"/>
+      <c r="Q153" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R107" s="2" t="inlineStr">
+      <c r="R153" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>La Mary</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Via Marcona, 70</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>02/36599229</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n"/>
-      <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>Porcobrado</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>Via Jacopo dal Verme, 17</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>02/87030181 - 338/3339120</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr"/>
+      <c r="E154" s="1" t="inlineStr"/>
+      <c r="F154" s="1" t="inlineStr"/>
+      <c r="G154" s="1" t="inlineStr"/>
+      <c r="H154" s="1" t="inlineStr"/>
+      <c r="I154" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="n"/>
-      <c r="L108" s="2" t="n"/>
-      <c r="M108" s="2" t="n"/>
-      <c r="N108" s="2" t="n"/>
-      <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
-      <c r="Q108" s="2" t="inlineStr">
+      <c r="J154" s="1" t="inlineStr"/>
+      <c r="K154" s="1" t="inlineStr"/>
+      <c r="L154" s="1" t="inlineStr"/>
+      <c r="M154" s="1" t="inlineStr"/>
+      <c r="N154" s="1" t="inlineStr"/>
+      <c r="O154" s="1" t="inlineStr"/>
+      <c r="P154" s="1" t="inlineStr"/>
+      <c r="Q154" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R108" s="2" t="inlineStr">
+      <c r="R154" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Le Polveri - panificio diurno</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Via Vespri Siciliani, 16</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>Silvano - vini e cibi al banco</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Morbegno, 2</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>02/72193827</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr"/>
+      <c r="E155" s="1" t="inlineStr"/>
+      <c r="F155" s="1" t="inlineStr">
+        <is>
+          <t>silvano_viniecibi</t>
+        </is>
+      </c>
+      <c r="G155" s="1" t="inlineStr"/>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J155" s="1" t="inlineStr"/>
+      <c r="K155" s="1" t="inlineStr"/>
+      <c r="L155" s="1" t="inlineStr"/>
+      <c r="M155" s="1" t="inlineStr"/>
+      <c r="N155" s="1" t="inlineStr"/>
+      <c r="O155" s="1" t="inlineStr"/>
+      <c r="P155" s="1" t="inlineStr"/>
+      <c r="Q155" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R155" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>Temp enoteca</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>Via Pasquale Sottocorno, 17</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>347/2402269</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>www.tempenoteca.it</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="inlineStr"/>
+      <c r="F156" s="1" t="inlineStr">
+        <is>
+          <t>temp.enoteca</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="inlineStr"/>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J156" s="1" t="inlineStr"/>
+      <c r="K156" s="1" t="inlineStr"/>
+      <c r="L156" s="1" t="inlineStr"/>
+      <c r="M156" s="1" t="inlineStr"/>
+      <c r="N156" s="1" t="inlineStr"/>
+      <c r="O156" s="1" t="inlineStr"/>
+      <c r="P156" s="1" t="inlineStr"/>
+      <c r="Q156" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R156" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>Kilburn</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>Via Panfilo Castaldi, 35</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>02/36580751</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>www.kilburncocktailbarmilano.it</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>KilburnMilano</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="inlineStr">
+        <is>
+          <t>kilburn_milano</t>
+        </is>
+      </c>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="inlineStr"/>
+      <c r="K157" s="1" t="inlineStr"/>
+      <c r="L157" s="1" t="inlineStr"/>
+      <c r="M157" s="1" t="inlineStr"/>
+      <c r="N157" s="1" t="inlineStr"/>
+      <c r="O157" s="1" t="inlineStr"/>
+      <c r="P157" s="1" t="inlineStr"/>
+      <c r="Q157" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R157" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Lacerba</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>Via Orti, 4</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>02/ 545 5475</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>www.lacerba.it</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>lacerba.milano</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t>lacerba.milano</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="inlineStr"/>
+      <c r="K158" s="1" t="inlineStr"/>
+      <c r="L158" s="1" t="inlineStr"/>
+      <c r="M158" s="1" t="inlineStr"/>
+      <c r="N158" s="1" t="inlineStr"/>
+      <c r="O158" s="1" t="inlineStr"/>
+      <c r="P158" s="1" t="inlineStr"/>
+      <c r="Q158" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R158" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>Mag cafè</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>Ripa di Porta Ticinese, 3</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>02/39562875</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr"/>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>magcafemilano</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>magcafe</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="inlineStr"/>
+      <c r="K159" s="1" t="inlineStr"/>
+      <c r="L159" s="1" t="inlineStr"/>
+      <c r="M159" s="1" t="inlineStr"/>
+      <c r="N159" s="1" t="inlineStr"/>
+      <c r="O159" s="1" t="inlineStr"/>
+      <c r="P159" s="1" t="inlineStr"/>
+      <c r="Q159" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R159" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>Norah was drunk</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>Via Nicola Antonio Porpora, 169</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>02/83428246 - 375/7746998</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr"/>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>norahwasdrunk</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>norah_milano</t>
+        </is>
+      </c>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="inlineStr"/>
+      <c r="K160" s="1" t="inlineStr"/>
+      <c r="L160" s="1" t="inlineStr"/>
+      <c r="M160" s="1" t="inlineStr"/>
+      <c r="N160" s="1" t="inlineStr"/>
+      <c r="O160" s="1" t="inlineStr"/>
+      <c r="P160" s="1" t="inlineStr"/>
+      <c r="Q160" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R160" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>Via Angelo Fumagalli, 1</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>02/8372865</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>www.ritacocktails.com</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>RitaCocktails</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t>ritacocktails</t>
+        </is>
+      </c>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="inlineStr"/>
+      <c r="K161" s="1" t="inlineStr"/>
+      <c r="L161" s="1" t="inlineStr"/>
+      <c r="M161" s="1" t="inlineStr"/>
+      <c r="N161" s="1" t="inlineStr"/>
+      <c r="O161" s="1" t="inlineStr"/>
+      <c r="P161" s="1" t="inlineStr"/>
+      <c r="Q161" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R161" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>Scott Bar</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>Viale Bianca Maria, 4</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>02/00244399</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr"/>
+      <c r="E162" s="1" t="inlineStr"/>
+      <c r="F162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr"/>
+      <c r="H162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J162" s="1" t="inlineStr"/>
+      <c r="K162" s="1" t="inlineStr"/>
+      <c r="L162" s="1" t="inlineStr"/>
+      <c r="M162" s="1" t="inlineStr"/>
+      <c r="N162" s="1" t="inlineStr"/>
+      <c r="O162" s="1" t="inlineStr"/>
+      <c r="P162" s="1" t="inlineStr"/>
+      <c r="Q162" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R162" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Tripstillery</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Alvar Aalto, snc</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>02/62061443</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr"/>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>tripstillery</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t>tripstillery</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J163" s="1" t="inlineStr"/>
+      <c r="K163" s="1" t="inlineStr"/>
+      <c r="L163" s="1" t="inlineStr"/>
+      <c r="M163" s="1" t="inlineStr"/>
+      <c r="N163" s="1" t="inlineStr"/>
+      <c r="O163" s="1" t="inlineStr"/>
+      <c r="P163" s="1" t="inlineStr"/>
+      <c r="Q163" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R163" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Bonci - pizza in teglia</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>Via Nicola Piccinni, 3</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>340/8223165</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr"/>
+      <c r="E164" s="1" t="inlineStr"/>
+      <c r="F164" s="1" t="inlineStr"/>
+      <c r="G164" s="1" t="inlineStr"/>
+      <c r="H164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J164" s="1" t="inlineStr"/>
+      <c r="K164" s="1" t="inlineStr"/>
+      <c r="L164" s="1" t="inlineStr"/>
+      <c r="M164" s="1" t="inlineStr"/>
+      <c r="N164" s="1" t="inlineStr"/>
+      <c r="O164" s="1" t="inlineStr"/>
+      <c r="P164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R164" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>Carmen Gelato</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>Via Carlo Ravizza, 3</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>02/84230543</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>www.carmengelato.com</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t>carmengelato.ita</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="inlineStr">
+        <is>
+          <t>carmen_gelato</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J165" s="1" t="inlineStr"/>
+      <c r="K165" s="1" t="inlineStr"/>
+      <c r="L165" s="1" t="inlineStr"/>
+      <c r="M165" s="1" t="inlineStr"/>
+      <c r="N165" s="1" t="inlineStr"/>
+      <c r="O165" s="1" t="inlineStr"/>
+      <c r="P165" s="1" t="inlineStr"/>
+      <c r="Q165" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R165" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>Ciacco</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>Via Spadari, 13</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>02/39663592</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>www.ciaccolab.it</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>ciaccogelato</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
+      <c r="L166" s="1" t="inlineStr"/>
+      <c r="M166" s="1" t="inlineStr"/>
+      <c r="N166" s="1" t="inlineStr"/>
+      <c r="O166" s="1" t="inlineStr"/>
+      <c r="P166" s="1" t="inlineStr"/>
+      <c r="Q166" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R166" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Gelateria LatteNeve</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>Via Vigevano, 27</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>02/39811258</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr"/>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>lattenevemilano</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t>latteneve</t>
+        </is>
+      </c>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
+      <c r="L167" s="1" t="inlineStr"/>
+      <c r="M167" s="1" t="inlineStr"/>
+      <c r="N167" s="1" t="inlineStr"/>
+      <c r="O167" s="1" t="inlineStr"/>
+      <c r="P167" s="1" t="inlineStr"/>
+      <c r="Q167" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R167" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>Gelateria Paganelli</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Via Adda, 3</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>02/42441183</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr"/>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>gelateriapaganelli</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="inlineStr">
+        <is>
+          <t>gelateriapaganelli</t>
+        </is>
+      </c>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
+      <c r="L168" s="1" t="inlineStr"/>
+      <c r="M168" s="1" t="inlineStr"/>
+      <c r="N168" s="1" t="inlineStr"/>
+      <c r="O168" s="1" t="inlineStr"/>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R168" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Gelateria Prossima Fermata</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>Via Melchiorre Gioia, 131</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>333/3112637</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>www.gelateria.company.site</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>gelateria.Prossima.Fermata</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="inlineStr">
+        <is>
+          <t>gelateria.prossima.fermata</t>
+        </is>
+      </c>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
+      <c r="L169" s="1" t="inlineStr"/>
+      <c r="M169" s="1" t="inlineStr"/>
+      <c r="N169" s="1" t="inlineStr"/>
+      <c r="O169" s="1" t="inlineStr"/>
+      <c r="P169" s="1" t="inlineStr"/>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R169" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>Gelato Giusto</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>Via San Gregorio, 17</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>02/29510284</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>www.gelatogiusto.it</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>gelatogiustomi</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="inlineStr">
+        <is>
+          <t>gelatogiusto</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I170" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J170" s="1" t="inlineStr"/>
+      <c r="K170" s="1" t="inlineStr"/>
+      <c r="L170" s="1" t="inlineStr"/>
+      <c r="M170" s="1" t="inlineStr"/>
+      <c r="N170" s="1" t="inlineStr"/>
+      <c r="O170" s="1" t="inlineStr"/>
+      <c r="P170" s="1" t="inlineStr"/>
+      <c r="Q170" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R170" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>GnomoGelato</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Cherubini, 3</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>02/4818134</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>www.lognomogelato.it</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="inlineStr">
+        <is>
+          <t>gnomogelato</t>
+        </is>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
+      <c r="L171" s="1" t="inlineStr"/>
+      <c r="M171" s="1" t="inlineStr"/>
+      <c r="N171" s="1" t="inlineStr"/>
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Gusto 17</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>Via Savona, 17</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>02/39811835</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>www.gusto17.com</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t>gusto17ilgelato</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="inlineStr">
+        <is>
+          <t>gusto17_ilgelato</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
+      <c r="L172" s="1" t="inlineStr"/>
+      <c r="M172" s="1" t="inlineStr"/>
+      <c r="N172" s="1" t="inlineStr"/>
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R172" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Il Massimo del Gelato</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>Via Lodovico Castelvetro, 18</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>02/3494943</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>www.ilmassimodelgelato.it</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="inlineStr">
+        <is>
+          <t>ilmassimodelgelatomilano</t>
+        </is>
+      </c>
+      <c r="F173" s="1" t="inlineStr">
+        <is>
+          <t>massimodelgelato</t>
+        </is>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I173" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J173" s="1" t="inlineStr"/>
+      <c r="K173" s="1" t="inlineStr"/>
+      <c r="L173" s="1" t="inlineStr"/>
+      <c r="M173" s="1" t="inlineStr"/>
+      <c r="N173" s="1" t="inlineStr"/>
+      <c r="O173" s="1" t="inlineStr"/>
+      <c r="P173" s="1" t="inlineStr"/>
+      <c r="Q173" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R173" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>La Bottega del Gelato Cardelli dal 1964</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>Via Giovanni Battista Pergolesi, 3</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>02/2940 0076</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>www.labottegadelgelato.it</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t>labottegadelgelatocardelli</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t>labottegadelgelatocardelli</t>
+        </is>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I174" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J174" s="1" t="inlineStr"/>
+      <c r="K174" s="1" t="inlineStr"/>
+      <c r="L174" s="1" t="inlineStr"/>
+      <c r="M174" s="1" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr"/>
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R174" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>La Gelateria della Musica</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>Via Lodovico il Moro, 3</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>02/39288619</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>www.lagelateriadellamusica.it</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>lagelateriadellamusica</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="inlineStr">
+        <is>
+          <t>lagelateriadellamusica</t>
+        </is>
+      </c>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I175" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J175" s="1" t="inlineStr"/>
+      <c r="K175" s="1" t="inlineStr"/>
+      <c r="L175" s="1" t="inlineStr"/>
+      <c r="M175" s="1" t="inlineStr"/>
+      <c r="N175" s="1" t="inlineStr"/>
+      <c r="O175" s="1" t="inlineStr"/>
+      <c r="P175" s="1" t="inlineStr"/>
+      <c r="Q175" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R175" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Macelleria Popolare</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>Piazza XXIV Maggio - Mercato Coperto</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>02/39468368</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr"/>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>mangiaridistradaalmercato</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="inlineStr">
+        <is>
+          <t>noi_della_macelleriapopolare</t>
+        </is>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
+      <c r="L176" s="1" t="inlineStr"/>
+      <c r="M176" s="1" t="inlineStr"/>
+      <c r="N176" s="1" t="inlineStr"/>
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R176" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Orto Gelato</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>Via Salvatore Pianell, 45</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>02/09954588</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr"/>
+      <c r="E177" s="1" t="inlineStr"/>
+      <c r="F177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr"/>
+      <c r="H177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J177" s="1" t="inlineStr"/>
+      <c r="K177" s="1" t="inlineStr"/>
+      <c r="L177" s="1" t="inlineStr"/>
+      <c r="M177" s="1" t="inlineStr"/>
+      <c r="N177" s="1" t="inlineStr"/>
+      <c r="O177" s="1" t="inlineStr"/>
+      <c r="P177" s="1" t="inlineStr"/>
+      <c r="Q177" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R177" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Out of the Box</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>Via Marcello Malpighi, 7</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>02/36637300</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr"/>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>outofthebox.gelato</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
+      <c r="L178" s="1" t="inlineStr"/>
+      <c r="M178" s="1" t="inlineStr"/>
+      <c r="N178" s="1" t="inlineStr"/>
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R178" s="1" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Pantera Pizza Rustica</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>Piazza XXIV Maggio - Mercato Coperto</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>www.lepolveri.com</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>lepolveri</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="D179" s="1" t="inlineStr"/>
+      <c r="E179" s="1" t="inlineStr"/>
+      <c r="F179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr"/>
+      <c r="H179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="n"/>
-      <c r="L109" s="2" t="n"/>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="2" t="n"/>
-      <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
+      <c r="L179" s="1" t="inlineStr"/>
+      <c r="M179" s="1" t="inlineStr"/>
+      <c r="N179" s="1" t="inlineStr"/>
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="R179" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>L'ile Douce</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Via Luigi Porro Lambertenghi, 15</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>02/49780658</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>www.iledoucemilano.it</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>iledoucemilano</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>iledoucemilano</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Pavè Gelati&amp;Granite</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Via Cesare Battisti, 21</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>02/94383619</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>www.pavemilano.com</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t>pavemilano</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t>pavemilano</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I180" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="n"/>
-      <c r="L110" s="2" t="n"/>
-      <c r="M110" s="2" t="n"/>
-      <c r="N110" s="2" t="n"/>
-      <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="inlineStr">
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
+      <c r="L180" s="1" t="inlineStr"/>
+      <c r="M180" s="1" t="inlineStr"/>
+      <c r="N180" s="1" t="inlineStr"/>
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
+      <c r="R180" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Loste Cafè</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Via Francesco Guicciardini, 3</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>02/45375475</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>www.lostecafe.com</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>lostecafemilano</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>lostecafemilano</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>Rigoletto</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>Via Cola di Rienzo, 2</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>02/38239075</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>www.gelateriarigoletto.it</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t>gelateriarigoletto.it</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="inlineStr">
+        <is>
+          <t>gelateriarigoletto</t>
+        </is>
+      </c>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I181" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="inlineStr">
+      <c r="J181" s="1" t="inlineStr"/>
+      <c r="K181" s="1" t="inlineStr"/>
+      <c r="L181" s="1" t="inlineStr"/>
+      <c r="M181" s="1" t="inlineStr"/>
+      <c r="N181" s="1" t="inlineStr"/>
+      <c r="O181" s="1" t="inlineStr"/>
+      <c r="P181" s="1" t="inlineStr"/>
+      <c r="Q181" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R111" s="2" t="inlineStr">
+      <c r="R181" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Marlà</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Corso Lodi, 15</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>02/36536410</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>www.marlapasticceria.it</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>creiamodolcienonsolo</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>marlapasticceria</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Terra Gelato</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Via Vitruvio, 38</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>02/91948458</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>www.terragelato.it</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>TerraGelato</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t>terragelato</t>
+        </is>
+      </c>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I182" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="n"/>
-      <c r="L112" s="2" t="n"/>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="2" t="n"/>
-      <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="inlineStr">
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
+      <c r="L182" s="1" t="inlineStr"/>
+      <c r="M182" s="1" t="inlineStr"/>
+      <c r="N182" s="1" t="inlineStr"/>
+      <c r="O182" s="1" t="inlineStr"/>
+      <c r="P182" s="1" t="inlineStr"/>
+      <c r="Q182" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R112" s="2" t="inlineStr">
+      <c r="R182" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Nowhere - Coffee &amp; Community</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Via Vetere, 14</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>389/1078092</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>nowherecafe.it</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>nowherecafe.milano</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Tra le righe Gelato &amp; Friends</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>Via Teodosio, 44</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>02/91762549</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr"/>
+      <c r="E183" s="1" t="inlineStr"/>
+      <c r="F183" s="1" t="inlineStr"/>
+      <c r="G183" s="1" t="inlineStr"/>
+      <c r="H183" s="1" t="inlineStr"/>
+      <c r="I183" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="n"/>
-      <c r="L113" s="2" t="n"/>
-      <c r="M113" s="2" t="n"/>
-      <c r="N113" s="2" t="n"/>
-      <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
-      <c r="Q113" s="2" t="inlineStr">
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
+      <c r="L183" s="1" t="inlineStr"/>
+      <c r="M183" s="1" t="inlineStr"/>
+      <c r="N183" s="1" t="inlineStr"/>
+      <c r="O183" s="1" t="inlineStr"/>
+      <c r="P183" s="1" t="inlineStr"/>
+      <c r="Q183" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="R183" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Orsonero Coffee</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Broggi, 15</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>366/5477441</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>www.orsonerocoffee.it</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>orsonerocoffee</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>orsonerocoffee</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Trapizzino</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Ripa di Porta Ticinese, 2</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>02/91570928</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>www.trapizzino.it</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>trapizzino</t>
+        </is>
+      </c>
+      <c r="F184" s="1" t="inlineStr">
+        <is>
+          <t>trapizzino</t>
+        </is>
+      </c>
+      <c r="G184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I184" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
-      <c r="L114" s="2" t="n"/>
-      <c r="M114" s="2" t="n"/>
-      <c r="N114" s="2" t="n"/>
-      <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="inlineStr">
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="inlineStr"/>
+      <c r="M184" s="1" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr"/>
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr">
         <is>
           <t>Non verificato in questa sessione</t>
         </is>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="R184" s="1" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Sfoglia Pastry Lab</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Via Nicola Piccinni, 3</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>345/1662856</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="n"/>
-      <c r="K115" s="2" t="n"/>
-      <c r="L115" s="2" t="n"/>
-      <c r="M115" s="2" t="n"/>
-      <c r="N115" s="2" t="n"/>
-      <c r="O115" s="2" t="n"/>
-      <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R115" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Signor Lievito</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Via Maestri Campionesi, 26</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>02/91678209</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>www.signor-lievito.com</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>signorlievito</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>signor_lievito</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="n"/>
-      <c r="K116" s="2" t="n"/>
-      <c r="L116" s="2" t="n"/>
-      <c r="M116" s="2" t="n"/>
-      <c r="N116" s="2" t="n"/>
-      <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
-      <c r="Q116" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R116" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Tre Chicchere</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Via Gian Antonio Boltraffio, 12</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>02/69007248</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Trechicchere</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>trechicchere</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="n"/>
-      <c r="K117" s="2" t="n"/>
-      <c r="L117" s="2" t="n"/>
-      <c r="M117" s="2" t="n"/>
-      <c r="N117" s="2" t="n"/>
-      <c r="O117" s="2" t="n"/>
-      <c r="P117" s="2" t="n"/>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R117" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Ziva</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Via Federico Faruffini, 2</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>02/99266436</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>www.zivapasticceria.it</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>zivapasticceria</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>zivapasticceria</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="n"/>
-      <c r="K118" s="2" t="n"/>
-      <c r="L118" s="2" t="n"/>
-      <c r="M118" s="2" t="n"/>
-      <c r="N118" s="2" t="n"/>
-      <c r="O118" s="2" t="n"/>
-      <c r="P118" s="2" t="n"/>
-      <c r="Q118" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R118" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Gastronomia Yamamoto</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Via Amedei, 5</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>02/36741426</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>www.gastronomiayamamoto.it</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>gastronomiayamamoto</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>gastronomiayamamoto</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n"/>
-      <c r="K119" s="2" t="n"/>
-      <c r="L119" s="2" t="n"/>
-      <c r="M119" s="2" t="n"/>
-      <c r="N119" s="2" t="n"/>
-      <c r="O119" s="2" t="n"/>
-      <c r="P119" s="2" t="n"/>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R119" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Hygge</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Sapeto, 3</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="n"/>
-      <c r="K120" s="2" t="n"/>
-      <c r="L120" s="2" t="n"/>
-      <c r="M120" s="2" t="n"/>
-      <c r="N120" s="2" t="n"/>
-      <c r="O120" s="2" t="n"/>
-      <c r="P120" s="2" t="n"/>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R120" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>June Collective</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Via Varesina, 162 c/o Certosa District</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>junecollectivemilano</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="n"/>
-      <c r="K121" s="2" t="n"/>
-      <c r="L121" s="2" t="n"/>
-      <c r="M121" s="2" t="n"/>
-      <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R121" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Katsusanderia</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Via Bonvesin de la Riva, 3</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>www.katsusanderia.com</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>profile.php?id=100083562601123</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>katsusanderia</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="n"/>
-      <c r="K122" s="2" t="n"/>
-      <c r="L122" s="2" t="n"/>
-      <c r="M122" s="2" t="n"/>
-      <c r="N122" s="2" t="n"/>
-      <c r="O122" s="2" t="n"/>
-      <c r="P122" s="2" t="n"/>
-      <c r="Q122" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R122" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>La Ravioleria Sarpi</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Via Paolo Sarpi, 27</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>331/8870596</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>www.laravioleriasarpi.com</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>ravioleriasarpi</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>laravioleriasarpi</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="n"/>
-      <c r="K123" s="2" t="n"/>
-      <c r="L123" s="2" t="n"/>
-      <c r="M123" s="2" t="n"/>
-      <c r="N123" s="2" t="n"/>
-      <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R123" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Li - Sei Deli</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Via Vigevano, 9</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>02/49775083</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>www.lisei.it</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Li-Sei Deli</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>liseideli</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="n"/>
-      <c r="K124" s="2" t="n"/>
-      <c r="L124" s="2" t="n"/>
-      <c r="M124" s="2" t="n"/>
-      <c r="N124" s="2" t="n"/>
-      <c r="O124" s="2" t="n"/>
-      <c r="P124" s="2" t="n"/>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Lile in cucina</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Carlo Maciachini, 18</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>02/36735997</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="n"/>
-      <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="n"/>
-      <c r="L125" s="2" t="n"/>
-      <c r="M125" s="2" t="n"/>
-      <c r="N125" s="2" t="n"/>
-      <c r="O125" s="2" t="n"/>
-      <c r="P125" s="2" t="n"/>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R125" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Pan</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Via Leopoldo Cicognara, 19</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>340/8551831</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>www.panmilano.com</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>panmilano</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="n"/>
-      <c r="L126" s="2" t="n"/>
-      <c r="M126" s="2" t="n"/>
-      <c r="N126" s="2" t="n"/>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R126" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Rito</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Porta Venezia</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>02/38241909</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="n"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="n"/>
-      <c r="K127" s="2" t="n"/>
-      <c r="L127" s="2" t="n"/>
-      <c r="M127" s="2" t="n"/>
-      <c r="N127" s="2" t="n"/>
-      <c r="O127" s="2" t="n"/>
-      <c r="P127" s="2" t="n"/>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R127" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Sandì</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Via Francesco Hayez, 13</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>02/82046200</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>sandi_ristorante</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="n"/>
-      <c r="K128" s="2" t="n"/>
-      <c r="L128" s="2" t="n"/>
-      <c r="M128" s="2" t="n"/>
-      <c r="N128" s="2" t="n"/>
-      <c r="O128" s="2" t="n"/>
-      <c r="P128" s="2" t="n"/>
-      <c r="Q128" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R128" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Stadera - gastronomia contemporanea</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Largo della Crocetta, 1</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>340/6056240</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>staderamilano</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>stadera_milano</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="n"/>
-      <c r="L129" s="2" t="n"/>
-      <c r="M129" s="2" t="n"/>
-      <c r="N129" s="2" t="n"/>
-      <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R129" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Tone - Bread Lab.</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Via Donatello, 22</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>351/8731109</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>tone.milano.breadlab</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>tone.milano</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
-      <c r="L130" s="2" t="n"/>
-      <c r="M130" s="2" t="n"/>
-      <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="n"/>
-      <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R130" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>Via Stampa</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Via Stampa, 8</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>02/30554088</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>www.viastampa.it</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>viastampa_milano</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="n"/>
-      <c r="K131" s="2" t="n"/>
-      <c r="L131" s="2" t="n"/>
-      <c r="M131" s="2" t="n"/>
-      <c r="N131" s="2" t="n"/>
-      <c r="O131" s="2" t="n"/>
-      <c r="P131" s="2" t="n"/>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R131" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Zibo - campo base</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Via Caminadella, 21</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>02/35999463</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>www.zibocuochiitineranti.it</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>zibocuochi</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>zibocuochi</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="n"/>
-      <c r="K132" s="2" t="n"/>
-      <c r="L132" s="2" t="n"/>
-      <c r="M132" s="2" t="n"/>
-      <c r="N132" s="2" t="n"/>
-      <c r="O132" s="2" t="n"/>
-      <c r="P132" s="2" t="n"/>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>La Medina</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Via Tolentino, 1</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>388/7940829</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n"/>
-      <c r="E133" s="2" t="n"/>
-      <c r="F133" s="2" t="n"/>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="n"/>
-      <c r="K133" s="2" t="n"/>
-      <c r="L133" s="2" t="n"/>
-      <c r="M133" s="2" t="n"/>
-      <c r="N133" s="2" t="n"/>
-      <c r="O133" s="2" t="n"/>
-      <c r="P133" s="2" t="n"/>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>La Teiera Eclettica</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Via Melzo, 30</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>02/29419101</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>www.teieraeclettica.it</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>LaTeieraEclettica</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>la_teiera_eclettica</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="n"/>
-      <c r="K134" s="2" t="n"/>
-      <c r="L134" s="2" t="n"/>
-      <c r="M134" s="2" t="n"/>
-      <c r="N134" s="2" t="n"/>
-      <c r="O134" s="2" t="n"/>
-      <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Momenteeria</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Via Giosuè Carducci, 38</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>02/36532185</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="n"/>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="n"/>
-      <c r="K135" s="2" t="n"/>
-      <c r="L135" s="2" t="n"/>
-      <c r="M135" s="2" t="n"/>
-      <c r="N135" s="2" t="n"/>
-      <c r="O135" s="2" t="n"/>
-      <c r="P135" s="2" t="n"/>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Pasticceria Passerini dal 1919</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Via Victor Hugo, 4</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>02/8693614</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>www.passerinilecco.it</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>pasticceriapasserini</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="n"/>
-      <c r="K136" s="2" t="n"/>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="n"/>
-      <c r="O136" s="2" t="n"/>
-      <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Brylla</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Via Giovanni Rasori, 12</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>02/64089167</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-      <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="n"/>
-      <c r="K137" s="2" t="n"/>
-      <c r="L137" s="2" t="n"/>
-      <c r="M137" s="2" t="n"/>
-      <c r="N137" s="2" t="n"/>
-      <c r="O137" s="2" t="n"/>
-      <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Cantine Isola</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Via Paolo Sarpi, 30</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>02/3315249</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>www.cantineisola.com</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>cantineisola</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>cantine_isola</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n"/>
-      <c r="K138" s="2" t="n"/>
-      <c r="L138" s="2" t="n"/>
-      <c r="M138" s="2" t="n"/>
-      <c r="N138" s="2" t="n"/>
-      <c r="O138" s="2" t="n"/>
-      <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Ceresio 7</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Via Ceresio, 7</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>02/31039221</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>www.ceresio7.com</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>ceresio7</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>ceresio7</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="n"/>
-      <c r="L139" s="2" t="n"/>
-      <c r="M139" s="2" t="n"/>
-      <c r="N139" s="2" t="n"/>
-      <c r="O139" s="2" t="n"/>
-      <c r="P139" s="2" t="n"/>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Cru</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Sempione, 6</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>342/3040081</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>www.crumilano.com</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>crumilanowinebar</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>cru_milano</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n"/>
-      <c r="K140" s="2" t="n"/>
-      <c r="L140" s="2" t="n"/>
-      <c r="M140" s="2" t="n"/>
-      <c r="N140" s="2" t="n"/>
-      <c r="O140" s="2" t="n"/>
-      <c r="P140" s="2" t="n"/>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Enoteca Naturale</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Via Santa Croce, 19/A</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>02/82770589</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>www.enotecanaturale.it</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>enotecanaturale</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>enotecanaturale</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n"/>
-      <c r="K141" s="2" t="n"/>
-      <c r="L141" s="2" t="n"/>
-      <c r="M141" s="2" t="n"/>
-      <c r="N141" s="2" t="n"/>
-      <c r="O141" s="2" t="n"/>
-      <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R141" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Flor. | born to be wine</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Via Vigevano, 6</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>340/8587572</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>www.florwine.com</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>milanoflor</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>florenoteca.milano</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="n"/>
-      <c r="N142" s="2" t="n"/>
-      <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Mesté - vino e fornelli</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Via Corrado II il Salico, 12</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>346/8061538</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>www.meste.it</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>mestemilano</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>mestemilano</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n"/>
-      <c r="K143" s="2" t="n"/>
-      <c r="L143" s="2" t="n"/>
-      <c r="M143" s="2" t="n"/>
-      <c r="N143" s="2" t="n"/>
-      <c r="O143" s="2" t="n"/>
-      <c r="P143" s="2" t="n"/>
-      <c r="Q143" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R143" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Millésime 1990 - sorsi di Francia</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Via Raffaello Sanzio, 4</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>02/36534945</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="n"/>
-      <c r="G144" s="2" t="n"/>
-      <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n"/>
-      <c r="K144" s="2" t="n"/>
-      <c r="L144" s="2" t="n"/>
-      <c r="M144" s="2" t="n"/>
-      <c r="N144" s="2" t="n"/>
-      <c r="O144" s="2" t="n"/>
-      <c r="P144" s="2" t="n"/>
-      <c r="Q144" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R144" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Nik’s &amp; Co</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Via Giovanni Schiaparelli, 14</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>02/91571797</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>www.niksandco.it</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>niksandco</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>niks_co</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>01/02/2026</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="n"/>
-      <c r="L145" s="2" t="n"/>
-      <c r="M145" s="2" t="n"/>
-      <c r="N145" s="2" t="n"/>
-      <c r="O145" s="2" t="n"/>
-      <c r="P145" s="2" t="n"/>
-      <c r="Q145" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R145" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Shiua</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Via Solari, 43</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>345/0229180</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="n"/>
-      <c r="L146" s="2" t="n"/>
-      <c r="M146" s="2" t="n"/>
-      <c r="N146" s="2" t="n"/>
-      <c r="O146" s="2" t="n"/>
-      <c r="P146" s="2" t="n"/>
-      <c r="Q146" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R146" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Tipografia Alimentare</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>Via Dolomiti, 1</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>02/83537868</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>www.tipografiaalimentare.it</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>tipografiaalimentare</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>tipografiaalimentare</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n"/>
-      <c r="K147" s="2" t="n"/>
-      <c r="L147" s="2" t="n"/>
-      <c r="M147" s="2" t="n"/>
-      <c r="N147" s="2" t="n"/>
-      <c r="O147" s="2" t="n"/>
-      <c r="P147" s="2" t="n"/>
-      <c r="Q147" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R147" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Vineria Eretica</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Via Rosolino Pilo, 14</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>02/45942171</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>www.vineriaeretica.it</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>vineriaeretica</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n"/>
-      <c r="K148" s="2" t="n"/>
-      <c r="L148" s="2" t="n"/>
-      <c r="M148" s="2" t="n"/>
-      <c r="N148" s="2" t="n"/>
-      <c r="O148" s="2" t="n"/>
-      <c r="P148" s="2" t="n"/>
-      <c r="Q148" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R148" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Vinodromo</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>Via Salasco, 21</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>02/32960708</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n"/>
-      <c r="G149" s="2" t="n"/>
-      <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n"/>
-      <c r="K149" s="2" t="n"/>
-      <c r="L149" s="2" t="n"/>
-      <c r="M149" s="2" t="n"/>
-      <c r="N149" s="2" t="n"/>
-      <c r="O149" s="2" t="n"/>
-      <c r="P149" s="2" t="n"/>
-      <c r="Q149" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R149" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Wineria</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Carlo Caneva, 4</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>02/39464196</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="n"/>
-      <c r="G150" s="2" t="n"/>
-      <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n"/>
-      <c r="K150" s="2" t="n"/>
-      <c r="L150" s="2" t="n"/>
-      <c r="M150" s="2" t="n"/>
-      <c r="N150" s="2" t="n"/>
-      <c r="O150" s="2" t="n"/>
-      <c r="P150" s="2" t="n"/>
-      <c r="Q150" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R150" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>Barba</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>Via San Gregorio, 40</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>02/36515846</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
-      <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="n"/>
-      <c r="L151" s="2" t="n"/>
-      <c r="M151" s="2" t="n"/>
-      <c r="N151" s="2" t="n"/>
-      <c r="O151" s="2" t="n"/>
-      <c r="P151" s="2" t="n"/>
-      <c r="Q151" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R151" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Osteria alla Concorrenza</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Via Melzo, 12</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>02/91672012</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>www.osteriaallaconcorrenza.superbexperience.com</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>osteriaallaconcorrenza</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>osteria_alla_concorrenza</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n"/>
-      <c r="K152" s="2" t="n"/>
-      <c r="L152" s="2" t="n"/>
-      <c r="M152" s="2" t="n"/>
-      <c r="N152" s="2" t="n"/>
-      <c r="O152" s="2" t="n"/>
-      <c r="P152" s="2" t="n"/>
-      <c r="Q152" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R152" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>Palinurobar</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>Via Giovanni Paisello, 28</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>www.palinurobar.it</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>palinurobar</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="n"/>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="n"/>
-      <c r="L153" s="2" t="n"/>
-      <c r="M153" s="2" t="n"/>
-      <c r="N153" s="2" t="n"/>
-      <c r="O153" s="2" t="n"/>
-      <c r="P153" s="2" t="n"/>
-      <c r="Q153" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R153" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Porcobrado</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Via Jacopo dal Verme, 17</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>02/87030181 - 338/3339120</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="n"/>
-      <c r="L154" s="2" t="n"/>
-      <c r="M154" s="2" t="n"/>
-      <c r="N154" s="2" t="n"/>
-      <c r="O154" s="2" t="n"/>
-      <c r="P154" s="2" t="n"/>
-      <c r="Q154" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R154" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Silvano - vini e cibi al banco</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Morbegno, 2</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>02/72193827</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>silvano_viniecibi</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="n"/>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n"/>
-      <c r="K155" s="2" t="n"/>
-      <c r="L155" s="2" t="n"/>
-      <c r="M155" s="2" t="n"/>
-      <c r="N155" s="2" t="n"/>
-      <c r="O155" s="2" t="n"/>
-      <c r="P155" s="2" t="n"/>
-      <c r="Q155" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R155" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Temp enoteca</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Via Pasquale Sottocorno, 17</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>347/2402269</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>www.tempenoteca.it</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="n"/>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>temp.enoteca</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="n"/>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n"/>
-      <c r="K156" s="2" t="n"/>
-      <c r="L156" s="2" t="n"/>
-      <c r="M156" s="2" t="n"/>
-      <c r="N156" s="2" t="n"/>
-      <c r="O156" s="2" t="n"/>
-      <c r="P156" s="2" t="n"/>
-      <c r="Q156" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R156" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Kilburn</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>Via Panfilo Castaldi, 35</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>02/36580751</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>www.kilburncocktailbarmilano.it</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>KilburnMilano</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>kilburn_milano</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n"/>
-      <c r="K157" s="2" t="n"/>
-      <c r="L157" s="2" t="n"/>
-      <c r="M157" s="2" t="n"/>
-      <c r="N157" s="2" t="n"/>
-      <c r="O157" s="2" t="n"/>
-      <c r="P157" s="2" t="n"/>
-      <c r="Q157" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R157" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Lacerba</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Via Orti, 4</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>02/ 545 5475</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>www.lacerba.it</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>lacerba.milano</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>lacerba.milano</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n"/>
-      <c r="K158" s="2" t="n"/>
-      <c r="L158" s="2" t="n"/>
-      <c r="M158" s="2" t="n"/>
-      <c r="N158" s="2" t="n"/>
-      <c r="O158" s="2" t="n"/>
-      <c r="P158" s="2" t="n"/>
-      <c r="Q158" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R158" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Mag cafè</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>Ripa di Porta Ticinese, 3</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>02/39562875</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>magcafemilano</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>magcafe</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n"/>
-      <c r="K159" s="2" t="n"/>
-      <c r="L159" s="2" t="n"/>
-      <c r="M159" s="2" t="n"/>
-      <c r="N159" s="2" t="n"/>
-      <c r="O159" s="2" t="n"/>
-      <c r="P159" s="2" t="n"/>
-      <c r="Q159" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R159" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Norah was drunk</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Via Nicola Antonio Porpora, 169</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>02/83428246 - 375/7746998</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>norahwasdrunk</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>norah_milano</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n"/>
-      <c r="K160" s="2" t="n"/>
-      <c r="L160" s="2" t="n"/>
-      <c r="M160" s="2" t="n"/>
-      <c r="N160" s="2" t="n"/>
-      <c r="O160" s="2" t="n"/>
-      <c r="P160" s="2" t="n"/>
-      <c r="Q160" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R160" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>Rita</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>Via Angelo Fumagalli, 1</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>02/8372865</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>www.ritacocktails.com</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>RitaCocktails</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>ritacocktails</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n"/>
-      <c r="K161" s="2" t="n"/>
-      <c r="L161" s="2" t="n"/>
-      <c r="M161" s="2" t="n"/>
-      <c r="N161" s="2" t="n"/>
-      <c r="O161" s="2" t="n"/>
-      <c r="P161" s="2" t="n"/>
-      <c r="Q161" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R161" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Scott Bar</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>Viale Bianca Maria, 4</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>02/00244399</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="n"/>
-      <c r="G162" s="2" t="n"/>
-      <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="n"/>
-      <c r="L162" s="2" t="n"/>
-      <c r="M162" s="2" t="n"/>
-      <c r="N162" s="2" t="n"/>
-      <c r="O162" s="2" t="n"/>
-      <c r="P162" s="2" t="n"/>
-      <c r="Q162" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R162" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Tripstillery</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Piazza Alvar Aalto, snc</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>02/62061443</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>tripstillery</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>tripstillery</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n"/>
-      <c r="K163" s="2" t="n"/>
-      <c r="L163" s="2" t="n"/>
-      <c r="M163" s="2" t="n"/>
-      <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="n"/>
-      <c r="P163" s="2" t="n"/>
-      <c r="Q163" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R163" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Bonci - pizza in teglia</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Via Nicola Piccinni, 3</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>340/8223165</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" s="2" t="n"/>
-      <c r="F164" s="2" t="n"/>
-      <c r="G164" s="2" t="n"/>
-      <c r="H164" s="2" t="n"/>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n"/>
-      <c r="K164" s="2" t="n"/>
-      <c r="L164" s="2" t="n"/>
-      <c r="M164" s="2" t="n"/>
-      <c r="N164" s="2" t="n"/>
-      <c r="O164" s="2" t="n"/>
-      <c r="P164" s="2" t="n"/>
-      <c r="Q164" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R164" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Carmen Gelato</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Via Carlo Ravizza, 3</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>02/84230543</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>www.carmengelato.com</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>carmengelato.ita</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>carmen_gelato</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n"/>
-      <c r="K165" s="2" t="n"/>
-      <c r="L165" s="2" t="n"/>
-      <c r="M165" s="2" t="n"/>
-      <c r="N165" s="2" t="n"/>
-      <c r="O165" s="2" t="n"/>
-      <c r="P165" s="2" t="n"/>
-      <c r="Q165" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R165" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Ciacco</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Via Spadari, 13</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>02/39663592</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>www.ciaccolab.it</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>ciaccogelato</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="n"/>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n"/>
-      <c r="K166" s="2" t="n"/>
-      <c r="L166" s="2" t="n"/>
-      <c r="M166" s="2" t="n"/>
-      <c r="N166" s="2" t="n"/>
-      <c r="O166" s="2" t="n"/>
-      <c r="P166" s="2" t="n"/>
-      <c r="Q166" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R166" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Gelateria LatteNeve</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Via Vigevano, 27</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>02/39811258</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>lattenevemilano</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>latteneve</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n"/>
-      <c r="K167" s="2" t="n"/>
-      <c r="L167" s="2" t="n"/>
-      <c r="M167" s="2" t="n"/>
-      <c r="N167" s="2" t="n"/>
-      <c r="O167" s="2" t="n"/>
-      <c r="P167" s="2" t="n"/>
-      <c r="Q167" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R167" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Gelateria Paganelli</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Via Adda, 3</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>02/42441183</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>gelateriapaganelli</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>gelateriapaganelli</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n"/>
-      <c r="K168" s="2" t="n"/>
-      <c r="L168" s="2" t="n"/>
-      <c r="M168" s="2" t="n"/>
-      <c r="N168" s="2" t="n"/>
-      <c r="O168" s="2" t="n"/>
-      <c r="P168" s="2" t="n"/>
-      <c r="Q168" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R168" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>Gelateria Prossima Fermata</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Via Melchiorre Gioia, 131</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>333/3112637</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>www.gelateria.company.site</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>gelateria.Prossima.Fermata</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>gelateria.prossima.fermata</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n"/>
-      <c r="K169" s="2" t="n"/>
-      <c r="L169" s="2" t="n"/>
-      <c r="M169" s="2" t="n"/>
-      <c r="N169" s="2" t="n"/>
-      <c r="O169" s="2" t="n"/>
-      <c r="P169" s="2" t="n"/>
-      <c r="Q169" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R169" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Gelato Giusto</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>Via San Gregorio, 17</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>02/29510284</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>www.gelatogiusto.it</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>gelatogiustomi</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>gelatogiusto</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n"/>
-      <c r="K170" s="2" t="n"/>
-      <c r="L170" s="2" t="n"/>
-      <c r="M170" s="2" t="n"/>
-      <c r="N170" s="2" t="n"/>
-      <c r="O170" s="2" t="n"/>
-      <c r="P170" s="2" t="n"/>
-      <c r="Q170" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R170" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>GnomoGelato</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>Via Francesco Cherubini, 3</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>02/4818134</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>www.lognomogelato.it</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>gnomogelato</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>gnomogelato</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n"/>
-      <c r="K171" s="2" t="n"/>
-      <c r="L171" s="2" t="n"/>
-      <c r="M171" s="2" t="n"/>
-      <c r="N171" s="2" t="n"/>
-      <c r="O171" s="2" t="n"/>
-      <c r="P171" s="2" t="n"/>
-      <c r="Q171" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Gusto 17</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Via Savona, 17</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>02/39811835</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>www.gusto17.com</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>gusto17ilgelato</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>gusto17_ilgelato</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n"/>
-      <c r="K172" s="2" t="n"/>
-      <c r="L172" s="2" t="n"/>
-      <c r="M172" s="2" t="n"/>
-      <c r="N172" s="2" t="n"/>
-      <c r="O172" s="2" t="n"/>
-      <c r="P172" s="2" t="n"/>
-      <c r="Q172" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R172" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Il Massimo del Gelato</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Via Lodovico Castelvetro, 18</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>02/3494943</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>www.ilmassimodelgelato.it</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>ilmassimodelgelatomilano</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>massimodelgelato</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n"/>
-      <c r="K173" s="2" t="n"/>
-      <c r="L173" s="2" t="n"/>
-      <c r="M173" s="2" t="n"/>
-      <c r="N173" s="2" t="n"/>
-      <c r="O173" s="2" t="n"/>
-      <c r="P173" s="2" t="n"/>
-      <c r="Q173" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R173" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>La Bottega del Gelato Cardelli dal 1964</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Via Giovanni Battista Pergolesi, 3</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>02/2940 0076</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>www.labottegadelgelato.it</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>labottegadelgelatocardelli</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>labottegadelgelatocardelli</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n"/>
-      <c r="K174" s="2" t="n"/>
-      <c r="L174" s="2" t="n"/>
-      <c r="M174" s="2" t="n"/>
-      <c r="N174" s="2" t="n"/>
-      <c r="O174" s="2" t="n"/>
-      <c r="P174" s="2" t="n"/>
-      <c r="Q174" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R174" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>La Gelateria della Musica</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Via Lodovico il Moro, 3</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>02/39288619</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>www.lagelateriadellamusica.it</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>lagelateriadellamusica</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>lagelateriadellamusica</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n"/>
-      <c r="K175" s="2" t="n"/>
-      <c r="L175" s="2" t="n"/>
-      <c r="M175" s="2" t="n"/>
-      <c r="N175" s="2" t="n"/>
-      <c r="O175" s="2" t="n"/>
-      <c r="P175" s="2" t="n"/>
-      <c r="Q175" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R175" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Macelleria Popolare</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>Piazza XXIV Maggio - Mercato Coperto</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>02/39468368</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>mangiaridistradaalmercato</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>noi_della_macelleriapopolare</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n"/>
-      <c r="K176" s="2" t="n"/>
-      <c r="L176" s="2" t="n"/>
-      <c r="M176" s="2" t="n"/>
-      <c r="N176" s="2" t="n"/>
-      <c r="O176" s="2" t="n"/>
-      <c r="P176" s="2" t="n"/>
-      <c r="Q176" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R176" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>Orto Gelato</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>Via Salvatore Pianell, 45</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>02/09954588</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="n"/>
-      <c r="F177" s="2" t="n"/>
-      <c r="G177" s="2" t="n"/>
-      <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n"/>
-      <c r="K177" s="2" t="n"/>
-      <c r="L177" s="2" t="n"/>
-      <c r="M177" s="2" t="n"/>
-      <c r="N177" s="2" t="n"/>
-      <c r="O177" s="2" t="n"/>
-      <c r="P177" s="2" t="n"/>
-      <c r="Q177" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R177" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>Out of the Box</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>Via Marcello Malpighi, 7</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>02/36637300</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>outofthebox.gelato</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="n"/>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="n"/>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n"/>
-      <c r="K178" s="2" t="n"/>
-      <c r="L178" s="2" t="n"/>
-      <c r="M178" s="2" t="n"/>
-      <c r="N178" s="2" t="n"/>
-      <c r="O178" s="2" t="n"/>
-      <c r="P178" s="2" t="n"/>
-      <c r="Q178" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R178" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Pantera Pizza Rustica</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>Piazza XXIV Maggio - Mercato Coperto</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="2" t="n"/>
-      <c r="F179" s="2" t="n"/>
-      <c r="G179" s="2" t="n"/>
-      <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n"/>
-      <c r="K179" s="2" t="n"/>
-      <c r="L179" s="2" t="n"/>
-      <c r="M179" s="2" t="n"/>
-      <c r="N179" s="2" t="n"/>
-      <c r="O179" s="2" t="n"/>
-      <c r="P179" s="2" t="n"/>
-      <c r="Q179" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R179" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Pavè Gelati&amp;Granite</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Via Cesare Battisti, 21</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>02/94383619</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>www.pavemilano.com</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>pavemilano</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>pavemilano</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n"/>
-      <c r="K180" s="2" t="n"/>
-      <c r="L180" s="2" t="n"/>
-      <c r="M180" s="2" t="n"/>
-      <c r="N180" s="2" t="n"/>
-      <c r="O180" s="2" t="n"/>
-      <c r="P180" s="2" t="n"/>
-      <c r="Q180" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R180" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>Rigoletto</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>Via Cola di Rienzo, 2</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>02/38239075</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>www.gelateriarigoletto.it</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>gelateriarigoletto.it</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>gelateriarigoletto</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n"/>
-      <c r="K181" s="2" t="n"/>
-      <c r="L181" s="2" t="n"/>
-      <c r="M181" s="2" t="n"/>
-      <c r="N181" s="2" t="n"/>
-      <c r="O181" s="2" t="n"/>
-      <c r="P181" s="2" t="n"/>
-      <c r="Q181" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R181" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Terra Gelato</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>Via Vitruvio, 38</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>02/91948458</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>www.terragelato.it</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>TerraGelato</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>terragelato</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n"/>
-      <c r="K182" s="2" t="n"/>
-      <c r="L182" s="2" t="n"/>
-      <c r="M182" s="2" t="n"/>
-      <c r="N182" s="2" t="n"/>
-      <c r="O182" s="2" t="n"/>
-      <c r="P182" s="2" t="n"/>
-      <c r="Q182" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R182" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>Tra le righe Gelato &amp; Friends</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>Via Teodosio, 44</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>02/91762549</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" s="2" t="n"/>
-      <c r="F183" s="2" t="n"/>
-      <c r="G183" s="2" t="n"/>
-      <c r="H183" s="2" t="n"/>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n"/>
-      <c r="K183" s="2" t="n"/>
-      <c r="L183" s="2" t="n"/>
-      <c r="M183" s="2" t="n"/>
-      <c r="N183" s="2" t="n"/>
-      <c r="O183" s="2" t="n"/>
-      <c r="P183" s="2" t="n"/>
-      <c r="Q183" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R183" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Ripa di Porta Ticinese, 2</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>02/91570928</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>www.trapizzino.it</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>trapizzino</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>trapizzino</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n"/>
-      <c r="K184" s="2" t="n"/>
-      <c r="L184" s="2" t="n"/>
-      <c r="M184" s="2" t="n"/>
-      <c r="N184" s="2" t="n"/>
-      <c r="O184" s="2" t="n"/>
-      <c r="P184" s="2" t="n"/>
-      <c r="Q184" s="2" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R184" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -6557,44 +6557,62 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>Coffee Studio 7gr.</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>Corso Venezia, 31</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>02/38238682</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
-      <c r="F103" s="1" t="inlineStr"/>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J103" s="1" t="inlineStr"/>
-      <c r="K103" s="1" t="inlineStr"/>
-      <c r="L103" s="1" t="inlineStr"/>
-      <c r="M103" s="1" t="inlineStr"/>
-      <c r="N103" s="1" t="inlineStr"/>
-      <c r="O103" s="1" t="inlineStr"/>
-      <c r="P103" s="1" t="inlineStr"/>
-      <c r="Q103" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Égalité</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Via Melzo, 22</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>02/91763465</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>www.egalitemilano.it</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>egalitemilano</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>egalite_milano</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (egalitemilano) | IG: trovato (egalite_milano)</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -6603,32 +6621,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Égalité</t>
+          <t>Fòla</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Via Melzo, 22</t>
+          <t>Via Luigi Varanini, 12</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>02/91763465</t>
+          <t>02/49713413</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>www.egalitemilano.it</t>
+          <t>www.folamilano.com</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>egalitemilano</t>
+          <t>fola.milano.nolo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>egalite_milano</t>
+          <t>fola.milano</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6646,6 +6664,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '18'}, 'mer</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>Si</t>
@@ -6653,7 +6681,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (egalitemilano) | IG: trovato (egalite_milano)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (fola.milano.nolo) | IG: trovato (fola.milano)</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -6665,42 +6693,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Fòla</t>
+          <t>I Dolci Namura</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Via Luigi Varanini, 12</t>
+          <t>Via Lodovico Castelvetro, 16</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>02/49713413</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>www.folamilano.com</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>fola.milano.nolo</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>fola.milano</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/34534176</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6715,17 +6718,12 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '18'}, 'mer</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07:30', 'closes': '20'}, '</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (fola.milano.nolo) | IG: trovato (fola.milano)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -6737,17 +6735,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>I Dolci Namura</t>
+          <t>La Bruma</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Via Lodovico Castelvetro, 16</t>
+          <t>Piazza Vetra, 21</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>02/34534176</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6762,12 +6760,12 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07:30', 'closes': '20'}, '</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '19'}, 'martedì': {'opens': '08', 'closes':</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -6779,17 +6777,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>La Bruma</t>
+          <t>La Mary</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Piazza Vetra, 21</t>
+          <t>Via Marcona, 70</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>02/36599229</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6804,12 +6802,12 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '19'}, 'martedì': {'opens': '08', 'closes':</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07', 'closes': '20'}, 'mer</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -6821,17 +6819,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>La Mary</t>
+          <t>Le Polveri - panificio diurno</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Via Marcona, 70</t>
+          <t>Via Vespri Siciliani, 16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>02/36599229</t>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>www.lepolveri.com</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>lepolveri</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6846,12 +6859,17 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '07', 'closes': '20'}, 'mer</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '18:30'}, '</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (lepolveri)</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -6863,27 +6881,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Le Polveri - panificio diurno</t>
+          <t>L'ile Douce</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Via Vespri Siciliani, 16</t>
+          <t>Via Luigi Porro Lambertenghi, 15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>02/49780658</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>www.lepolveri.com</t>
+          <t>www.iledoucemilano.it</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>iledoucemilano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>lepolveri</t>
+          <t>iledoucemilano</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6901,11 +6929,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '18:30'}, '</t>
-        </is>
-      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Si</t>
@@ -6913,7 +6936,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (lepolveri)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (iledoucemilano) | IG: trovato (iledoucemilano)</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -6925,32 +6948,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>L'ile Douce</t>
+          <t>Loste Cafè</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Via Luigi Porro Lambertenghi, 15</t>
+          <t>Via Francesco Guicciardini, 3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>02/49780658</t>
+          <t>02/45375475</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>www.iledoucemilano.it</t>
+          <t>www.lostecafe.com</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>iledoucemilano</t>
+          <t>lostecafemilano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>iledoucemilano</t>
+          <t>lostecafemilano</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6968,11 +6991,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Si</t>
@@ -6980,7 +6998,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (iledoucemilano) | IG: trovato (iledoucemilano)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lostecafemilano) | IG: trovato (lostecafemilano)</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -6992,32 +7010,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Loste Cafè</t>
+          <t>Marlà</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Via Francesco Guicciardini, 3</t>
+          <t>Corso Lodi, 15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>02/45375475</t>
+          <t>02/36536410</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>www.lostecafe.com</t>
+          <t>www.marlapasticceria.it</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>lostecafemilano</t>
+          <t>creiamodolcienonsolo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>lostecafemilano</t>
+          <t>marlapasticceria</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7035,6 +7053,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '19'}, 'mer</t>
+        </is>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7042,7 +7070,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lostecafemilano) | IG: trovato (lostecafemilano)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (creiamodolcienonsolo) | IG: trovato (marlapasticceria)</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -7054,32 +7082,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Marlà</t>
+          <t>Nowhere - Coffee &amp; Community</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corso Lodi, 15</t>
+          <t>Via Vetere, 14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>02/36536410</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>www.marlapasticceria.it</t>
+          <t>389/1078092</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>creiamodolcienonsolo</t>
+          <t>nowherecafe.it</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>marlapasticceria</t>
+          <t>nowherecafe.milano</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7104,7 +7127,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '19'}, 'mer</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08:30', 'closes': '16'}, '</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -7114,7 +7137,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (creiamodolcienonsolo) | IG: trovato (marlapasticceria)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (nowherecafe.it) | IG: trovato (nowherecafe.milano)</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -7126,27 +7149,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Nowhere - Coffee &amp; Community</t>
+          <t>Orsonero Coffee</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Via Vetere, 14</t>
+          <t>Via Giuseppe Broggi, 15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>389/1078092</t>
+          <t>366/5477441</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>www.orsonerocoffee.it</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>nowherecafe.it</t>
+          <t>orsonerocoffee</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>nowherecafe.milano</t>
+          <t>orsonerocoffee</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7171,7 +7199,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08:30', 'closes': '16'}, '</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '17'}, 'mer</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -7181,7 +7209,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (nowherecafe.it) | IG: trovato (nowherecafe.milano)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (orsonerocoffee) | IG: trovato (orsonerocoffee)</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -7193,42 +7221,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Orsonero Coffee</t>
+          <t>Sfoglia Pastry Lab</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Via Giuseppe Broggi, 15</t>
+          <t>Via Nicola Piccinni, 3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>366/5477441</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>www.orsonerocoffee.it</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>orsonerocoffee</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>orsonerocoffee</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>345/1662856</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7243,17 +7246,12 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '17'}, 'mer</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '21'}, 'martedì': {'opens': '08', 'closes':</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (orsonerocoffee) | IG: trovato (orsonerocoffee)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -7265,17 +7263,42 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sfoglia Pastry Lab</t>
+          <t>Signor Lievito</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Via Nicola Piccinni, 3</t>
+          <t>Via Maestri Campionesi, 26</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>345/1662856</t>
+          <t>02/91678209</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>www.signor-lievito.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>signorlievito</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>signor_lievito</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7290,12 +7313,17 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '21'}, 'martedì': {'opens': '08', 'closes':</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '16'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (signorlievito) | IG: trovato (signor_lievito)</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -7307,32 +7335,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Signor Lievito</t>
+          <t>Tre Chicchere</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Via Maestri Campionesi, 26</t>
+          <t>Via Gian Antonio Boltraffio, 12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>02/91678209</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>www.signor-lievito.com</t>
+          <t>02/69007248</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>signorlievito</t>
+          <t>Trechicchere</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>signor_lievito</t>
+          <t>trechicchere</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7357,7 +7380,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '16'}, 'mer</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '13'}, 'martedì': {'opens': '08, 13:30', 'c</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -7367,7 +7390,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (signorlievito) | IG: trovato (signor_lievito)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (Trechicchere) | IG: trovato (trechicchere)</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -7379,27 +7402,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tre Chicchere</t>
+          <t>Ziva</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Via Gian Antonio Boltraffio, 12</t>
+          <t>Via Federico Faruffini, 2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>02/69007248</t>
+          <t>02/99266436</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>www.zivapasticceria.it</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trechicchere</t>
+          <t>zivapasticceria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>trechicchere</t>
+          <t>zivapasticceria</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7417,16 +7445,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '13'}, 'martedì': {'opens': '08, 13:30', 'c</t>
-        </is>
-      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7434,7 +7452,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (Trechicchere) | IG: trovato (trechicchere)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (zivapasticceria) | IG: trovato (zivapasticceria)</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -7446,32 +7464,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ziva</t>
+          <t>Gastronomia Yamamoto</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Via Federico Faruffini, 2</t>
+          <t>Via Amedei, 5</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>02/99266436</t>
+          <t>02/36741426</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>www.zivapasticceria.it</t>
+          <t>www.gastronomiayamamoto.it</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>zivapasticceria</t>
+          <t>gastronomiayamamoto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>zivapasticceria</t>
+          <t>gastronomiayamamoto</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7489,6 +7507,11 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7496,7 +7519,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (zivapasticceria) | IG: trovato (zivapasticceria)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gastronomiayamamoto) | IG: trovato (gastronomiayamamoto)</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -7508,42 +7531,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Gastronomia Yamamoto</t>
+          <t>Hygge</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Via Amedei, 5</t>
+          <t>Via Giuseppe Sapeto, 3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>02/36741426</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>www.gastronomiayamamoto.it</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>gastronomiayamamoto</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>gastronomiayamamoto</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7556,14 +7554,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gastronomiayamamoto) | IG: trovato (gastronomiayamamoto)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -7575,12 +7568,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hygge</t>
+          <t>June Collective</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Via Giuseppe Sapeto, 3</t>
+          <t>Via Varesina, 162 c/o Certosa District</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7588,6 +7581,16 @@
           <t>n.d.</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>junecollectivemilano</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7598,9 +7601,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '09:30', 'closes': '15'}, 'martedì': {'opens': '09:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (junecollectivemilano)</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -7612,12 +7625,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>June Collective</t>
+          <t>Katsusanderia</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Via Varesina, 162 c/o Certosa District</t>
+          <t>Via Bonvesin de la Riva, 3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7625,9 +7638,24 @@
           <t>n.d.</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>www.katsusanderia.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>profile.php?id=100083562601123</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>junecollectivemilano</t>
+          <t>katsusanderia</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7647,7 +7675,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '09:30', 'closes': '15'}, 'martedì': {'opens': '09:30', 'cl</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19', 'closes': '15, 23</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -7657,7 +7685,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (junecollectivemilano)</t>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100083562601123) | IG: trovato (katsusanderia)</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -7669,32 +7697,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Katsusanderia</t>
+          <t>La Ravioleria Sarpi</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Via Bonvesin de la Riva, 3</t>
+          <t>Via Paolo Sarpi, 27</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>331/8870596</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>www.katsusanderia.com</t>
+          <t>www.laravioleriasarpi.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>profile.php?id=100083562601123</t>
+          <t>ravioleriasarpi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>katsusanderia</t>
+          <t>laravioleriasarpi</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7719,7 +7747,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19', 'closes': '15, 23</t>
+          <t>{'lunedì': {'opens': '10:30, 16', 'closes': '15, 22', 'break': '15–16'}, 'marted</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -7729,7 +7757,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100083562601123) | IG: trovato (katsusanderia)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ravioleriasarpi) | IG: trovato (laravioleriasarpi)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -7741,32 +7769,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>La Ravioleria Sarpi</t>
+          <t>Li - Sei Deli</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Via Paolo Sarpi, 27</t>
+          <t>Via Vigevano, 9</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>331/8870596</t>
+          <t>02/49775083</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>www.laravioleriasarpi.com</t>
+          <t>www.lisei.it</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ravioleriasarpi</t>
+          <t>Li-Sei Deli</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>laravioleriasarpi</t>
+          <t>liseideli</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7791,7 +7819,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '10:30, 16', 'closes': '15, 22', 'break': '15–16'}, 'marted</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -7801,7 +7829,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ravioleriasarpi) | IG: trovato (laravioleriasarpi)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Li-Sei Deli) | IG: trovato (liseideli)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -7813,42 +7841,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Li - Sei Deli</t>
+          <t>Lile in cucina</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Via Vigevano, 9</t>
+          <t>Piazza Carlo Maciachini, 18</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>02/49775083</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>www.lisei.it</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Li-Sei Deli</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>liseideli</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/36735997</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7863,17 +7866,12 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '08:30', 'closes': '19'}, 'martedì': {'opens': '08:30', 'cl</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Li-Sei Deli) | IG: trovato (liseideli)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -7885,17 +7883,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lile in cucina</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Piazza Carlo Maciachini, 18</t>
+          <t>Via Leopoldo Cicognara, 19</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>02/36735997</t>
+          <t>340/8551831</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>www.panmilano.com</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>panmilano</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7910,12 +7923,17 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08:30', 'closes': '19'}, 'martedì': {'opens': '08:30', 'cl</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '17'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (panmilano)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -7927,32 +7945,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Rito</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Via Leopoldo Cicognara, 19</t>
+          <t>Porta Venezia</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>340/8551831</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>www.panmilano.com</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>panmilano</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/38241909</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7967,17 +7970,12 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '17'}, 'martedì': {'opens': '08', 'closes':</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '08', 'closes': '16'}, 'martedì': {'opens': '08', 'closes':</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (panmilano)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -7989,17 +7987,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Rito</t>
+          <t>Sandì</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Porta Venezia</t>
+          <t>Via Francesco Hayez, 13</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>02/38241909</t>
+          <t>02/82046200</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>sandi_ristorante</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8014,12 +8022,17 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '16'}, 'martedì': {'opens': '08', 'closes':</t>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '15'}, 'martedì': {'opens': 'Chiuso'}, '</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (sandi_ristorante)</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -8031,22 +8044,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sandì</t>
+          <t>Stadera - gastronomia contemporanea</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Via Francesco Hayez, 13</t>
+          <t>Largo della Crocetta, 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>02/82046200</t>
+          <t>340/6056240</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>staderamilano</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>sandi_ristorante</t>
+          <t>stadera_milano</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8066,7 +8089,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30', 'closes': '15'}, 'martedì': {'opens': 'Chiuso'}, '</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '11:30, 18', 'closes': '15,</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8076,7 +8099,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (sandi_ristorante)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (staderamilano) | IG: trovato (stadera_milano)</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -8088,27 +8111,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Stadera - gastronomia contemporanea</t>
+          <t>Tone - Bread Lab.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Largo della Crocetta, 1</t>
+          <t>Via Donatello, 22</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>340/6056240</t>
+          <t>351/8731109</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>staderamilano</t>
+          <t>tone.milano.breadlab</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>stadera_milano</t>
+          <t>tone.milano</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8133,7 +8156,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '11:30, 18', 'closes': '15,</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8143,7 +8166,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (staderamilano) | IG: trovato (stadera_milano)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (tone.milano.breadlab) | IG: trovato (tone.milano)</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -8155,32 +8178,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tone - Bread Lab.</t>
+          <t>Via Stampa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Via Donatello, 22</t>
+          <t>Via Stampa, 8</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>351/8731109</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>tone.milano.breadlab</t>
+          <t>02/30554088</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>www.viastampa.it</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>tone.milano</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>viastampa_milano</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8198,11 +8216,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
-        </is>
-      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8210,7 +8223,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (tone.milano.breadlab) | IG: trovato (tone.milano)</t>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (viastampa_milano)</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -8222,27 +8235,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Via Stampa</t>
+          <t>Zibo - campo base</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Via Stampa, 8</t>
+          <t>Via Caminadella, 21</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>02/30554088</t>
+          <t>02/35999463</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>www.viastampa.it</t>
+          <t>www.zibocuochiitineranti.it</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>zibocuochi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>viastampa_milano</t>
+          <t>zibocuochi</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8260,6 +8283,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8267,7 +8295,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (viastampa_milano)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (zibocuochi) | IG: trovato (zibocuochi)</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -8279,42 +8307,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Zibo - campo base</t>
+          <t>La Medina</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Via Caminadella, 21</t>
+          <t>Via Tolentino, 1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>02/35999463</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>www.zibocuochiitineranti.it</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>zibocuochi</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>zibocuochi</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>388/7940829</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8327,19 +8330,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (zibocuochi) | IG: trovato (zibocuochi)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -8351,17 +8344,42 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>La Medina</t>
+          <t>La Teiera Eclettica</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Via Tolentino, 1</t>
+          <t>Via Melzo, 30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>388/7940829</t>
+          <t>02/29419101</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>www.teieraeclettica.it</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LaTeieraEclettica</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>la_teiera_eclettica</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8374,9 +8392,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10, 14:45', 'closes': '13:</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (LaTeieraEclettica) | IG: trovato (la_teiera_eclettica)</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -8388,42 +8416,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>La Teiera Eclettica</t>
+          <t>Momenteeria</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Via Melzo, 30</t>
+          <t>Via Giosuè Carducci, 38</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>02/29419101</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>www.teieraeclettica.it</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>LaTeieraEclettica</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>la_teiera_eclettica</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>02/36532185</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8438,908 +8441,931 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10, 14:45', 'closes': '13:</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '20'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Coffee Studio 7gr.</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>Corso Venezia, 31</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>02/38238682</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr"/>
+      <c r="G135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
+      <c r="L135" s="1" t="inlineStr"/>
+      <c r="M135" s="1" t="inlineStr"/>
+      <c r="N135" s="1" t="inlineStr"/>
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R135" s="1" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Pasticceria Passerini dal 1919</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Via Victor Hugo, 4</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>02/8693614</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>www.passerinilecco.it</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>pasticceriapasserini</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (LaTeieraEclettica) | IG: trovato (la_teiera_eclettica)</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (pasticceriapasserini)</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Momenteeria</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Via Giosuè Carducci, 38</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>02/36532185</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Brylla</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Via Giovanni Rasori, 12</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>02/64089167</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '20'}, 'mer</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17', 'closes': '22'}, 'martedì': {'opens': '17', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>Pasticceria Passerini dal 1919</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>Via Victor Hugo, 4</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>02/8693614</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="inlineStr">
-        <is>
-          <t>www.passerinilecco.it</t>
-        </is>
-      </c>
-      <c r="E136" s="1" t="inlineStr"/>
-      <c r="F136" s="1" t="inlineStr">
-        <is>
-          <t>pasticceriapasserini</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="inlineStr"/>
-      <c r="H136" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J136" s="1" t="inlineStr"/>
-      <c r="K136" s="1" t="inlineStr"/>
-      <c r="L136" s="1" t="inlineStr"/>
-      <c r="M136" s="1" t="inlineStr"/>
-      <c r="N136" s="1" t="inlineStr"/>
-      <c r="O136" s="1" t="inlineStr"/>
-      <c r="P136" s="1" t="inlineStr"/>
-      <c r="Q136" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R136" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>Brylla</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>Via Giovanni Rasori, 12</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>02/64089167</t>
-        </is>
-      </c>
-      <c r="D137" s="1" t="inlineStr"/>
-      <c r="E137" s="1" t="inlineStr"/>
-      <c r="F137" s="1" t="inlineStr"/>
-      <c r="G137" s="1" t="inlineStr"/>
-      <c r="H137" s="1" t="inlineStr"/>
-      <c r="I137" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J137" s="1" t="inlineStr"/>
-      <c r="K137" s="1" t="inlineStr"/>
-      <c r="L137" s="1" t="inlineStr"/>
-      <c r="M137" s="1" t="inlineStr"/>
-      <c r="N137" s="1" t="inlineStr"/>
-      <c r="O137" s="1" t="inlineStr"/>
-      <c r="P137" s="1" t="inlineStr"/>
-      <c r="Q137" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R137" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
     <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Cantine Isola</t>
         </is>
       </c>
-      <c r="B138" s="1" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Via Paolo Sarpi, 30</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>02/3315249</t>
         </is>
       </c>
-      <c r="D138" s="1" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>www.cantineisola.com</t>
         </is>
       </c>
-      <c r="E138" s="1" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>cantineisola</t>
         </is>
       </c>
-      <c r="F138" s="1" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>cantine_isola</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H138" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I138" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J138" s="1" t="inlineStr"/>
-      <c r="K138" s="1" t="inlineStr"/>
-      <c r="L138" s="1" t="inlineStr"/>
-      <c r="M138" s="1" t="inlineStr"/>
-      <c r="N138" s="1" t="inlineStr"/>
-      <c r="O138" s="1" t="inlineStr"/>
-      <c r="P138" s="1" t="inlineStr"/>
-      <c r="Q138" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R138" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cantineisola) | IG: trovato (cantine_isola)</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Ceresio 7</t>
         </is>
       </c>
-      <c r="B139" s="1" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Via Ceresio, 7</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>02/31039221</t>
         </is>
       </c>
-      <c r="D139" s="1" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>www.ceresio7.com</t>
         </is>
       </c>
-      <c r="E139" s="1" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="F139" s="1" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>ceresio7</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J139" s="1" t="inlineStr"/>
-      <c r="K139" s="1" t="inlineStr"/>
-      <c r="L139" s="1" t="inlineStr"/>
-      <c r="M139" s="1" t="inlineStr"/>
-      <c r="N139" s="1" t="inlineStr"/>
-      <c r="O139" s="1" t="inlineStr"/>
-      <c r="P139" s="1" t="inlineStr"/>
-      <c r="Q139" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R139" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '01'}, 'martedì': {'opens': '12:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (ceresio7) | IG: trovato (ceresio7)</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Cru</t>
         </is>
       </c>
-      <c r="B140" s="1" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Piazza Sempione, 6</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>342/3040081</t>
         </is>
       </c>
-      <c r="D140" s="1" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>www.crumilano.com</t>
         </is>
       </c>
-      <c r="E140" s="1" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>crumilanowinebar</t>
         </is>
       </c>
-      <c r="F140" s="1" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>cru_milano</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J140" s="1" t="inlineStr"/>
-      <c r="K140" s="1" t="inlineStr"/>
-      <c r="L140" s="1" t="inlineStr"/>
-      <c r="M140" s="1" t="inlineStr"/>
-      <c r="N140" s="1" t="inlineStr"/>
-      <c r="O140" s="1" t="inlineStr"/>
-      <c r="P140" s="1" t="inlineStr"/>
-      <c r="Q140" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R140" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (crumilanowinebar) | IG: trovato (cru_milano)</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Enoteca Naturale</t>
         </is>
       </c>
-      <c r="B141" s="1" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Via Santa Croce, 19/A</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>02/82770589</t>
         </is>
       </c>
-      <c r="D141" s="1" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>www.enotecanaturale.it</t>
         </is>
       </c>
-      <c r="E141" s="1" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="F141" s="1" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>enotecanaturale</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J141" s="1" t="inlineStr"/>
-      <c r="K141" s="1" t="inlineStr"/>
-      <c r="L141" s="1" t="inlineStr"/>
-      <c r="M141" s="1" t="inlineStr"/>
-      <c r="N141" s="1" t="inlineStr"/>
-      <c r="O141" s="1" t="inlineStr"/>
-      <c r="P141" s="1" t="inlineStr"/>
-      <c r="Q141" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R141" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (enotecanaturale) | IG: trovato (enotecanaturale)</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Flor. | born to be wine</t>
         </is>
       </c>
-      <c r="B142" s="1" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Via Vigevano, 6</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>340/8587572</t>
         </is>
       </c>
-      <c r="D142" s="1" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>www.florwine.com</t>
         </is>
       </c>
-      <c r="E142" s="1" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>milanoflor</t>
         </is>
       </c>
-      <c r="F142" s="1" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>florenoteca.milano</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J142" s="1" t="inlineStr"/>
-      <c r="K142" s="1" t="inlineStr"/>
-      <c r="L142" s="1" t="inlineStr"/>
-      <c r="M142" s="1" t="inlineStr"/>
-      <c r="N142" s="1" t="inlineStr"/>
-      <c r="O142" s="1" t="inlineStr"/>
-      <c r="P142" s="1" t="inlineStr"/>
-      <c r="Q142" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R142" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (milanoflor) | IG: trovato (florenoteca.milano)</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Mesté - vino e fornelli</t>
         </is>
       </c>
-      <c r="B143" s="1" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Via Corrado II il Salico, 12</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>346/8061538</t>
         </is>
       </c>
-      <c r="D143" s="1" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>www.meste.it</t>
         </is>
       </c>
-      <c r="E143" s="1" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="F143" s="1" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>mestemilano</t>
         </is>
       </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J143" s="1" t="inlineStr"/>
-      <c r="K143" s="1" t="inlineStr"/>
-      <c r="L143" s="1" t="inlineStr"/>
-      <c r="M143" s="1" t="inlineStr"/>
-      <c r="N143" s="1" t="inlineStr"/>
-      <c r="O143" s="1" t="inlineStr"/>
-      <c r="P143" s="1" t="inlineStr"/>
-      <c r="Q143" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R143" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 18:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (mestemilano) | IG: trovato (mestemilano)</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Millésime 1990 - sorsi di Francia</t>
         </is>
       </c>
-      <c r="B144" s="1" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Via Raffaello Sanzio, 4</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>02/36534945</t>
         </is>
       </c>
-      <c r="D144" s="1" t="inlineStr"/>
-      <c r="E144" s="1" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J144" s="1" t="inlineStr"/>
-      <c r="K144" s="1" t="inlineStr"/>
-      <c r="L144" s="1" t="inlineStr"/>
-      <c r="M144" s="1" t="inlineStr"/>
-      <c r="N144" s="1" t="inlineStr"/>
-      <c r="O144" s="1" t="inlineStr"/>
-      <c r="P144" s="1" t="inlineStr"/>
-      <c r="Q144" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R144" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Nik’s &amp; Co</t>
         </is>
       </c>
-      <c r="B145" s="1" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Via Giovanni Schiaparelli, 14</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>02/91571797</t>
         </is>
       </c>
-      <c r="D145" s="1" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>www.niksandco.it</t>
         </is>
       </c>
-      <c r="E145" s="1" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>niksandco</t>
         </is>
       </c>
-      <c r="F145" s="1" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>niks_co</t>
         </is>
       </c>
-      <c r="G145" s="1" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>01/02/2026</t>
         </is>
       </c>
-      <c r="H145" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J145" s="1" t="inlineStr"/>
-      <c r="K145" s="1" t="inlineStr"/>
-      <c r="L145" s="1" t="inlineStr"/>
-      <c r="M145" s="1" t="inlineStr"/>
-      <c r="N145" s="1" t="inlineStr"/>
-      <c r="O145" s="1" t="inlineStr"/>
-      <c r="P145" s="1" t="inlineStr"/>
-      <c r="Q145" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R145" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (niksandco) | IG: trovato (niks_co)</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Shiua</t>
         </is>
       </c>
-      <c r="B146" s="1" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Via Solari, 43</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>345/0229180</t>
         </is>
       </c>
-      <c r="D146" s="1" t="inlineStr"/>
-      <c r="E146" s="1" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J146" s="1" t="inlineStr"/>
-      <c r="K146" s="1" t="inlineStr"/>
-      <c r="L146" s="1" t="inlineStr"/>
-      <c r="M146" s="1" t="inlineStr"/>
-      <c r="N146" s="1" t="inlineStr"/>
-      <c r="O146" s="1" t="inlineStr"/>
-      <c r="P146" s="1" t="inlineStr"/>
-      <c r="Q146" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R146" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Tipografia Alimentare</t>
         </is>
       </c>
-      <c r="B147" s="1" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Via Dolomiti, 1</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>02/83537868</t>
         </is>
       </c>
-      <c r="D147" s="1" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>www.tipografiaalimentare.it</t>
         </is>
       </c>
-      <c r="E147" s="1" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="F147" s="1" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>tipografiaalimentare</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J147" s="1" t="inlineStr"/>
-      <c r="K147" s="1" t="inlineStr"/>
-      <c r="L147" s="1" t="inlineStr"/>
-      <c r="M147" s="1" t="inlineStr"/>
-      <c r="N147" s="1" t="inlineStr"/>
-      <c r="O147" s="1" t="inlineStr"/>
-      <c r="P147" s="1" t="inlineStr"/>
-      <c r="Q147" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R147" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (tipografiaalimentare) | IG: trovato (tipografiaalimentare)</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Vineria Eretica</t>
         </is>
       </c>
-      <c r="B148" s="1" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Via Rosolino Pilo, 14</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>02/45942171</t>
         </is>
       </c>
-      <c r="D148" s="1" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>www.vineriaeretica.it</t>
         </is>
       </c>
-      <c r="E148" s="1" t="inlineStr"/>
-      <c r="F148" s="1" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>vineriaeretica</t>
         </is>
       </c>
-      <c r="G148" s="1" t="inlineStr"/>
-      <c r="H148" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I148" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J148" s="1" t="inlineStr"/>
-      <c r="K148" s="1" t="inlineStr"/>
-      <c r="L148" s="1" t="inlineStr"/>
-      <c r="M148" s="1" t="inlineStr"/>
-      <c r="N148" s="1" t="inlineStr"/>
-      <c r="O148" s="1" t="inlineStr"/>
-      <c r="P148" s="1" t="inlineStr"/>
-      <c r="Q148" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R148" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': '18', 'close</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (vineriaeretica)</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>Vinodromo</t>
         </is>
       </c>
-      <c r="B149" s="1" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Via Salasco, 21</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>02/32960708</t>
         </is>
       </c>
-      <c r="D149" s="1" t="inlineStr"/>
-      <c r="E149" s="1" t="inlineStr"/>
-      <c r="F149" s="1" t="inlineStr"/>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J149" s="1" t="inlineStr"/>
-      <c r="K149" s="1" t="inlineStr"/>
-      <c r="L149" s="1" t="inlineStr"/>
-      <c r="M149" s="1" t="inlineStr"/>
-      <c r="N149" s="1" t="inlineStr"/>
-      <c r="O149" s="1" t="inlineStr"/>
-      <c r="P149" s="1" t="inlineStr"/>
-      <c r="Q149" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R149" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>Wineria</t>
         </is>
       </c>
-      <c r="B150" s="1" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Piazza Carlo Caneva, 4</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>02/39464196</t>
         </is>
       </c>
-      <c r="D150" s="1" t="inlineStr"/>
-      <c r="E150" s="1" t="inlineStr"/>
-      <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr"/>
-      <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J150" s="1" t="inlineStr"/>
-      <c r="K150" s="1" t="inlineStr"/>
-      <c r="L150" s="1" t="inlineStr"/>
-      <c r="M150" s="1" t="inlineStr"/>
-      <c r="N150" s="1" t="inlineStr"/>
-      <c r="O150" s="1" t="inlineStr"/>
-      <c r="P150" s="1" t="inlineStr"/>
-      <c r="Q150" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R150" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '15', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -9378,1048 +9404,1113 @@
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>Osteria alla Concorrenza</t>
         </is>
       </c>
-      <c r="B152" s="1" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Via Melzo, 12</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>02/91672012</t>
         </is>
       </c>
-      <c r="D152" s="1" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>www.osteriaallaconcorrenza.superbexperience.com</t>
         </is>
       </c>
-      <c r="E152" s="1" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>osteriaallaconcorrenza</t>
         </is>
       </c>
-      <c r="F152" s="1" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>osteria_alla_concorrenza</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J152" s="1" t="inlineStr"/>
-      <c r="K152" s="1" t="inlineStr"/>
-      <c r="L152" s="1" t="inlineStr"/>
-      <c r="M152" s="1" t="inlineStr"/>
-      <c r="N152" s="1" t="inlineStr"/>
-      <c r="O152" s="1" t="inlineStr"/>
-      <c r="P152" s="1" t="inlineStr"/>
-      <c r="Q152" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R152" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriaallaconcorrenza) | IG: trovato (osteria_alla_concorrenza)</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>Palinurobar</t>
         </is>
       </c>
-      <c r="B153" s="1" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Via Giovanni Paisello, 28</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D153" s="1" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>www.palinurobar.it</t>
         </is>
       </c>
-      <c r="E153" s="1" t="inlineStr"/>
-      <c r="F153" s="1" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>palinurobar</t>
         </is>
       </c>
-      <c r="G153" s="1" t="inlineStr"/>
-      <c r="H153" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I153" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J153" s="1" t="inlineStr"/>
-      <c r="K153" s="1" t="inlineStr"/>
-      <c r="L153" s="1" t="inlineStr"/>
-      <c r="M153" s="1" t="inlineStr"/>
-      <c r="N153" s="1" t="inlineStr"/>
-      <c r="O153" s="1" t="inlineStr"/>
-      <c r="P153" s="1" t="inlineStr"/>
-      <c r="Q153" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R153" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17:45', 'closes': '00'}, 'martedì': {'opens': '17:45', 'cl</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (palinurobar)</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Porcobrado</t>
         </is>
       </c>
-      <c r="B154" s="1" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Via Jacopo dal Verme, 17</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>02/87030181 - 338/3339120</t>
         </is>
       </c>
-      <c r="D154" s="1" t="inlineStr"/>
-      <c r="E154" s="1" t="inlineStr"/>
-      <c r="F154" s="1" t="inlineStr"/>
-      <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J154" s="1" t="inlineStr"/>
-      <c r="K154" s="1" t="inlineStr"/>
-      <c r="L154" s="1" t="inlineStr"/>
-      <c r="M154" s="1" t="inlineStr"/>
-      <c r="N154" s="1" t="inlineStr"/>
-      <c r="O154" s="1" t="inlineStr"/>
-      <c r="P154" s="1" t="inlineStr"/>
-      <c r="Q154" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R154" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Silvano - vini e cibi al banco</t>
         </is>
       </c>
-      <c r="B155" s="1" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Piazza Morbegno, 2</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>02/72193827</t>
         </is>
       </c>
-      <c r="D155" s="1" t="inlineStr"/>
-      <c r="E155" s="1" t="inlineStr"/>
-      <c r="F155" s="1" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>silvano_viniecibi</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I155" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J155" s="1" t="inlineStr"/>
-      <c r="K155" s="1" t="inlineStr"/>
-      <c r="L155" s="1" t="inlineStr"/>
-      <c r="M155" s="1" t="inlineStr"/>
-      <c r="N155" s="1" t="inlineStr"/>
-      <c r="O155" s="1" t="inlineStr"/>
-      <c r="P155" s="1" t="inlineStr"/>
-      <c r="Q155" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R155" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (silvano_viniecibi)</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>Temp enoteca</t>
         </is>
       </c>
-      <c r="B156" s="1" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Via Pasquale Sottocorno, 17</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>347/2402269</t>
         </is>
       </c>
-      <c r="D156" s="1" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>www.tempenoteca.it</t>
         </is>
       </c>
-      <c r="E156" s="1" t="inlineStr"/>
-      <c r="F156" s="1" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>temp.enoteca</t>
         </is>
       </c>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I156" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J156" s="1" t="inlineStr"/>
-      <c r="K156" s="1" t="inlineStr"/>
-      <c r="L156" s="1" t="inlineStr"/>
-      <c r="M156" s="1" t="inlineStr"/>
-      <c r="N156" s="1" t="inlineStr"/>
-      <c r="O156" s="1" t="inlineStr"/>
-      <c r="P156" s="1" t="inlineStr"/>
-      <c r="Q156" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R156" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (temp.enoteca)</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>Kilburn</t>
         </is>
       </c>
-      <c r="B157" s="1" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Via Panfilo Castaldi, 35</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>02/36580751</t>
         </is>
       </c>
-      <c r="D157" s="1" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>www.kilburncocktailbarmilano.it</t>
         </is>
       </c>
-      <c r="E157" s="1" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>KilburnMilano</t>
         </is>
       </c>
-      <c r="F157" s="1" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>kilburn_milano</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I157" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J157" s="1" t="inlineStr"/>
-      <c r="K157" s="1" t="inlineStr"/>
-      <c r="L157" s="1" t="inlineStr"/>
-      <c r="M157" s="1" t="inlineStr"/>
-      <c r="N157" s="1" t="inlineStr"/>
-      <c r="O157" s="1" t="inlineStr"/>
-      <c r="P157" s="1" t="inlineStr"/>
-      <c r="Q157" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R157" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19', 'closes': '00'}, 'martedì': {'opens': '19', 'closes':</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (KilburnMilano) | IG: trovato (kilburn_milano)</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>Lacerba</t>
         </is>
       </c>
-      <c r="B158" s="1" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Via Orti, 4</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>02/ 545 5475</t>
         </is>
       </c>
-      <c r="D158" s="1" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>www.lacerba.it</t>
         </is>
       </c>
-      <c r="E158" s="1" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>lacerba.milano</t>
         </is>
       </c>
-      <c r="F158" s="1" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>lacerba.milano</t>
         </is>
       </c>
-      <c r="G158" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H158" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I158" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J158" s="1" t="inlineStr"/>
-      <c r="K158" s="1" t="inlineStr"/>
-      <c r="L158" s="1" t="inlineStr"/>
-      <c r="M158" s="1" t="inlineStr"/>
-      <c r="N158" s="1" t="inlineStr"/>
-      <c r="O158" s="1" t="inlineStr"/>
-      <c r="P158" s="1" t="inlineStr"/>
-      <c r="Q158" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R158" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lacerba.milano) | IG: trovato (lacerba.milano)</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>Mag cafè</t>
         </is>
       </c>
-      <c r="B159" s="1" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Ripa di Porta Ticinese, 3</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>02/39562875</t>
         </is>
       </c>
-      <c r="D159" s="1" t="inlineStr"/>
-      <c r="E159" s="1" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>magcafemilano</t>
         </is>
       </c>
-      <c r="F159" s="1" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>magcafe</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H159" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I159" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J159" s="1" t="inlineStr"/>
-      <c r="K159" s="1" t="inlineStr"/>
-      <c r="L159" s="1" t="inlineStr"/>
-      <c r="M159" s="1" t="inlineStr"/>
-      <c r="N159" s="1" t="inlineStr"/>
-      <c r="O159" s="1" t="inlineStr"/>
-      <c r="P159" s="1" t="inlineStr"/>
-      <c r="Q159" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R159" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '02'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (magcafemilano) | IG: trovato (magcafe)</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>Norah was drunk</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Via Nicola Antonio Porpora, 169</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>02/83428246 - 375/7746998</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr"/>
-      <c r="E160" s="1" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>norahwasdrunk</t>
         </is>
       </c>
-      <c r="F160" s="1" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>norah_milano</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J160" s="1" t="inlineStr"/>
-      <c r="K160" s="1" t="inlineStr"/>
-      <c r="L160" s="1" t="inlineStr"/>
-      <c r="M160" s="1" t="inlineStr"/>
-      <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr"/>
-      <c r="P160" s="1" t="inlineStr"/>
-      <c r="Q160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R160" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '02'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (norahwasdrunk) | IG: trovato (norah_milano)</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="inlineStr">
+      <c r="A161" t="inlineStr">
         <is>
           <t>Rita</t>
         </is>
       </c>
-      <c r="B161" s="1" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Via Angelo Fumagalli, 1</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>02/8372865</t>
         </is>
       </c>
-      <c r="D161" s="1" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>www.ritacocktails.com</t>
         </is>
       </c>
-      <c r="E161" s="1" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>RitaCocktails</t>
         </is>
       </c>
-      <c r="F161" s="1" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>ritacocktails</t>
         </is>
       </c>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H161" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I161" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J161" s="1" t="inlineStr"/>
-      <c r="K161" s="1" t="inlineStr"/>
-      <c r="L161" s="1" t="inlineStr"/>
-      <c r="M161" s="1" t="inlineStr"/>
-      <c r="N161" s="1" t="inlineStr"/>
-      <c r="O161" s="1" t="inlineStr"/>
-      <c r="P161" s="1" t="inlineStr"/>
-      <c r="Q161" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R161" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (RitaCocktails) | IG: trovato (ritacocktails)</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>Scott Bar</t>
         </is>
       </c>
-      <c r="B162" s="1" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Viale Bianca Maria, 4</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>02/00244399</t>
         </is>
       </c>
-      <c r="D162" s="1" t="inlineStr"/>
-      <c r="E162" s="1" t="inlineStr"/>
-      <c r="F162" s="1" t="inlineStr"/>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J162" s="1" t="inlineStr"/>
-      <c r="K162" s="1" t="inlineStr"/>
-      <c r="L162" s="1" t="inlineStr"/>
-      <c r="M162" s="1" t="inlineStr"/>
-      <c r="N162" s="1" t="inlineStr"/>
-      <c r="O162" s="1" t="inlineStr"/>
-      <c r="P162" s="1" t="inlineStr"/>
-      <c r="Q162" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R162" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12, 17', 'closes': '14:30, 01', 'break': '14:30–17'}, 'mar</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>Tripstillery</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Piazza Alvar Aalto, snc</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>02/62061443</t>
         </is>
       </c>
-      <c r="D163" s="1" t="inlineStr"/>
-      <c r="E163" s="1" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>tripstillery</t>
         </is>
       </c>
-      <c r="F163" s="1" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>tripstillery</t>
         </is>
       </c>
-      <c r="G163" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I163" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J163" s="1" t="inlineStr"/>
-      <c r="K163" s="1" t="inlineStr"/>
-      <c r="L163" s="1" t="inlineStr"/>
-      <c r="M163" s="1" t="inlineStr"/>
-      <c r="N163" s="1" t="inlineStr"/>
-      <c r="O163" s="1" t="inlineStr"/>
-      <c r="P163" s="1" t="inlineStr"/>
-      <c r="Q163" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R163" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (tripstillery) | IG: trovato (tripstillery)</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>Bonci - pizza in teglia</t>
         </is>
       </c>
-      <c r="B164" s="1" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Via Nicola Piccinni, 3</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>340/8223165</t>
         </is>
       </c>
-      <c r="D164" s="1" t="inlineStr"/>
-      <c r="E164" s="1" t="inlineStr"/>
-      <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr"/>
-      <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J164" s="1" t="inlineStr"/>
-      <c r="K164" s="1" t="inlineStr"/>
-      <c r="L164" s="1" t="inlineStr"/>
-      <c r="M164" s="1" t="inlineStr"/>
-      <c r="N164" s="1" t="inlineStr"/>
-      <c r="O164" s="1" t="inlineStr"/>
-      <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R164" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '21:30'}, 'martedì': {'opens': '11', 'close</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>Carmen Gelato</t>
         </is>
       </c>
-      <c r="B165" s="1" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Via Carlo Ravizza, 3</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>02/84230543</t>
         </is>
       </c>
-      <c r="D165" s="1" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>www.carmengelato.com</t>
         </is>
       </c>
-      <c r="E165" s="1" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>carmengelato.ita</t>
         </is>
       </c>
-      <c r="F165" s="1" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>carmen_gelato</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H165" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I165" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J165" s="1" t="inlineStr"/>
-      <c r="K165" s="1" t="inlineStr"/>
-      <c r="L165" s="1" t="inlineStr"/>
-      <c r="M165" s="1" t="inlineStr"/>
-      <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr"/>
-      <c r="P165" s="1" t="inlineStr"/>
-      <c r="Q165" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R165" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '13', 'closes': '22:30'}, 'martedì': {'opens': '13', 'close</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (carmengelato.ita) | IG: trovato (carmen_gelato)</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>Ciacco</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Via Spadari, 13</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>02/39663592</t>
         </is>
       </c>
-      <c r="D166" s="1" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>www.ciaccolab.it</t>
         </is>
       </c>
-      <c r="E166" s="1" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>ciaccogelato</t>
         </is>
       </c>
-      <c r="F166" s="1" t="inlineStr"/>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J166" s="1" t="inlineStr"/>
-      <c r="K166" s="1" t="inlineStr"/>
-      <c r="L166" s="1" t="inlineStr"/>
-      <c r="M166" s="1" t="inlineStr"/>
-      <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr"/>
-      <c r="P166" s="1" t="inlineStr"/>
-      <c r="Q166" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R166" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '15:30'}, 'martedì': {'opens': '12:30, 1</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (ciaccogelato) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>Gelateria LatteNeve</t>
         </is>
       </c>
-      <c r="B167" s="1" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Via Vigevano, 27</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>02/39811258</t>
         </is>
       </c>
-      <c r="D167" s="1" t="inlineStr"/>
-      <c r="E167" s="1" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>lattenevemilano</t>
         </is>
       </c>
-      <c r="F167" s="1" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>latteneve</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I167" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J167" s="1" t="inlineStr"/>
-      <c r="K167" s="1" t="inlineStr"/>
-      <c r="L167" s="1" t="inlineStr"/>
-      <c r="M167" s="1" t="inlineStr"/>
-      <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr"/>
-      <c r="P167" s="1" t="inlineStr"/>
-      <c r="Q167" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R167" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:45', 'closes': '22'}, 'martedì': {'opens': '12:45', 'cl</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattenevemilano) | IG: trovato (latteneve)</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>Gelateria Paganelli</t>
         </is>
       </c>
-      <c r="B168" s="1" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Via Adda, 3</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>02/42441183</t>
         </is>
       </c>
-      <c r="D168" s="1" t="inlineStr"/>
-      <c r="E168" s="1" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>gelateriapaganelli</t>
         </is>
       </c>
-      <c r="F168" s="1" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>gelateriapaganelli</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J168" s="1" t="inlineStr"/>
-      <c r="K168" s="1" t="inlineStr"/>
-      <c r="L168" s="1" t="inlineStr"/>
-      <c r="M168" s="1" t="inlineStr"/>
-      <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr"/>
-      <c r="P168" s="1" t="inlineStr"/>
-      <c r="Q168" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R168" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11:30', 'closes': '21:30'}, 'martedì': {'opens': '11:30',</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (gelateriapaganelli) | IG: trovato (gelateriapaganelli)</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Gelateria Prossima Fermata</t>
         </is>
       </c>
-      <c r="B169" s="1" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Via Melchiorre Gioia, 131</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>333/3112637</t>
         </is>
       </c>
-      <c r="D169" s="1" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>www.gelateria.company.site</t>
         </is>
       </c>
-      <c r="E169" s="1" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>gelateria.Prossima.Fermata</t>
         </is>
       </c>
-      <c r="F169" s="1" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>gelateria.prossima.fermata</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr"/>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R169" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateria.Prossima.Fermata) | IG: trovato (gelateria.prossima.fermata)</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
